--- a/Fractal Sweep/forward_test/forward_test_tracker.xlsx
+++ b/Fractal Sweep/forward_test/forward_test_tracker.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Trades" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="_Equity" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -103,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -122,8 +123,14 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -131,14 +138,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -242,7 +247,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Summary'!E12</f>
+              <f>'_Equity'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -260,7 +265,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Summary'!$E$13:$E$512</f>
+              <f>'_Equity'!$B$2:$B$501</f>
             </numRef>
           </val>
         </ser>
@@ -440,9 +445,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3600000"/>
@@ -11891,15 +11896,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F512"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11927,8 +11934,13 @@
           <t>Rolling windows</t>
         </is>
       </c>
-    </row>
-    <row r="5">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Forward-test status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Total trades logged</t>
@@ -11944,7 +11956,16 @@
         </is>
       </c>
       <c r="E5" s="11">
-        <f>IFERROR(COUNTIFS(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-30),0,MIN(30,COUNTA(Trades!M2:M501)),1),"WIN")/(COUNTIFS(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-30),0,MIN(30,COUNTA(Trades!M2:M501)),1),"WIN")+COUNTIFS(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-30),0,MIN(30,COUNTA(Trades!M2:M501)),1),"LOSS")),0)</f>
+        <f>IFERROR(COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-30),0,MIN(30,COUNTA(Trades!M2:M501)),1),"WIN")/(COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-30),0,MIN(30,COUNTA(Trades!M2:M501)),1),"WIN")+COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-30),0,MIN(30,COUNTA(Trades!M2:M501)),1),"LOSS")),0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H5" s="12">
+        <f>IF(B5&lt;30,"⏳ Noise — keep tracking",IF(B5&lt;100,"📊 Trend — too early to call",IF(B10&lt;0.45,"🛑 STOP — WR below 45%",IF(B11&lt;0,"🛑 STOP — EV negative","✓ On track"))))</f>
         <v/>
       </c>
     </row>
@@ -11963,8 +11984,17 @@
           <t>Last 30 — EV</t>
         </is>
       </c>
-      <c r="E6" s="12">
-        <f>IFERROR(SUMPRODUCT(OFFSET(Trades!N2,MAX(0,COUNTA(Trades!M2:M501)-30),0,MIN(30,COUNTA(Trades!M2:M501)),1))/MIN(30,COUNTA(Trades!M2:M501)),0)</f>
+      <c r="E6" s="13">
+        <f>IFERROR(SUM(OFFSET(Trades!N2,MAX(0,COUNTA(Trades!M2:M501)-30),0,MIN(30,COUNTA(Trades!M2:M501)),1))/(COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-30),0,MIN(30,COUNTA(Trades!M2:M501)),1),"WIN")+COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-30),0,MIN(30,COUNTA(Trades!M2:M501)),1),"LOSS")+COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-30),0,MIN(30,COUNTA(Trades!M2:M501)),1),"BE")),0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Trades to next phase</t>
+        </is>
+      </c>
+      <c r="H6" s="14">
+        <f>IF(B5&lt;30,"~"&amp;(30-B5)&amp;" more for trend signal",IF(B5&lt;100,"~"&amp;(100-B5)&amp;" more for early call",IF(B5&lt;200,"~"&amp;(200-B5)&amp;" more for robust validation","Validated")))</f>
         <v/>
       </c>
     </row>
@@ -11984,7 +12014,7 @@
         </is>
       </c>
       <c r="E7" s="11">
-        <f>IFERROR(COUNTIFS(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-50),0,MIN(50,COUNTA(Trades!M2:M501)),1),"WIN")/(COUNTIFS(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-50),0,MIN(50,COUNTA(Trades!M2:M501)),1),"WIN")+COUNTIFS(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-50),0,MIN(50,COUNTA(Trades!M2:M501)),1),"LOSS")),0)</f>
+        <f>IFERROR(COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-50),0,MIN(50,COUNTA(Trades!M2:M501)),1),"WIN")/(COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-50),0,MIN(50,COUNTA(Trades!M2:M501)),1),"WIN")+COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-50),0,MIN(50,COUNTA(Trades!M2:M501)),1),"LOSS")),0)</f>
         <v/>
       </c>
     </row>
@@ -12003,8 +12033,8 @@
           <t>Last 50 — EV</t>
         </is>
       </c>
-      <c r="E8" s="12">
-        <f>IFERROR(SUMPRODUCT(OFFSET(Trades!N2,MAX(0,COUNTA(Trades!M2:M501)-50),0,MIN(50,COUNTA(Trades!M2:M501)),1))/MIN(50,COUNTA(Trades!M2:M501)),0)</f>
+      <c r="E8" s="13">
+        <f>IFERROR(SUM(OFFSET(Trades!N2,MAX(0,COUNTA(Trades!M2:M501)-50),0,MIN(50,COUNTA(Trades!M2:M501)),1))/(COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-50),0,MIN(50,COUNTA(Trades!M2:M501)),1),"WIN")+COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-50),0,MIN(50,COUNTA(Trades!M2:M501)),1),"LOSS")+COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-50),0,MIN(50,COUNTA(Trades!M2:M501)),1),"BE")),0)</f>
         <v/>
       </c>
     </row>
@@ -12024,7 +12054,7 @@
         </is>
       </c>
       <c r="E9" s="11">
-        <f>IFERROR(COUNTIFS(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-100),0,MIN(100,COUNTA(Trades!M2:M501)),1),"WIN")/(COUNTIFS(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-100),0,MIN(100,COUNTA(Trades!M2:M501)),1),"WIN")+COUNTIFS(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-100),0,MIN(100,COUNTA(Trades!M2:M501)),1),"LOSS")),0)</f>
+        <f>IFERROR(COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-100),0,MIN(100,COUNTA(Trades!M2:M501)),1),"WIN")/(COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-100),0,MIN(100,COUNTA(Trades!M2:M501)),1),"WIN")+COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-100),0,MIN(100,COUNTA(Trades!M2:M501)),1),"LOSS")),0)</f>
         <v/>
       </c>
     </row>
@@ -12043,8 +12073,8 @@
           <t>Last 100 — EV</t>
         </is>
       </c>
-      <c r="E10" s="12">
-        <f>IFERROR(SUMPRODUCT(OFFSET(Trades!N2,MAX(0,COUNTA(Trades!M2:M501)-100),0,MIN(100,COUNTA(Trades!M2:M501)),1))/MIN(100,COUNTA(Trades!M2:M501)),0)</f>
+      <c r="E10" s="13">
+        <f>IFERROR(SUM(OFFSET(Trades!N2,MAX(0,COUNTA(Trades!M2:M501)-100),0,MIN(100,COUNTA(Trades!M2:M501)),1))/(COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-100),0,MIN(100,COUNTA(Trades!M2:M501)),1),"WIN")+COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-100),0,MIN(100,COUNTA(Trades!M2:M501)),1),"LOSS")+COUNTIF(OFFSET(Trades!M2,MAX(0,COUNTA(Trades!M2:M501)-100),0,MIN(100,COUNTA(Trades!M2:M501)),1),"BE")),0)</f>
         <v/>
       </c>
     </row>
@@ -12054,7 +12084,7 @@
           <t>Avg R per trade (EV)</t>
         </is>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="13">
         <f>IFERROR(SUM(Trades!N2:N501)/(B6+B7+B8),0)</f>
         <v/>
       </c>
@@ -12065,19 +12095,9 @@
           <t>Profit factor</t>
         </is>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="15">
         <f>IFERROR(SUMIF(Trades!N2:N501,"&gt;0")/ABS(SUMIF(Trades!N2:N501,"&lt;0")),0)</f>
         <v/>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>running_R</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>drawdown_R</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -12086,16 +12106,8 @@
           <t>Total R</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="16">
         <f>SUM(Trades!N2:N501)</f>
-        <v/>
-      </c>
-      <c r="E13" s="4">
-        <f>IF(OR(Trades!M2="WIN",Trades!M2="LOSS"),Trades!N2,0)</f>
-        <v/>
-      </c>
-      <c r="F13" s="15">
-        <f>MIN(0,E13-MAX($E$13:E13))</f>
         <v/>
       </c>
     </row>
@@ -12105,16 +12117,8 @@
           <t>Total P&amp;L ($)</t>
         </is>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="17">
         <f>SUM(Trades!S2:S501)</f>
-        <v/>
-      </c>
-      <c r="E14" s="4">
-        <f>IF(OR(Trades!M3="WIN",Trades!M3="LOSS"),E13+Trades!N3,E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="15">
-        <f>MIN(0,E14-MAX($E$13:E14))</f>
         <v/>
       </c>
     </row>
@@ -12124,5000 +12128,6647 @@
           <t>Max drawdown (R)</t>
         </is>
       </c>
-      <c r="B15" s="13">
-        <f>IFERROR(MIN(F13:F512),0)</f>
-        <v/>
-      </c>
-      <c r="E15" s="4">
-        <f>IF(OR(Trades!M4="WIN",Trades!M4="LOSS"),E14+Trades!N4,E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="15">
-        <f>MIN(0,E15-MAX($E$13:E15))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Forward-test status</t>
-        </is>
-      </c>
-      <c r="E16" s="4">
-        <f>IF(OR(Trades!M5="WIN",Trades!M5="LOSS"),E15+Trades!N5,E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="15">
-        <f>MIN(0,E16-MAX($E$13:E16))</f>
+      <c r="B15" s="15">
+        <f>IFERROR(MIN(_Equity!C2:C501),0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>(auto)</t>
-        </is>
-      </c>
-      <c r="B17" s="17">
-        <f>IF(B5&lt;30,"⏳ Noise — keep tracking",IF(B5&lt;100,"📊 Trend — too early to call",IF(B10&lt;0.45,"🛑 STOP — WR below 45%",IF(B11&lt;0,"🛑 STOP — EV negative","✓ On track"))))</f>
-        <v/>
-      </c>
-      <c r="E17" s="4">
-        <f>IF(OR(Trades!M6="WIN",Trades!M6="LOSS"),E16+Trades!N6,E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="15">
-        <f>MIN(0,E17-MAX($E$13:E17))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="E18" s="4">
-        <f>IF(OR(Trades!M7="WIN",Trades!M7="LOSS"),E17+Trades!N7,E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="15">
-        <f>MIN(0,E18-MAX($E$13:E18))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="E19" s="4">
-        <f>IF(OR(Trades!M8="WIN",Trades!M8="LOSS"),E18+Trades!N8,E18)</f>
-        <v/>
-      </c>
-      <c r="F19" s="15">
-        <f>MIN(0,E19-MAX($E$13:E19))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Decision rules</t>
         </is>
       </c>
-      <c r="E20" s="4">
-        <f>IF(OR(Trades!M9="WIN",Trades!M9="LOSS"),E19+Trades!N9,E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="15">
-        <f>MIN(0,E20-MAX($E$13:E20))</f>
-        <v/>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>🛑 Stop trading if cumulative drawdown &gt; 15R = $3,375</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>🛑 Stop if WR &lt; 45% on Last-50 window</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>🛑 Stop if EV &lt; 0R on Last-100 window</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>🛑 Stop trading if cumulative drawdown &gt; 15R = $3,375</t>
+          <t>✓  Continue if WR 50-65% on rolling windows (within expected variance)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>🛑 Stop if WR &lt; 45% on Last-50 window</t>
+          <t>✓  Continue through 5-trade losing streaks (math says they're common at 59% WR)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>🛑 Stop if EV &lt; 0R on Last-100 window</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>✓  Continue if WR 50-65% on rolling windows (within expected variance)</t>
+          <t>Validation criteria — what 'edge confirmed' looks like after ~200 trades:</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>✓  Continue through 5-trade losing streaks (math says they're common at 59% WR)</t>
+          <t>• WR consistently 55–62% on rolling windows</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="E26" s="4">
-        <f>IF(OR(Trades!M15="WIN",Trades!M15="LOSS"),E25+Trades!N15,E25)</f>
-        <v/>
-      </c>
-      <c r="F26" s="15">
-        <f>MIN(0,E26-MAX($E$13:E26))</f>
-        <v/>
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>• Avg R per trade between +0.10 and +0.18</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>Validation criteria — what 'edge confirmed' looks like after ~200 trades:</t>
+          <t>• Max drawdown stayed within 15R</t>
         </is>
-      </c>
-      <c r="E27" s="4">
-        <f>IF(OR(Trades!M16="WIN",Trades!M16="LOSS"),E26+Trades!N16,E26)</f>
-        <v/>
-      </c>
-      <c r="F27" s="15">
-        <f>MIN(0,E27-MAX($E$13:E27))</f>
-        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>• WR consistently 55–62% on rolling windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>• Avg R per trade between +0.10 and +0.18</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>• Max drawdown stayed within 15R</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
           <t>• Profit factor 1.4 or higher</t>
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Equity curve chart: see _Equity tab.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A22:H22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C501"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>trade_no</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>running_R</t>
+        </is>
+      </c>
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>drawdown_R</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4">
+        <f>IF(OR(Trades!M2="WIN",Trades!M2="LOSS"),Trades!N2,0)</f>
+        <v/>
+      </c>
+      <c r="C2" s="20">
+        <f>MIN(0,B2-MAX($B$2:B2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4">
+        <f>IF(OR(Trades!M3="WIN",Trades!M3="LOSS"),B2+Trades!N3,B2)</f>
+        <v/>
+      </c>
+      <c r="C3" s="20">
+        <f>MIN(0,B3-MAX($B$2:B3))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4">
+        <f>IF(OR(Trades!M4="WIN",Trades!M4="LOSS"),B3+Trades!N4,B3)</f>
+        <v/>
+      </c>
+      <c r="C4" s="20">
+        <f>MIN(0,B4-MAX($B$2:B4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
+        <f>IF(OR(Trades!M5="WIN",Trades!M5="LOSS"),B4+Trades!N5,B4)</f>
+        <v/>
+      </c>
+      <c r="C5" s="20">
+        <f>MIN(0,B5-MAX($B$2:B5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4">
+        <f>IF(OR(Trades!M6="WIN",Trades!M6="LOSS"),B5+Trades!N6,B5)</f>
+        <v/>
+      </c>
+      <c r="C6" s="20">
+        <f>MIN(0,B6-MAX($B$2:B6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4">
+        <f>IF(OR(Trades!M7="WIN",Trades!M7="LOSS"),B6+Trades!N7,B6)</f>
+        <v/>
+      </c>
+      <c r="C7" s="20">
+        <f>MIN(0,B7-MAX($B$2:B7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4">
+        <f>IF(OR(Trades!M8="WIN",Trades!M8="LOSS"),B7+Trades!N8,B7)</f>
+        <v/>
+      </c>
+      <c r="C8" s="20">
+        <f>MIN(0,B8-MAX($B$2:B8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4">
+        <f>IF(OR(Trades!M9="WIN",Trades!M9="LOSS"),B8+Trades!N9,B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="20">
+        <f>MIN(0,B9-MAX($B$2:B9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4">
+        <f>IF(OR(Trades!M10="WIN",Trades!M10="LOSS"),B9+Trades!N10,B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="20">
+        <f>MIN(0,B10-MAX($B$2:B10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4">
+        <f>IF(OR(Trades!M11="WIN",Trades!M11="LOSS"),B10+Trades!N11,B10)</f>
+        <v/>
+      </c>
+      <c r="C11" s="20">
+        <f>MIN(0,B11-MAX($B$2:B11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4">
+        <f>IF(OR(Trades!M12="WIN",Trades!M12="LOSS"),B11+Trades!N12,B11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="20">
+        <f>MIN(0,B12-MAX($B$2:B12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4">
+        <f>IF(OR(Trades!M13="WIN",Trades!M13="LOSS"),B12+Trades!N13,B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="20">
+        <f>MIN(0,B13-MAX($B$2:B13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4">
+        <f>IF(OR(Trades!M14="WIN",Trades!M14="LOSS"),B13+Trades!N14,B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="20">
+        <f>MIN(0,B14-MAX($B$2:B14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4">
+        <f>IF(OR(Trades!M15="WIN",Trades!M15="LOSS"),B14+Trades!N15,B14)</f>
+        <v/>
+      </c>
+      <c r="C15" s="20">
+        <f>MIN(0,B15-MAX($B$2:B15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4">
+        <f>IF(OR(Trades!M16="WIN",Trades!M16="LOSS"),B15+Trades!N16,B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="20">
+        <f>MIN(0,B16-MAX($B$2:B16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4">
+        <f>IF(OR(Trades!M17="WIN",Trades!M17="LOSS"),B16+Trades!N17,B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="20">
+        <f>MIN(0,B17-MAX($B$2:B17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4">
+        <f>IF(OR(Trades!M18="WIN",Trades!M18="LOSS"),B17+Trades!N18,B17)</f>
+        <v/>
+      </c>
+      <c r="C18" s="20">
+        <f>MIN(0,B18-MAX($B$2:B18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4">
+        <f>IF(OR(Trades!M19="WIN",Trades!M19="LOSS"),B18+Trades!N19,B18)</f>
+        <v/>
+      </c>
+      <c r="C19" s="20">
+        <f>MIN(0,B19-MAX($B$2:B19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4">
+        <f>IF(OR(Trades!M20="WIN",Trades!M20="LOSS"),B19+Trades!N20,B19)</f>
+        <v/>
+      </c>
+      <c r="C20" s="20">
+        <f>MIN(0,B20-MAX($B$2:B20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4">
+        <f>IF(OR(Trades!M21="WIN",Trades!M21="LOSS"),B20+Trades!N21,B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="20">
+        <f>MIN(0,B21-MAX($B$2:B21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4">
+        <f>IF(OR(Trades!M22="WIN",Trades!M22="LOSS"),B21+Trades!N22,B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="20">
+        <f>MIN(0,B22-MAX($B$2:B22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4">
+        <f>IF(OR(Trades!M23="WIN",Trades!M23="LOSS"),B22+Trades!N23,B22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="20">
+        <f>MIN(0,B23-MAX($B$2:B23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4">
+        <f>IF(OR(Trades!M24="WIN",Trades!M24="LOSS"),B23+Trades!N24,B23)</f>
+        <v/>
+      </c>
+      <c r="C24" s="20">
+        <f>MIN(0,B24-MAX($B$2:B24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4">
+        <f>IF(OR(Trades!M25="WIN",Trades!M25="LOSS"),B24+Trades!N25,B24)</f>
+        <v/>
+      </c>
+      <c r="C25" s="20">
+        <f>MIN(0,B25-MAX($B$2:B25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4">
+        <f>IF(OR(Trades!M26="WIN",Trades!M26="LOSS"),B25+Trades!N26,B25)</f>
+        <v/>
+      </c>
+      <c r="C26" s="20">
+        <f>MIN(0,B26-MAX($B$2:B26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4">
+        <f>IF(OR(Trades!M27="WIN",Trades!M27="LOSS"),B26+Trades!N27,B26)</f>
+        <v/>
+      </c>
+      <c r="C27" s="20">
+        <f>MIN(0,B27-MAX($B$2:B27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4">
+        <f>IF(OR(Trades!M28="WIN",Trades!M28="LOSS"),B27+Trades!N28,B27)</f>
+        <v/>
+      </c>
+      <c r="C28" s="20">
+        <f>MIN(0,B28-MAX($B$2:B28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4">
+        <f>IF(OR(Trades!M29="WIN",Trades!M29="LOSS"),B28+Trades!N29,B28)</f>
+        <v/>
+      </c>
+      <c r="C29" s="20">
+        <f>MIN(0,B29-MAX($B$2:B29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4">
+        <f>IF(OR(Trades!M30="WIN",Trades!M30="LOSS"),B29+Trades!N30,B29)</f>
+        <v/>
+      </c>
+      <c r="C30" s="20">
+        <f>MIN(0,B30-MAX($B$2:B30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4">
+        <f>IF(OR(Trades!M31="WIN",Trades!M31="LOSS"),B30+Trades!N31,B30)</f>
+        <v/>
+      </c>
+      <c r="C31" s="20">
+        <f>MIN(0,B31-MAX($B$2:B31))</f>
+        <v/>
+      </c>
+    </row>
     <row r="32">
-      <c r="E32" s="4">
-        <f>IF(OR(Trades!M21="WIN",Trades!M21="LOSS"),E31+Trades!N21,E31)</f>
-        <v/>
-      </c>
-      <c r="F32" s="15">
-        <f>MIN(0,E32-MAX($E$13:E32))</f>
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4">
+        <f>IF(OR(Trades!M32="WIN",Trades!M32="LOSS"),B31+Trades!N32,B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="20">
+        <f>MIN(0,B32-MAX($B$2:B32))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="E33" s="4">
-        <f>IF(OR(Trades!M22="WIN",Trades!M22="LOSS"),E32+Trades!N22,E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="15">
-        <f>MIN(0,E33-MAX($E$13:E33))</f>
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4">
+        <f>IF(OR(Trades!M33="WIN",Trades!M33="LOSS"),B32+Trades!N33,B32)</f>
+        <v/>
+      </c>
+      <c r="C33" s="20">
+        <f>MIN(0,B33-MAX($B$2:B33))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="E34" s="4">
-        <f>IF(OR(Trades!M23="WIN",Trades!M23="LOSS"),E33+Trades!N23,E33)</f>
-        <v/>
-      </c>
-      <c r="F34" s="15">
-        <f>MIN(0,E34-MAX($E$13:E34))</f>
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4">
+        <f>IF(OR(Trades!M34="WIN",Trades!M34="LOSS"),B33+Trades!N34,B33)</f>
+        <v/>
+      </c>
+      <c r="C34" s="20">
+        <f>MIN(0,B34-MAX($B$2:B34))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="E35" s="4">
-        <f>IF(OR(Trades!M24="WIN",Trades!M24="LOSS"),E34+Trades!N24,E34)</f>
-        <v/>
-      </c>
-      <c r="F35" s="15">
-        <f>MIN(0,E35-MAX($E$13:E35))</f>
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4">
+        <f>IF(OR(Trades!M35="WIN",Trades!M35="LOSS"),B34+Trades!N35,B34)</f>
+        <v/>
+      </c>
+      <c r="C35" s="20">
+        <f>MIN(0,B35-MAX($B$2:B35))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="E36" s="4">
-        <f>IF(OR(Trades!M25="WIN",Trades!M25="LOSS"),E35+Trades!N25,E35)</f>
-        <v/>
-      </c>
-      <c r="F36" s="15">
-        <f>MIN(0,E36-MAX($E$13:E36))</f>
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4">
+        <f>IF(OR(Trades!M36="WIN",Trades!M36="LOSS"),B35+Trades!N36,B35)</f>
+        <v/>
+      </c>
+      <c r="C36" s="20">
+        <f>MIN(0,B36-MAX($B$2:B36))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="E37" s="4">
-        <f>IF(OR(Trades!M26="WIN",Trades!M26="LOSS"),E36+Trades!N26,E36)</f>
-        <v/>
-      </c>
-      <c r="F37" s="15">
-        <f>MIN(0,E37-MAX($E$13:E37))</f>
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4">
+        <f>IF(OR(Trades!M37="WIN",Trades!M37="LOSS"),B36+Trades!N37,B36)</f>
+        <v/>
+      </c>
+      <c r="C37" s="20">
+        <f>MIN(0,B37-MAX($B$2:B37))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="E38" s="4">
-        <f>IF(OR(Trades!M27="WIN",Trades!M27="LOSS"),E37+Trades!N27,E37)</f>
-        <v/>
-      </c>
-      <c r="F38" s="15">
-        <f>MIN(0,E38-MAX($E$13:E38))</f>
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4">
+        <f>IF(OR(Trades!M38="WIN",Trades!M38="LOSS"),B37+Trades!N38,B37)</f>
+        <v/>
+      </c>
+      <c r="C38" s="20">
+        <f>MIN(0,B38-MAX($B$2:B38))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="E39" s="4">
-        <f>IF(OR(Trades!M28="WIN",Trades!M28="LOSS"),E38+Trades!N28,E38)</f>
-        <v/>
-      </c>
-      <c r="F39" s="15">
-        <f>MIN(0,E39-MAX($E$13:E39))</f>
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4">
+        <f>IF(OR(Trades!M39="WIN",Trades!M39="LOSS"),B38+Trades!N39,B38)</f>
+        <v/>
+      </c>
+      <c r="C39" s="20">
+        <f>MIN(0,B39-MAX($B$2:B39))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="E40" s="4">
-        <f>IF(OR(Trades!M29="WIN",Trades!M29="LOSS"),E39+Trades!N29,E39)</f>
-        <v/>
-      </c>
-      <c r="F40" s="15">
-        <f>MIN(0,E40-MAX($E$13:E40))</f>
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4">
+        <f>IF(OR(Trades!M40="WIN",Trades!M40="LOSS"),B39+Trades!N40,B39)</f>
+        <v/>
+      </c>
+      <c r="C40" s="20">
+        <f>MIN(0,B40-MAX($B$2:B40))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="E41" s="4">
-        <f>IF(OR(Trades!M30="WIN",Trades!M30="LOSS"),E40+Trades!N30,E40)</f>
-        <v/>
-      </c>
-      <c r="F41" s="15">
-        <f>MIN(0,E41-MAX($E$13:E41))</f>
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4">
+        <f>IF(OR(Trades!M41="WIN",Trades!M41="LOSS"),B40+Trades!N41,B40)</f>
+        <v/>
+      </c>
+      <c r="C41" s="20">
+        <f>MIN(0,B41-MAX($B$2:B41))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="E42" s="4">
-        <f>IF(OR(Trades!M31="WIN",Trades!M31="LOSS"),E41+Trades!N31,E41)</f>
-        <v/>
-      </c>
-      <c r="F42" s="15">
-        <f>MIN(0,E42-MAX($E$13:E42))</f>
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4">
+        <f>IF(OR(Trades!M42="WIN",Trades!M42="LOSS"),B41+Trades!N42,B41)</f>
+        <v/>
+      </c>
+      <c r="C42" s="20">
+        <f>MIN(0,B42-MAX($B$2:B42))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="E43" s="4">
-        <f>IF(OR(Trades!M32="WIN",Trades!M32="LOSS"),E42+Trades!N32,E42)</f>
-        <v/>
-      </c>
-      <c r="F43" s="15">
-        <f>MIN(0,E43-MAX($E$13:E43))</f>
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4">
+        <f>IF(OR(Trades!M43="WIN",Trades!M43="LOSS"),B42+Trades!N43,B42)</f>
+        <v/>
+      </c>
+      <c r="C43" s="20">
+        <f>MIN(0,B43-MAX($B$2:B43))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="E44" s="4">
-        <f>IF(OR(Trades!M33="WIN",Trades!M33="LOSS"),E43+Trades!N33,E43)</f>
-        <v/>
-      </c>
-      <c r="F44" s="15">
-        <f>MIN(0,E44-MAX($E$13:E44))</f>
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4">
+        <f>IF(OR(Trades!M44="WIN",Trades!M44="LOSS"),B43+Trades!N44,B43)</f>
+        <v/>
+      </c>
+      <c r="C44" s="20">
+        <f>MIN(0,B44-MAX($B$2:B44))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="E45" s="4">
-        <f>IF(OR(Trades!M34="WIN",Trades!M34="LOSS"),E44+Trades!N34,E44)</f>
-        <v/>
-      </c>
-      <c r="F45" s="15">
-        <f>MIN(0,E45-MAX($E$13:E45))</f>
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4">
+        <f>IF(OR(Trades!M45="WIN",Trades!M45="LOSS"),B44+Trades!N45,B44)</f>
+        <v/>
+      </c>
+      <c r="C45" s="20">
+        <f>MIN(0,B45-MAX($B$2:B45))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="E46" s="4">
-        <f>IF(OR(Trades!M35="WIN",Trades!M35="LOSS"),E45+Trades!N35,E45)</f>
-        <v/>
-      </c>
-      <c r="F46" s="15">
-        <f>MIN(0,E46-MAX($E$13:E46))</f>
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4">
+        <f>IF(OR(Trades!M46="WIN",Trades!M46="LOSS"),B45+Trades!N46,B45)</f>
+        <v/>
+      </c>
+      <c r="C46" s="20">
+        <f>MIN(0,B46-MAX($B$2:B46))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="E47" s="4">
-        <f>IF(OR(Trades!M36="WIN",Trades!M36="LOSS"),E46+Trades!N36,E46)</f>
-        <v/>
-      </c>
-      <c r="F47" s="15">
-        <f>MIN(0,E47-MAX($E$13:E47))</f>
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4">
+        <f>IF(OR(Trades!M47="WIN",Trades!M47="LOSS"),B46+Trades!N47,B46)</f>
+        <v/>
+      </c>
+      <c r="C47" s="20">
+        <f>MIN(0,B47-MAX($B$2:B47))</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="E48" s="4">
-        <f>IF(OR(Trades!M37="WIN",Trades!M37="LOSS"),E47+Trades!N37,E47)</f>
-        <v/>
-      </c>
-      <c r="F48" s="15">
-        <f>MIN(0,E48-MAX($E$13:E48))</f>
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4">
+        <f>IF(OR(Trades!M48="WIN",Trades!M48="LOSS"),B47+Trades!N48,B47)</f>
+        <v/>
+      </c>
+      <c r="C48" s="20">
+        <f>MIN(0,B48-MAX($B$2:B48))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="E49" s="4">
-        <f>IF(OR(Trades!M38="WIN",Trades!M38="LOSS"),E48+Trades!N38,E48)</f>
-        <v/>
-      </c>
-      <c r="F49" s="15">
-        <f>MIN(0,E49-MAX($E$13:E49))</f>
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4">
+        <f>IF(OR(Trades!M49="WIN",Trades!M49="LOSS"),B48+Trades!N49,B48)</f>
+        <v/>
+      </c>
+      <c r="C49" s="20">
+        <f>MIN(0,B49-MAX($B$2:B49))</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="E50" s="4">
-        <f>IF(OR(Trades!M39="WIN",Trades!M39="LOSS"),E49+Trades!N39,E49)</f>
-        <v/>
-      </c>
-      <c r="F50" s="15">
-        <f>MIN(0,E50-MAX($E$13:E50))</f>
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4">
+        <f>IF(OR(Trades!M50="WIN",Trades!M50="LOSS"),B49+Trades!N50,B49)</f>
+        <v/>
+      </c>
+      <c r="C50" s="20">
+        <f>MIN(0,B50-MAX($B$2:B50))</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="E51" s="4">
-        <f>IF(OR(Trades!M40="WIN",Trades!M40="LOSS"),E50+Trades!N40,E50)</f>
-        <v/>
-      </c>
-      <c r="F51" s="15">
-        <f>MIN(0,E51-MAX($E$13:E51))</f>
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4">
+        <f>IF(OR(Trades!M51="WIN",Trades!M51="LOSS"),B50+Trades!N51,B50)</f>
+        <v/>
+      </c>
+      <c r="C51" s="20">
+        <f>MIN(0,B51-MAX($B$2:B51))</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="E52" s="4">
-        <f>IF(OR(Trades!M41="WIN",Trades!M41="LOSS"),E51+Trades!N41,E51)</f>
-        <v/>
-      </c>
-      <c r="F52" s="15">
-        <f>MIN(0,E52-MAX($E$13:E52))</f>
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="4">
+        <f>IF(OR(Trades!M52="WIN",Trades!M52="LOSS"),B51+Trades!N52,B51)</f>
+        <v/>
+      </c>
+      <c r="C52" s="20">
+        <f>MIN(0,B52-MAX($B$2:B52))</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="E53" s="4">
-        <f>IF(OR(Trades!M42="WIN",Trades!M42="LOSS"),E52+Trades!N42,E52)</f>
-        <v/>
-      </c>
-      <c r="F53" s="15">
-        <f>MIN(0,E53-MAX($E$13:E53))</f>
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4">
+        <f>IF(OR(Trades!M53="WIN",Trades!M53="LOSS"),B52+Trades!N53,B52)</f>
+        <v/>
+      </c>
+      <c r="C53" s="20">
+        <f>MIN(0,B53-MAX($B$2:B53))</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="E54" s="4">
-        <f>IF(OR(Trades!M43="WIN",Trades!M43="LOSS"),E53+Trades!N43,E53)</f>
-        <v/>
-      </c>
-      <c r="F54" s="15">
-        <f>MIN(0,E54-MAX($E$13:E54))</f>
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4">
+        <f>IF(OR(Trades!M54="WIN",Trades!M54="LOSS"),B53+Trades!N54,B53)</f>
+        <v/>
+      </c>
+      <c r="C54" s="20">
+        <f>MIN(0,B54-MAX($B$2:B54))</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="E55" s="4">
-        <f>IF(OR(Trades!M44="WIN",Trades!M44="LOSS"),E54+Trades!N44,E54)</f>
-        <v/>
-      </c>
-      <c r="F55" s="15">
-        <f>MIN(0,E55-MAX($E$13:E55))</f>
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4">
+        <f>IF(OR(Trades!M55="WIN",Trades!M55="LOSS"),B54+Trades!N55,B54)</f>
+        <v/>
+      </c>
+      <c r="C55" s="20">
+        <f>MIN(0,B55-MAX($B$2:B55))</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="E56" s="4">
-        <f>IF(OR(Trades!M45="WIN",Trades!M45="LOSS"),E55+Trades!N45,E55)</f>
-        <v/>
-      </c>
-      <c r="F56" s="15">
-        <f>MIN(0,E56-MAX($E$13:E56))</f>
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="4">
+        <f>IF(OR(Trades!M56="WIN",Trades!M56="LOSS"),B55+Trades!N56,B55)</f>
+        <v/>
+      </c>
+      <c r="C56" s="20">
+        <f>MIN(0,B56-MAX($B$2:B56))</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="E57" s="4">
-        <f>IF(OR(Trades!M46="WIN",Trades!M46="LOSS"),E56+Trades!N46,E56)</f>
-        <v/>
-      </c>
-      <c r="F57" s="15">
-        <f>MIN(0,E57-MAX($E$13:E57))</f>
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4">
+        <f>IF(OR(Trades!M57="WIN",Trades!M57="LOSS"),B56+Trades!N57,B56)</f>
+        <v/>
+      </c>
+      <c r="C57" s="20">
+        <f>MIN(0,B57-MAX($B$2:B57))</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="E58" s="4">
-        <f>IF(OR(Trades!M47="WIN",Trades!M47="LOSS"),E57+Trades!N47,E57)</f>
-        <v/>
-      </c>
-      <c r="F58" s="15">
-        <f>MIN(0,E58-MAX($E$13:E58))</f>
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4">
+        <f>IF(OR(Trades!M58="WIN",Trades!M58="LOSS"),B57+Trades!N58,B57)</f>
+        <v/>
+      </c>
+      <c r="C58" s="20">
+        <f>MIN(0,B58-MAX($B$2:B58))</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="E59" s="4">
-        <f>IF(OR(Trades!M48="WIN",Trades!M48="LOSS"),E58+Trades!N48,E58)</f>
-        <v/>
-      </c>
-      <c r="F59" s="15">
-        <f>MIN(0,E59-MAX($E$13:E59))</f>
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4">
+        <f>IF(OR(Trades!M59="WIN",Trades!M59="LOSS"),B58+Trades!N59,B58)</f>
+        <v/>
+      </c>
+      <c r="C59" s="20">
+        <f>MIN(0,B59-MAX($B$2:B59))</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="E60" s="4">
-        <f>IF(OR(Trades!M49="WIN",Trades!M49="LOSS"),E59+Trades!N49,E59)</f>
-        <v/>
-      </c>
-      <c r="F60" s="15">
-        <f>MIN(0,E60-MAX($E$13:E60))</f>
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4">
+        <f>IF(OR(Trades!M60="WIN",Trades!M60="LOSS"),B59+Trades!N60,B59)</f>
+        <v/>
+      </c>
+      <c r="C60" s="20">
+        <f>MIN(0,B60-MAX($B$2:B60))</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="E61" s="4">
-        <f>IF(OR(Trades!M50="WIN",Trades!M50="LOSS"),E60+Trades!N50,E60)</f>
-        <v/>
-      </c>
-      <c r="F61" s="15">
-        <f>MIN(0,E61-MAX($E$13:E61))</f>
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4">
+        <f>IF(OR(Trades!M61="WIN",Trades!M61="LOSS"),B60+Trades!N61,B60)</f>
+        <v/>
+      </c>
+      <c r="C61" s="20">
+        <f>MIN(0,B61-MAX($B$2:B61))</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="E62" s="4">
-        <f>IF(OR(Trades!M51="WIN",Trades!M51="LOSS"),E61+Trades!N51,E61)</f>
-        <v/>
-      </c>
-      <c r="F62" s="15">
-        <f>MIN(0,E62-MAX($E$13:E62))</f>
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4">
+        <f>IF(OR(Trades!M62="WIN",Trades!M62="LOSS"),B61+Trades!N62,B61)</f>
+        <v/>
+      </c>
+      <c r="C62" s="20">
+        <f>MIN(0,B62-MAX($B$2:B62))</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="E63" s="4">
-        <f>IF(OR(Trades!M52="WIN",Trades!M52="LOSS"),E62+Trades!N52,E62)</f>
-        <v/>
-      </c>
-      <c r="F63" s="15">
-        <f>MIN(0,E63-MAX($E$13:E63))</f>
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4">
+        <f>IF(OR(Trades!M63="WIN",Trades!M63="LOSS"),B62+Trades!N63,B62)</f>
+        <v/>
+      </c>
+      <c r="C63" s="20">
+        <f>MIN(0,B63-MAX($B$2:B63))</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="E64" s="4">
-        <f>IF(OR(Trades!M53="WIN",Trades!M53="LOSS"),E63+Trades!N53,E63)</f>
-        <v/>
-      </c>
-      <c r="F64" s="15">
-        <f>MIN(0,E64-MAX($E$13:E64))</f>
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="4">
+        <f>IF(OR(Trades!M64="WIN",Trades!M64="LOSS"),B63+Trades!N64,B63)</f>
+        <v/>
+      </c>
+      <c r="C64" s="20">
+        <f>MIN(0,B64-MAX($B$2:B64))</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="E65" s="4">
-        <f>IF(OR(Trades!M54="WIN",Trades!M54="LOSS"),E64+Trades!N54,E64)</f>
-        <v/>
-      </c>
-      <c r="F65" s="15">
-        <f>MIN(0,E65-MAX($E$13:E65))</f>
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4">
+        <f>IF(OR(Trades!M65="WIN",Trades!M65="LOSS"),B64+Trades!N65,B64)</f>
+        <v/>
+      </c>
+      <c r="C65" s="20">
+        <f>MIN(0,B65-MAX($B$2:B65))</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="E66" s="4">
-        <f>IF(OR(Trades!M55="WIN",Trades!M55="LOSS"),E65+Trades!N55,E65)</f>
-        <v/>
-      </c>
-      <c r="F66" s="15">
-        <f>MIN(0,E66-MAX($E$13:E66))</f>
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="4">
+        <f>IF(OR(Trades!M66="WIN",Trades!M66="LOSS"),B65+Trades!N66,B65)</f>
+        <v/>
+      </c>
+      <c r="C66" s="20">
+        <f>MIN(0,B66-MAX($B$2:B66))</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="E67" s="4">
-        <f>IF(OR(Trades!M56="WIN",Trades!M56="LOSS"),E66+Trades!N56,E66)</f>
-        <v/>
-      </c>
-      <c r="F67" s="15">
-        <f>MIN(0,E67-MAX($E$13:E67))</f>
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="4">
+        <f>IF(OR(Trades!M67="WIN",Trades!M67="LOSS"),B66+Trades!N67,B66)</f>
+        <v/>
+      </c>
+      <c r="C67" s="20">
+        <f>MIN(0,B67-MAX($B$2:B67))</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="E68" s="4">
-        <f>IF(OR(Trades!M57="WIN",Trades!M57="LOSS"),E67+Trades!N57,E67)</f>
-        <v/>
-      </c>
-      <c r="F68" s="15">
-        <f>MIN(0,E68-MAX($E$13:E68))</f>
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="4">
+        <f>IF(OR(Trades!M68="WIN",Trades!M68="LOSS"),B67+Trades!N68,B67)</f>
+        <v/>
+      </c>
+      <c r="C68" s="20">
+        <f>MIN(0,B68-MAX($B$2:B68))</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="E69" s="4">
-        <f>IF(OR(Trades!M58="WIN",Trades!M58="LOSS"),E68+Trades!N58,E68)</f>
-        <v/>
-      </c>
-      <c r="F69" s="15">
-        <f>MIN(0,E69-MAX($E$13:E69))</f>
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="4">
+        <f>IF(OR(Trades!M69="WIN",Trades!M69="LOSS"),B68+Trades!N69,B68)</f>
+        <v/>
+      </c>
+      <c r="C69" s="20">
+        <f>MIN(0,B69-MAX($B$2:B69))</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="E70" s="4">
-        <f>IF(OR(Trades!M59="WIN",Trades!M59="LOSS"),E69+Trades!N59,E69)</f>
-        <v/>
-      </c>
-      <c r="F70" s="15">
-        <f>MIN(0,E70-MAX($E$13:E70))</f>
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="4">
+        <f>IF(OR(Trades!M70="WIN",Trades!M70="LOSS"),B69+Trades!N70,B69)</f>
+        <v/>
+      </c>
+      <c r="C70" s="20">
+        <f>MIN(0,B70-MAX($B$2:B70))</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="E71" s="4">
-        <f>IF(OR(Trades!M60="WIN",Trades!M60="LOSS"),E70+Trades!N60,E70)</f>
-        <v/>
-      </c>
-      <c r="F71" s="15">
-        <f>MIN(0,E71-MAX($E$13:E71))</f>
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="4">
+        <f>IF(OR(Trades!M71="WIN",Trades!M71="LOSS"),B70+Trades!N71,B70)</f>
+        <v/>
+      </c>
+      <c r="C71" s="20">
+        <f>MIN(0,B71-MAX($B$2:B71))</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="E72" s="4">
-        <f>IF(OR(Trades!M61="WIN",Trades!M61="LOSS"),E71+Trades!N61,E71)</f>
-        <v/>
-      </c>
-      <c r="F72" s="15">
-        <f>MIN(0,E72-MAX($E$13:E72))</f>
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="4">
+        <f>IF(OR(Trades!M72="WIN",Trades!M72="LOSS"),B71+Trades!N72,B71)</f>
+        <v/>
+      </c>
+      <c r="C72" s="20">
+        <f>MIN(0,B72-MAX($B$2:B72))</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="E73" s="4">
-        <f>IF(OR(Trades!M62="WIN",Trades!M62="LOSS"),E72+Trades!N62,E72)</f>
-        <v/>
-      </c>
-      <c r="F73" s="15">
-        <f>MIN(0,E73-MAX($E$13:E73))</f>
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="4">
+        <f>IF(OR(Trades!M73="WIN",Trades!M73="LOSS"),B72+Trades!N73,B72)</f>
+        <v/>
+      </c>
+      <c r="C73" s="20">
+        <f>MIN(0,B73-MAX($B$2:B73))</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="E74" s="4">
-        <f>IF(OR(Trades!M63="WIN",Trades!M63="LOSS"),E73+Trades!N63,E73)</f>
-        <v/>
-      </c>
-      <c r="F74" s="15">
-        <f>MIN(0,E74-MAX($E$13:E74))</f>
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="4">
+        <f>IF(OR(Trades!M74="WIN",Trades!M74="LOSS"),B73+Trades!N74,B73)</f>
+        <v/>
+      </c>
+      <c r="C74" s="20">
+        <f>MIN(0,B74-MAX($B$2:B74))</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="E75" s="4">
-        <f>IF(OR(Trades!M64="WIN",Trades!M64="LOSS"),E74+Trades!N64,E74)</f>
-        <v/>
-      </c>
-      <c r="F75" s="15">
-        <f>MIN(0,E75-MAX($E$13:E75))</f>
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4">
+        <f>IF(OR(Trades!M75="WIN",Trades!M75="LOSS"),B74+Trades!N75,B74)</f>
+        <v/>
+      </c>
+      <c r="C75" s="20">
+        <f>MIN(0,B75-MAX($B$2:B75))</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="E76" s="4">
-        <f>IF(OR(Trades!M65="WIN",Trades!M65="LOSS"),E75+Trades!N65,E75)</f>
-        <v/>
-      </c>
-      <c r="F76" s="15">
-        <f>MIN(0,E76-MAX($E$13:E76))</f>
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="4">
+        <f>IF(OR(Trades!M76="WIN",Trades!M76="LOSS"),B75+Trades!N76,B75)</f>
+        <v/>
+      </c>
+      <c r="C76" s="20">
+        <f>MIN(0,B76-MAX($B$2:B76))</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="E77" s="4">
-        <f>IF(OR(Trades!M66="WIN",Trades!M66="LOSS"),E76+Trades!N66,E76)</f>
-        <v/>
-      </c>
-      <c r="F77" s="15">
-        <f>MIN(0,E77-MAX($E$13:E77))</f>
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="4">
+        <f>IF(OR(Trades!M77="WIN",Trades!M77="LOSS"),B76+Trades!N77,B76)</f>
+        <v/>
+      </c>
+      <c r="C77" s="20">
+        <f>MIN(0,B77-MAX($B$2:B77))</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="E78" s="4">
-        <f>IF(OR(Trades!M67="WIN",Trades!M67="LOSS"),E77+Trades!N67,E77)</f>
-        <v/>
-      </c>
-      <c r="F78" s="15">
-        <f>MIN(0,E78-MAX($E$13:E78))</f>
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="4">
+        <f>IF(OR(Trades!M78="WIN",Trades!M78="LOSS"),B77+Trades!N78,B77)</f>
+        <v/>
+      </c>
+      <c r="C78" s="20">
+        <f>MIN(0,B78-MAX($B$2:B78))</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="E79" s="4">
-        <f>IF(OR(Trades!M68="WIN",Trades!M68="LOSS"),E78+Trades!N68,E78)</f>
-        <v/>
-      </c>
-      <c r="F79" s="15">
-        <f>MIN(0,E79-MAX($E$13:E79))</f>
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4">
+        <f>IF(OR(Trades!M79="WIN",Trades!M79="LOSS"),B78+Trades!N79,B78)</f>
+        <v/>
+      </c>
+      <c r="C79" s="20">
+        <f>MIN(0,B79-MAX($B$2:B79))</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="E80" s="4">
-        <f>IF(OR(Trades!M69="WIN",Trades!M69="LOSS"),E79+Trades!N69,E79)</f>
-        <v/>
-      </c>
-      <c r="F80" s="15">
-        <f>MIN(0,E80-MAX($E$13:E80))</f>
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="4">
+        <f>IF(OR(Trades!M80="WIN",Trades!M80="LOSS"),B79+Trades!N80,B79)</f>
+        <v/>
+      </c>
+      <c r="C80" s="20">
+        <f>MIN(0,B80-MAX($B$2:B80))</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="E81" s="4">
-        <f>IF(OR(Trades!M70="WIN",Trades!M70="LOSS"),E80+Trades!N70,E80)</f>
-        <v/>
-      </c>
-      <c r="F81" s="15">
-        <f>MIN(0,E81-MAX($E$13:E81))</f>
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4">
+        <f>IF(OR(Trades!M81="WIN",Trades!M81="LOSS"),B80+Trades!N81,B80)</f>
+        <v/>
+      </c>
+      <c r="C81" s="20">
+        <f>MIN(0,B81-MAX($B$2:B81))</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="E82" s="4">
-        <f>IF(OR(Trades!M71="WIN",Trades!M71="LOSS"),E81+Trades!N71,E81)</f>
-        <v/>
-      </c>
-      <c r="F82" s="15">
-        <f>MIN(0,E82-MAX($E$13:E82))</f>
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="4">
+        <f>IF(OR(Trades!M82="WIN",Trades!M82="LOSS"),B81+Trades!N82,B81)</f>
+        <v/>
+      </c>
+      <c r="C82" s="20">
+        <f>MIN(0,B82-MAX($B$2:B82))</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="E83" s="4">
-        <f>IF(OR(Trades!M72="WIN",Trades!M72="LOSS"),E82+Trades!N72,E82)</f>
-        <v/>
-      </c>
-      <c r="F83" s="15">
-        <f>MIN(0,E83-MAX($E$13:E83))</f>
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4">
+        <f>IF(OR(Trades!M83="WIN",Trades!M83="LOSS"),B82+Trades!N83,B82)</f>
+        <v/>
+      </c>
+      <c r="C83" s="20">
+        <f>MIN(0,B83-MAX($B$2:B83))</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="E84" s="4">
-        <f>IF(OR(Trades!M73="WIN",Trades!M73="LOSS"),E83+Trades!N73,E83)</f>
-        <v/>
-      </c>
-      <c r="F84" s="15">
-        <f>MIN(0,E84-MAX($E$13:E84))</f>
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="4">
+        <f>IF(OR(Trades!M84="WIN",Trades!M84="LOSS"),B83+Trades!N84,B83)</f>
+        <v/>
+      </c>
+      <c r="C84" s="20">
+        <f>MIN(0,B84-MAX($B$2:B84))</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="E85" s="4">
-        <f>IF(OR(Trades!M74="WIN",Trades!M74="LOSS"),E84+Trades!N74,E84)</f>
-        <v/>
-      </c>
-      <c r="F85" s="15">
-        <f>MIN(0,E85-MAX($E$13:E85))</f>
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="4">
+        <f>IF(OR(Trades!M85="WIN",Trades!M85="LOSS"),B84+Trades!N85,B84)</f>
+        <v/>
+      </c>
+      <c r="C85" s="20">
+        <f>MIN(0,B85-MAX($B$2:B85))</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="E86" s="4">
-        <f>IF(OR(Trades!M75="WIN",Trades!M75="LOSS"),E85+Trades!N75,E85)</f>
-        <v/>
-      </c>
-      <c r="F86" s="15">
-        <f>MIN(0,E86-MAX($E$13:E86))</f>
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="4">
+        <f>IF(OR(Trades!M86="WIN",Trades!M86="LOSS"),B85+Trades!N86,B85)</f>
+        <v/>
+      </c>
+      <c r="C86" s="20">
+        <f>MIN(0,B86-MAX($B$2:B86))</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="E87" s="4">
-        <f>IF(OR(Trades!M76="WIN",Trades!M76="LOSS"),E86+Trades!N76,E86)</f>
-        <v/>
-      </c>
-      <c r="F87" s="15">
-        <f>MIN(0,E87-MAX($E$13:E87))</f>
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4">
+        <f>IF(OR(Trades!M87="WIN",Trades!M87="LOSS"),B86+Trades!N87,B86)</f>
+        <v/>
+      </c>
+      <c r="C87" s="20">
+        <f>MIN(0,B87-MAX($B$2:B87))</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="E88" s="4">
-        <f>IF(OR(Trades!M77="WIN",Trades!M77="LOSS"),E87+Trades!N77,E87)</f>
-        <v/>
-      </c>
-      <c r="F88" s="15">
-        <f>MIN(0,E88-MAX($E$13:E88))</f>
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="4">
+        <f>IF(OR(Trades!M88="WIN",Trades!M88="LOSS"),B87+Trades!N88,B87)</f>
+        <v/>
+      </c>
+      <c r="C88" s="20">
+        <f>MIN(0,B88-MAX($B$2:B88))</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="E89" s="4">
-        <f>IF(OR(Trades!M78="WIN",Trades!M78="LOSS"),E88+Trades!N78,E88)</f>
-        <v/>
-      </c>
-      <c r="F89" s="15">
-        <f>MIN(0,E89-MAX($E$13:E89))</f>
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="4">
+        <f>IF(OR(Trades!M89="WIN",Trades!M89="LOSS"),B88+Trades!N89,B88)</f>
+        <v/>
+      </c>
+      <c r="C89" s="20">
+        <f>MIN(0,B89-MAX($B$2:B89))</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="E90" s="4">
-        <f>IF(OR(Trades!M79="WIN",Trades!M79="LOSS"),E89+Trades!N79,E89)</f>
-        <v/>
-      </c>
-      <c r="F90" s="15">
-        <f>MIN(0,E90-MAX($E$13:E90))</f>
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="4">
+        <f>IF(OR(Trades!M90="WIN",Trades!M90="LOSS"),B89+Trades!N90,B89)</f>
+        <v/>
+      </c>
+      <c r="C90" s="20">
+        <f>MIN(0,B90-MAX($B$2:B90))</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="E91" s="4">
-        <f>IF(OR(Trades!M80="WIN",Trades!M80="LOSS"),E90+Trades!N80,E90)</f>
-        <v/>
-      </c>
-      <c r="F91" s="15">
-        <f>MIN(0,E91-MAX($E$13:E91))</f>
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="4">
+        <f>IF(OR(Trades!M91="WIN",Trades!M91="LOSS"),B90+Trades!N91,B90)</f>
+        <v/>
+      </c>
+      <c r="C91" s="20">
+        <f>MIN(0,B91-MAX($B$2:B91))</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="E92" s="4">
-        <f>IF(OR(Trades!M81="WIN",Trades!M81="LOSS"),E91+Trades!N81,E91)</f>
-        <v/>
-      </c>
-      <c r="F92" s="15">
-        <f>MIN(0,E92-MAX($E$13:E92))</f>
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="4">
+        <f>IF(OR(Trades!M92="WIN",Trades!M92="LOSS"),B91+Trades!N92,B91)</f>
+        <v/>
+      </c>
+      <c r="C92" s="20">
+        <f>MIN(0,B92-MAX($B$2:B92))</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="E93" s="4">
-        <f>IF(OR(Trades!M82="WIN",Trades!M82="LOSS"),E92+Trades!N82,E92)</f>
-        <v/>
-      </c>
-      <c r="F93" s="15">
-        <f>MIN(0,E93-MAX($E$13:E93))</f>
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4">
+        <f>IF(OR(Trades!M93="WIN",Trades!M93="LOSS"),B92+Trades!N93,B92)</f>
+        <v/>
+      </c>
+      <c r="C93" s="20">
+        <f>MIN(0,B93-MAX($B$2:B93))</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="E94" s="4">
-        <f>IF(OR(Trades!M83="WIN",Trades!M83="LOSS"),E93+Trades!N83,E93)</f>
-        <v/>
-      </c>
-      <c r="F94" s="15">
-        <f>MIN(0,E94-MAX($E$13:E94))</f>
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="4">
+        <f>IF(OR(Trades!M94="WIN",Trades!M94="LOSS"),B93+Trades!N94,B93)</f>
+        <v/>
+      </c>
+      <c r="C94" s="20">
+        <f>MIN(0,B94-MAX($B$2:B94))</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="E95" s="4">
-        <f>IF(OR(Trades!M84="WIN",Trades!M84="LOSS"),E94+Trades!N84,E94)</f>
-        <v/>
-      </c>
-      <c r="F95" s="15">
-        <f>MIN(0,E95-MAX($E$13:E95))</f>
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4">
+        <f>IF(OR(Trades!M95="WIN",Trades!M95="LOSS"),B94+Trades!N95,B94)</f>
+        <v/>
+      </c>
+      <c r="C95" s="20">
+        <f>MIN(0,B95-MAX($B$2:B95))</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="E96" s="4">
-        <f>IF(OR(Trades!M85="WIN",Trades!M85="LOSS"),E95+Trades!N85,E95)</f>
-        <v/>
-      </c>
-      <c r="F96" s="15">
-        <f>MIN(0,E96-MAX($E$13:E96))</f>
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4">
+        <f>IF(OR(Trades!M96="WIN",Trades!M96="LOSS"),B95+Trades!N96,B95)</f>
+        <v/>
+      </c>
+      <c r="C96" s="20">
+        <f>MIN(0,B96-MAX($B$2:B96))</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="E97" s="4">
-        <f>IF(OR(Trades!M86="WIN",Trades!M86="LOSS"),E96+Trades!N86,E96)</f>
-        <v/>
-      </c>
-      <c r="F97" s="15">
-        <f>MIN(0,E97-MAX($E$13:E97))</f>
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4">
+        <f>IF(OR(Trades!M97="WIN",Trades!M97="LOSS"),B96+Trades!N97,B96)</f>
+        <v/>
+      </c>
+      <c r="C97" s="20">
+        <f>MIN(0,B97-MAX($B$2:B97))</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="E98" s="4">
-        <f>IF(OR(Trades!M87="WIN",Trades!M87="LOSS"),E97+Trades!N87,E97)</f>
-        <v/>
-      </c>
-      <c r="F98" s="15">
-        <f>MIN(0,E98-MAX($E$13:E98))</f>
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="4">
+        <f>IF(OR(Trades!M98="WIN",Trades!M98="LOSS"),B97+Trades!N98,B97)</f>
+        <v/>
+      </c>
+      <c r="C98" s="20">
+        <f>MIN(0,B98-MAX($B$2:B98))</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="E99" s="4">
-        <f>IF(OR(Trades!M88="WIN",Trades!M88="LOSS"),E98+Trades!N88,E98)</f>
-        <v/>
-      </c>
-      <c r="F99" s="15">
-        <f>MIN(0,E99-MAX($E$13:E99))</f>
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="4">
+        <f>IF(OR(Trades!M99="WIN",Trades!M99="LOSS"),B98+Trades!N99,B98)</f>
+        <v/>
+      </c>
+      <c r="C99" s="20">
+        <f>MIN(0,B99-MAX($B$2:B99))</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="E100" s="4">
-        <f>IF(OR(Trades!M89="WIN",Trades!M89="LOSS"),E99+Trades!N89,E99)</f>
-        <v/>
-      </c>
-      <c r="F100" s="15">
-        <f>MIN(0,E100-MAX($E$13:E100))</f>
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="4">
+        <f>IF(OR(Trades!M100="WIN",Trades!M100="LOSS"),B99+Trades!N100,B99)</f>
+        <v/>
+      </c>
+      <c r="C100" s="20">
+        <f>MIN(0,B100-MAX($B$2:B100))</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="E101" s="4">
-        <f>IF(OR(Trades!M90="WIN",Trades!M90="LOSS"),E100+Trades!N90,E100)</f>
-        <v/>
-      </c>
-      <c r="F101" s="15">
-        <f>MIN(0,E101-MAX($E$13:E101))</f>
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="4">
+        <f>IF(OR(Trades!M101="WIN",Trades!M101="LOSS"),B100+Trades!N101,B100)</f>
+        <v/>
+      </c>
+      <c r="C101" s="20">
+        <f>MIN(0,B101-MAX($B$2:B101))</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="E102" s="4">
-        <f>IF(OR(Trades!M91="WIN",Trades!M91="LOSS"),E101+Trades!N91,E101)</f>
-        <v/>
-      </c>
-      <c r="F102" s="15">
-        <f>MIN(0,E102-MAX($E$13:E102))</f>
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="4">
+        <f>IF(OR(Trades!M102="WIN",Trades!M102="LOSS"),B101+Trades!N102,B101)</f>
+        <v/>
+      </c>
+      <c r="C102" s="20">
+        <f>MIN(0,B102-MAX($B$2:B102))</f>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="E103" s="4">
-        <f>IF(OR(Trades!M92="WIN",Trades!M92="LOSS"),E102+Trades!N92,E102)</f>
-        <v/>
-      </c>
-      <c r="F103" s="15">
-        <f>MIN(0,E103-MAX($E$13:E103))</f>
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="4">
+        <f>IF(OR(Trades!M103="WIN",Trades!M103="LOSS"),B102+Trades!N103,B102)</f>
+        <v/>
+      </c>
+      <c r="C103" s="20">
+        <f>MIN(0,B103-MAX($B$2:B103))</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="E104" s="4">
-        <f>IF(OR(Trades!M93="WIN",Trades!M93="LOSS"),E103+Trades!N93,E103)</f>
-        <v/>
-      </c>
-      <c r="F104" s="15">
-        <f>MIN(0,E104-MAX($E$13:E104))</f>
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="4">
+        <f>IF(OR(Trades!M104="WIN",Trades!M104="LOSS"),B103+Trades!N104,B103)</f>
+        <v/>
+      </c>
+      <c r="C104" s="20">
+        <f>MIN(0,B104-MAX($B$2:B104))</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="E105" s="4">
-        <f>IF(OR(Trades!M94="WIN",Trades!M94="LOSS"),E104+Trades!N94,E104)</f>
-        <v/>
-      </c>
-      <c r="F105" s="15">
-        <f>MIN(0,E105-MAX($E$13:E105))</f>
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="4">
+        <f>IF(OR(Trades!M105="WIN",Trades!M105="LOSS"),B104+Trades!N105,B104)</f>
+        <v/>
+      </c>
+      <c r="C105" s="20">
+        <f>MIN(0,B105-MAX($B$2:B105))</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="E106" s="4">
-        <f>IF(OR(Trades!M95="WIN",Trades!M95="LOSS"),E105+Trades!N95,E105)</f>
-        <v/>
-      </c>
-      <c r="F106" s="15">
-        <f>MIN(0,E106-MAX($E$13:E106))</f>
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="4">
+        <f>IF(OR(Trades!M106="WIN",Trades!M106="LOSS"),B105+Trades!N106,B105)</f>
+        <v/>
+      </c>
+      <c r="C106" s="20">
+        <f>MIN(0,B106-MAX($B$2:B106))</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="E107" s="4">
-        <f>IF(OR(Trades!M96="WIN",Trades!M96="LOSS"),E106+Trades!N96,E106)</f>
-        <v/>
-      </c>
-      <c r="F107" s="15">
-        <f>MIN(0,E107-MAX($E$13:E107))</f>
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="4">
+        <f>IF(OR(Trades!M107="WIN",Trades!M107="LOSS"),B106+Trades!N107,B106)</f>
+        <v/>
+      </c>
+      <c r="C107" s="20">
+        <f>MIN(0,B107-MAX($B$2:B107))</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="E108" s="4">
-        <f>IF(OR(Trades!M97="WIN",Trades!M97="LOSS"),E107+Trades!N97,E107)</f>
-        <v/>
-      </c>
-      <c r="F108" s="15">
-        <f>MIN(0,E108-MAX($E$13:E108))</f>
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="4">
+        <f>IF(OR(Trades!M108="WIN",Trades!M108="LOSS"),B107+Trades!N108,B107)</f>
+        <v/>
+      </c>
+      <c r="C108" s="20">
+        <f>MIN(0,B108-MAX($B$2:B108))</f>
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="E109" s="4">
-        <f>IF(OR(Trades!M98="WIN",Trades!M98="LOSS"),E108+Trades!N98,E108)</f>
-        <v/>
-      </c>
-      <c r="F109" s="15">
-        <f>MIN(0,E109-MAX($E$13:E109))</f>
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="4">
+        <f>IF(OR(Trades!M109="WIN",Trades!M109="LOSS"),B108+Trades!N109,B108)</f>
+        <v/>
+      </c>
+      <c r="C109" s="20">
+        <f>MIN(0,B109-MAX($B$2:B109))</f>
         <v/>
       </c>
     </row>
     <row r="110">
-      <c r="E110" s="4">
-        <f>IF(OR(Trades!M99="WIN",Trades!M99="LOSS"),E109+Trades!N99,E109)</f>
-        <v/>
-      </c>
-      <c r="F110" s="15">
-        <f>MIN(0,E110-MAX($E$13:E110))</f>
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="4">
+        <f>IF(OR(Trades!M110="WIN",Trades!M110="LOSS"),B109+Trades!N110,B109)</f>
+        <v/>
+      </c>
+      <c r="C110" s="20">
+        <f>MIN(0,B110-MAX($B$2:B110))</f>
         <v/>
       </c>
     </row>
     <row r="111">
-      <c r="E111" s="4">
-        <f>IF(OR(Trades!M100="WIN",Trades!M100="LOSS"),E110+Trades!N100,E110)</f>
-        <v/>
-      </c>
-      <c r="F111" s="15">
-        <f>MIN(0,E111-MAX($E$13:E111))</f>
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="4">
+        <f>IF(OR(Trades!M111="WIN",Trades!M111="LOSS"),B110+Trades!N111,B110)</f>
+        <v/>
+      </c>
+      <c r="C111" s="20">
+        <f>MIN(0,B111-MAX($B$2:B111))</f>
         <v/>
       </c>
     </row>
     <row r="112">
-      <c r="E112" s="4">
-        <f>IF(OR(Trades!M101="WIN",Trades!M101="LOSS"),E111+Trades!N101,E111)</f>
-        <v/>
-      </c>
-      <c r="F112" s="15">
-        <f>MIN(0,E112-MAX($E$13:E112))</f>
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="4">
+        <f>IF(OR(Trades!M112="WIN",Trades!M112="LOSS"),B111+Trades!N112,B111)</f>
+        <v/>
+      </c>
+      <c r="C112" s="20">
+        <f>MIN(0,B112-MAX($B$2:B112))</f>
         <v/>
       </c>
     </row>
     <row r="113">
-      <c r="E113" s="4">
-        <f>IF(OR(Trades!M102="WIN",Trades!M102="LOSS"),E112+Trades!N102,E112)</f>
-        <v/>
-      </c>
-      <c r="F113" s="15">
-        <f>MIN(0,E113-MAX($E$13:E113))</f>
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="4">
+        <f>IF(OR(Trades!M113="WIN",Trades!M113="LOSS"),B112+Trades!N113,B112)</f>
+        <v/>
+      </c>
+      <c r="C113" s="20">
+        <f>MIN(0,B113-MAX($B$2:B113))</f>
         <v/>
       </c>
     </row>
     <row r="114">
-      <c r="E114" s="4">
-        <f>IF(OR(Trades!M103="WIN",Trades!M103="LOSS"),E113+Trades!N103,E113)</f>
-        <v/>
-      </c>
-      <c r="F114" s="15">
-        <f>MIN(0,E114-MAX($E$13:E114))</f>
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="4">
+        <f>IF(OR(Trades!M114="WIN",Trades!M114="LOSS"),B113+Trades!N114,B113)</f>
+        <v/>
+      </c>
+      <c r="C114" s="20">
+        <f>MIN(0,B114-MAX($B$2:B114))</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="E115" s="4">
-        <f>IF(OR(Trades!M104="WIN",Trades!M104="LOSS"),E114+Trades!N104,E114)</f>
-        <v/>
-      </c>
-      <c r="F115" s="15">
-        <f>MIN(0,E115-MAX($E$13:E115))</f>
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="4">
+        <f>IF(OR(Trades!M115="WIN",Trades!M115="LOSS"),B114+Trades!N115,B114)</f>
+        <v/>
+      </c>
+      <c r="C115" s="20">
+        <f>MIN(0,B115-MAX($B$2:B115))</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="E116" s="4">
-        <f>IF(OR(Trades!M105="WIN",Trades!M105="LOSS"),E115+Trades!N105,E115)</f>
-        <v/>
-      </c>
-      <c r="F116" s="15">
-        <f>MIN(0,E116-MAX($E$13:E116))</f>
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="4">
+        <f>IF(OR(Trades!M116="WIN",Trades!M116="LOSS"),B115+Trades!N116,B115)</f>
+        <v/>
+      </c>
+      <c r="C116" s="20">
+        <f>MIN(0,B116-MAX($B$2:B116))</f>
         <v/>
       </c>
     </row>
     <row r="117">
-      <c r="E117" s="4">
-        <f>IF(OR(Trades!M106="WIN",Trades!M106="LOSS"),E116+Trades!N106,E116)</f>
-        <v/>
-      </c>
-      <c r="F117" s="15">
-        <f>MIN(0,E117-MAX($E$13:E117))</f>
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="4">
+        <f>IF(OR(Trades!M117="WIN",Trades!M117="LOSS"),B116+Trades!N117,B116)</f>
+        <v/>
+      </c>
+      <c r="C117" s="20">
+        <f>MIN(0,B117-MAX($B$2:B117))</f>
         <v/>
       </c>
     </row>
     <row r="118">
-      <c r="E118" s="4">
-        <f>IF(OR(Trades!M107="WIN",Trades!M107="LOSS"),E117+Trades!N107,E117)</f>
-        <v/>
-      </c>
-      <c r="F118" s="15">
-        <f>MIN(0,E118-MAX($E$13:E118))</f>
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="4">
+        <f>IF(OR(Trades!M118="WIN",Trades!M118="LOSS"),B117+Trades!N118,B117)</f>
+        <v/>
+      </c>
+      <c r="C118" s="20">
+        <f>MIN(0,B118-MAX($B$2:B118))</f>
         <v/>
       </c>
     </row>
     <row r="119">
-      <c r="E119" s="4">
-        <f>IF(OR(Trades!M108="WIN",Trades!M108="LOSS"),E118+Trades!N108,E118)</f>
-        <v/>
-      </c>
-      <c r="F119" s="15">
-        <f>MIN(0,E119-MAX($E$13:E119))</f>
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="4">
+        <f>IF(OR(Trades!M119="WIN",Trades!M119="LOSS"),B118+Trades!N119,B118)</f>
+        <v/>
+      </c>
+      <c r="C119" s="20">
+        <f>MIN(0,B119-MAX($B$2:B119))</f>
         <v/>
       </c>
     </row>
     <row r="120">
-      <c r="E120" s="4">
-        <f>IF(OR(Trades!M109="WIN",Trades!M109="LOSS"),E119+Trades!N109,E119)</f>
-        <v/>
-      </c>
-      <c r="F120" s="15">
-        <f>MIN(0,E120-MAX($E$13:E120))</f>
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="4">
+        <f>IF(OR(Trades!M120="WIN",Trades!M120="LOSS"),B119+Trades!N120,B119)</f>
+        <v/>
+      </c>
+      <c r="C120" s="20">
+        <f>MIN(0,B120-MAX($B$2:B120))</f>
         <v/>
       </c>
     </row>
     <row r="121">
-      <c r="E121" s="4">
-        <f>IF(OR(Trades!M110="WIN",Trades!M110="LOSS"),E120+Trades!N110,E120)</f>
-        <v/>
-      </c>
-      <c r="F121" s="15">
-        <f>MIN(0,E121-MAX($E$13:E121))</f>
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="4">
+        <f>IF(OR(Trades!M121="WIN",Trades!M121="LOSS"),B120+Trades!N121,B120)</f>
+        <v/>
+      </c>
+      <c r="C121" s="20">
+        <f>MIN(0,B121-MAX($B$2:B121))</f>
         <v/>
       </c>
     </row>
     <row r="122">
-      <c r="E122" s="4">
-        <f>IF(OR(Trades!M111="WIN",Trades!M111="LOSS"),E121+Trades!N111,E121)</f>
-        <v/>
-      </c>
-      <c r="F122" s="15">
-        <f>MIN(0,E122-MAX($E$13:E122))</f>
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="4">
+        <f>IF(OR(Trades!M122="WIN",Trades!M122="LOSS"),B121+Trades!N122,B121)</f>
+        <v/>
+      </c>
+      <c r="C122" s="20">
+        <f>MIN(0,B122-MAX($B$2:B122))</f>
         <v/>
       </c>
     </row>
     <row r="123">
-      <c r="E123" s="4">
-        <f>IF(OR(Trades!M112="WIN",Trades!M112="LOSS"),E122+Trades!N112,E122)</f>
-        <v/>
-      </c>
-      <c r="F123" s="15">
-        <f>MIN(0,E123-MAX($E$13:E123))</f>
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="4">
+        <f>IF(OR(Trades!M123="WIN",Trades!M123="LOSS"),B122+Trades!N123,B122)</f>
+        <v/>
+      </c>
+      <c r="C123" s="20">
+        <f>MIN(0,B123-MAX($B$2:B123))</f>
         <v/>
       </c>
     </row>
     <row r="124">
-      <c r="E124" s="4">
-        <f>IF(OR(Trades!M113="WIN",Trades!M113="LOSS"),E123+Trades!N113,E123)</f>
-        <v/>
-      </c>
-      <c r="F124" s="15">
-        <f>MIN(0,E124-MAX($E$13:E124))</f>
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="4">
+        <f>IF(OR(Trades!M124="WIN",Trades!M124="LOSS"),B123+Trades!N124,B123)</f>
+        <v/>
+      </c>
+      <c r="C124" s="20">
+        <f>MIN(0,B124-MAX($B$2:B124))</f>
         <v/>
       </c>
     </row>
     <row r="125">
-      <c r="E125" s="4">
-        <f>IF(OR(Trades!M114="WIN",Trades!M114="LOSS"),E124+Trades!N114,E124)</f>
-        <v/>
-      </c>
-      <c r="F125" s="15">
-        <f>MIN(0,E125-MAX($E$13:E125))</f>
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="4">
+        <f>IF(OR(Trades!M125="WIN",Trades!M125="LOSS"),B124+Trades!N125,B124)</f>
+        <v/>
+      </c>
+      <c r="C125" s="20">
+        <f>MIN(0,B125-MAX($B$2:B125))</f>
         <v/>
       </c>
     </row>
     <row r="126">
-      <c r="E126" s="4">
-        <f>IF(OR(Trades!M115="WIN",Trades!M115="LOSS"),E125+Trades!N115,E125)</f>
-        <v/>
-      </c>
-      <c r="F126" s="15">
-        <f>MIN(0,E126-MAX($E$13:E126))</f>
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="4">
+        <f>IF(OR(Trades!M126="WIN",Trades!M126="LOSS"),B125+Trades!N126,B125)</f>
+        <v/>
+      </c>
+      <c r="C126" s="20">
+        <f>MIN(0,B126-MAX($B$2:B126))</f>
         <v/>
       </c>
     </row>
     <row r="127">
-      <c r="E127" s="4">
-        <f>IF(OR(Trades!M116="WIN",Trades!M116="LOSS"),E126+Trades!N116,E126)</f>
-        <v/>
-      </c>
-      <c r="F127" s="15">
-        <f>MIN(0,E127-MAX($E$13:E127))</f>
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="4">
+        <f>IF(OR(Trades!M127="WIN",Trades!M127="LOSS"),B126+Trades!N127,B126)</f>
+        <v/>
+      </c>
+      <c r="C127" s="20">
+        <f>MIN(0,B127-MAX($B$2:B127))</f>
         <v/>
       </c>
     </row>
     <row r="128">
-      <c r="E128" s="4">
-        <f>IF(OR(Trades!M117="WIN",Trades!M117="LOSS"),E127+Trades!N117,E127)</f>
-        <v/>
-      </c>
-      <c r="F128" s="15">
-        <f>MIN(0,E128-MAX($E$13:E128))</f>
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="4">
+        <f>IF(OR(Trades!M128="WIN",Trades!M128="LOSS"),B127+Trades!N128,B127)</f>
+        <v/>
+      </c>
+      <c r="C128" s="20">
+        <f>MIN(0,B128-MAX($B$2:B128))</f>
         <v/>
       </c>
     </row>
     <row r="129">
-      <c r="E129" s="4">
-        <f>IF(OR(Trades!M118="WIN",Trades!M118="LOSS"),E128+Trades!N118,E128)</f>
-        <v/>
-      </c>
-      <c r="F129" s="15">
-        <f>MIN(0,E129-MAX($E$13:E129))</f>
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="4">
+        <f>IF(OR(Trades!M129="WIN",Trades!M129="LOSS"),B128+Trades!N129,B128)</f>
+        <v/>
+      </c>
+      <c r="C129" s="20">
+        <f>MIN(0,B129-MAX($B$2:B129))</f>
         <v/>
       </c>
     </row>
     <row r="130">
-      <c r="E130" s="4">
-        <f>IF(OR(Trades!M119="WIN",Trades!M119="LOSS"),E129+Trades!N119,E129)</f>
-        <v/>
-      </c>
-      <c r="F130" s="15">
-        <f>MIN(0,E130-MAX($E$13:E130))</f>
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="4">
+        <f>IF(OR(Trades!M130="WIN",Trades!M130="LOSS"),B129+Trades!N130,B129)</f>
+        <v/>
+      </c>
+      <c r="C130" s="20">
+        <f>MIN(0,B130-MAX($B$2:B130))</f>
         <v/>
       </c>
     </row>
     <row r="131">
-      <c r="E131" s="4">
-        <f>IF(OR(Trades!M120="WIN",Trades!M120="LOSS"),E130+Trades!N120,E130)</f>
-        <v/>
-      </c>
-      <c r="F131" s="15">
-        <f>MIN(0,E131-MAX($E$13:E131))</f>
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="4">
+        <f>IF(OR(Trades!M131="WIN",Trades!M131="LOSS"),B130+Trades!N131,B130)</f>
+        <v/>
+      </c>
+      <c r="C131" s="20">
+        <f>MIN(0,B131-MAX($B$2:B131))</f>
         <v/>
       </c>
     </row>
     <row r="132">
-      <c r="E132" s="4">
-        <f>IF(OR(Trades!M121="WIN",Trades!M121="LOSS"),E131+Trades!N121,E131)</f>
-        <v/>
-      </c>
-      <c r="F132" s="15">
-        <f>MIN(0,E132-MAX($E$13:E132))</f>
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="4">
+        <f>IF(OR(Trades!M132="WIN",Trades!M132="LOSS"),B131+Trades!N132,B131)</f>
+        <v/>
+      </c>
+      <c r="C132" s="20">
+        <f>MIN(0,B132-MAX($B$2:B132))</f>
         <v/>
       </c>
     </row>
     <row r="133">
-      <c r="E133" s="4">
-        <f>IF(OR(Trades!M122="WIN",Trades!M122="LOSS"),E132+Trades!N122,E132)</f>
-        <v/>
-      </c>
-      <c r="F133" s="15">
-        <f>MIN(0,E133-MAX($E$13:E133))</f>
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="4">
+        <f>IF(OR(Trades!M133="WIN",Trades!M133="LOSS"),B132+Trades!N133,B132)</f>
+        <v/>
+      </c>
+      <c r="C133" s="20">
+        <f>MIN(0,B133-MAX($B$2:B133))</f>
         <v/>
       </c>
     </row>
     <row r="134">
-      <c r="E134" s="4">
-        <f>IF(OR(Trades!M123="WIN",Trades!M123="LOSS"),E133+Trades!N123,E133)</f>
-        <v/>
-      </c>
-      <c r="F134" s="15">
-        <f>MIN(0,E134-MAX($E$13:E134))</f>
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="4">
+        <f>IF(OR(Trades!M134="WIN",Trades!M134="LOSS"),B133+Trades!N134,B133)</f>
+        <v/>
+      </c>
+      <c r="C134" s="20">
+        <f>MIN(0,B134-MAX($B$2:B134))</f>
         <v/>
       </c>
     </row>
     <row r="135">
-      <c r="E135" s="4">
-        <f>IF(OR(Trades!M124="WIN",Trades!M124="LOSS"),E134+Trades!N124,E134)</f>
-        <v/>
-      </c>
-      <c r="F135" s="15">
-        <f>MIN(0,E135-MAX($E$13:E135))</f>
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="4">
+        <f>IF(OR(Trades!M135="WIN",Trades!M135="LOSS"),B134+Trades!N135,B134)</f>
+        <v/>
+      </c>
+      <c r="C135" s="20">
+        <f>MIN(0,B135-MAX($B$2:B135))</f>
         <v/>
       </c>
     </row>
     <row r="136">
-      <c r="E136" s="4">
-        <f>IF(OR(Trades!M125="WIN",Trades!M125="LOSS"),E135+Trades!N125,E135)</f>
-        <v/>
-      </c>
-      <c r="F136" s="15">
-        <f>MIN(0,E136-MAX($E$13:E136))</f>
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="4">
+        <f>IF(OR(Trades!M136="WIN",Trades!M136="LOSS"),B135+Trades!N136,B135)</f>
+        <v/>
+      </c>
+      <c r="C136" s="20">
+        <f>MIN(0,B136-MAX($B$2:B136))</f>
         <v/>
       </c>
     </row>
     <row r="137">
-      <c r="E137" s="4">
-        <f>IF(OR(Trades!M126="WIN",Trades!M126="LOSS"),E136+Trades!N126,E136)</f>
-        <v/>
-      </c>
-      <c r="F137" s="15">
-        <f>MIN(0,E137-MAX($E$13:E137))</f>
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="4">
+        <f>IF(OR(Trades!M137="WIN",Trades!M137="LOSS"),B136+Trades!N137,B136)</f>
+        <v/>
+      </c>
+      <c r="C137" s="20">
+        <f>MIN(0,B137-MAX($B$2:B137))</f>
         <v/>
       </c>
     </row>
     <row r="138">
-      <c r="E138" s="4">
-        <f>IF(OR(Trades!M127="WIN",Trades!M127="LOSS"),E137+Trades!N127,E137)</f>
-        <v/>
-      </c>
-      <c r="F138" s="15">
-        <f>MIN(0,E138-MAX($E$13:E138))</f>
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="4">
+        <f>IF(OR(Trades!M138="WIN",Trades!M138="LOSS"),B137+Trades!N138,B137)</f>
+        <v/>
+      </c>
+      <c r="C138" s="20">
+        <f>MIN(0,B138-MAX($B$2:B138))</f>
         <v/>
       </c>
     </row>
     <row r="139">
-      <c r="E139" s="4">
-        <f>IF(OR(Trades!M128="WIN",Trades!M128="LOSS"),E138+Trades!N128,E138)</f>
-        <v/>
-      </c>
-      <c r="F139" s="15">
-        <f>MIN(0,E139-MAX($E$13:E139))</f>
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="4">
+        <f>IF(OR(Trades!M139="WIN",Trades!M139="LOSS"),B138+Trades!N139,B138)</f>
+        <v/>
+      </c>
+      <c r="C139" s="20">
+        <f>MIN(0,B139-MAX($B$2:B139))</f>
         <v/>
       </c>
     </row>
     <row r="140">
-      <c r="E140" s="4">
-        <f>IF(OR(Trades!M129="WIN",Trades!M129="LOSS"),E139+Trades!N129,E139)</f>
-        <v/>
-      </c>
-      <c r="F140" s="15">
-        <f>MIN(0,E140-MAX($E$13:E140))</f>
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="4">
+        <f>IF(OR(Trades!M140="WIN",Trades!M140="LOSS"),B139+Trades!N140,B139)</f>
+        <v/>
+      </c>
+      <c r="C140" s="20">
+        <f>MIN(0,B140-MAX($B$2:B140))</f>
         <v/>
       </c>
     </row>
     <row r="141">
-      <c r="E141" s="4">
-        <f>IF(OR(Trades!M130="WIN",Trades!M130="LOSS"),E140+Trades!N130,E140)</f>
-        <v/>
-      </c>
-      <c r="F141" s="15">
-        <f>MIN(0,E141-MAX($E$13:E141))</f>
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="4">
+        <f>IF(OR(Trades!M141="WIN",Trades!M141="LOSS"),B140+Trades!N141,B140)</f>
+        <v/>
+      </c>
+      <c r="C141" s="20">
+        <f>MIN(0,B141-MAX($B$2:B141))</f>
         <v/>
       </c>
     </row>
     <row r="142">
-      <c r="E142" s="4">
-        <f>IF(OR(Trades!M131="WIN",Trades!M131="LOSS"),E141+Trades!N131,E141)</f>
-        <v/>
-      </c>
-      <c r="F142" s="15">
-        <f>MIN(0,E142-MAX($E$13:E142))</f>
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="4">
+        <f>IF(OR(Trades!M142="WIN",Trades!M142="LOSS"),B141+Trades!N142,B141)</f>
+        <v/>
+      </c>
+      <c r="C142" s="20">
+        <f>MIN(0,B142-MAX($B$2:B142))</f>
         <v/>
       </c>
     </row>
     <row r="143">
-      <c r="E143" s="4">
-        <f>IF(OR(Trades!M132="WIN",Trades!M132="LOSS"),E142+Trades!N132,E142)</f>
-        <v/>
-      </c>
-      <c r="F143" s="15">
-        <f>MIN(0,E143-MAX($E$13:E143))</f>
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="4">
+        <f>IF(OR(Trades!M143="WIN",Trades!M143="LOSS"),B142+Trades!N143,B142)</f>
+        <v/>
+      </c>
+      <c r="C143" s="20">
+        <f>MIN(0,B143-MAX($B$2:B143))</f>
         <v/>
       </c>
     </row>
     <row r="144">
-      <c r="E144" s="4">
-        <f>IF(OR(Trades!M133="WIN",Trades!M133="LOSS"),E143+Trades!N133,E143)</f>
-        <v/>
-      </c>
-      <c r="F144" s="15">
-        <f>MIN(0,E144-MAX($E$13:E144))</f>
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="4">
+        <f>IF(OR(Trades!M144="WIN",Trades!M144="LOSS"),B143+Trades!N144,B143)</f>
+        <v/>
+      </c>
+      <c r="C144" s="20">
+        <f>MIN(0,B144-MAX($B$2:B144))</f>
         <v/>
       </c>
     </row>
     <row r="145">
-      <c r="E145" s="4">
-        <f>IF(OR(Trades!M134="WIN",Trades!M134="LOSS"),E144+Trades!N134,E144)</f>
-        <v/>
-      </c>
-      <c r="F145" s="15">
-        <f>MIN(0,E145-MAX($E$13:E145))</f>
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="4">
+        <f>IF(OR(Trades!M145="WIN",Trades!M145="LOSS"),B144+Trades!N145,B144)</f>
+        <v/>
+      </c>
+      <c r="C145" s="20">
+        <f>MIN(0,B145-MAX($B$2:B145))</f>
         <v/>
       </c>
     </row>
     <row r="146">
-      <c r="E146" s="4">
-        <f>IF(OR(Trades!M135="WIN",Trades!M135="LOSS"),E145+Trades!N135,E145)</f>
-        <v/>
-      </c>
-      <c r="F146" s="15">
-        <f>MIN(0,E146-MAX($E$13:E146))</f>
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="4">
+        <f>IF(OR(Trades!M146="WIN",Trades!M146="LOSS"),B145+Trades!N146,B145)</f>
+        <v/>
+      </c>
+      <c r="C146" s="20">
+        <f>MIN(0,B146-MAX($B$2:B146))</f>
         <v/>
       </c>
     </row>
     <row r="147">
-      <c r="E147" s="4">
-        <f>IF(OR(Trades!M136="WIN",Trades!M136="LOSS"),E146+Trades!N136,E146)</f>
-        <v/>
-      </c>
-      <c r="F147" s="15">
-        <f>MIN(0,E147-MAX($E$13:E147))</f>
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="4">
+        <f>IF(OR(Trades!M147="WIN",Trades!M147="LOSS"),B146+Trades!N147,B146)</f>
+        <v/>
+      </c>
+      <c r="C147" s="20">
+        <f>MIN(0,B147-MAX($B$2:B147))</f>
         <v/>
       </c>
     </row>
     <row r="148">
-      <c r="E148" s="4">
-        <f>IF(OR(Trades!M137="WIN",Trades!M137="LOSS"),E147+Trades!N137,E147)</f>
-        <v/>
-      </c>
-      <c r="F148" s="15">
-        <f>MIN(0,E148-MAX($E$13:E148))</f>
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="4">
+        <f>IF(OR(Trades!M148="WIN",Trades!M148="LOSS"),B147+Trades!N148,B147)</f>
+        <v/>
+      </c>
+      <c r="C148" s="20">
+        <f>MIN(0,B148-MAX($B$2:B148))</f>
         <v/>
       </c>
     </row>
     <row r="149">
-      <c r="E149" s="4">
-        <f>IF(OR(Trades!M138="WIN",Trades!M138="LOSS"),E148+Trades!N138,E148)</f>
-        <v/>
-      </c>
-      <c r="F149" s="15">
-        <f>MIN(0,E149-MAX($E$13:E149))</f>
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="4">
+        <f>IF(OR(Trades!M149="WIN",Trades!M149="LOSS"),B148+Trades!N149,B148)</f>
+        <v/>
+      </c>
+      <c r="C149" s="20">
+        <f>MIN(0,B149-MAX($B$2:B149))</f>
         <v/>
       </c>
     </row>
     <row r="150">
-      <c r="E150" s="4">
-        <f>IF(OR(Trades!M139="WIN",Trades!M139="LOSS"),E149+Trades!N139,E149)</f>
-        <v/>
-      </c>
-      <c r="F150" s="15">
-        <f>MIN(0,E150-MAX($E$13:E150))</f>
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="4">
+        <f>IF(OR(Trades!M150="WIN",Trades!M150="LOSS"),B149+Trades!N150,B149)</f>
+        <v/>
+      </c>
+      <c r="C150" s="20">
+        <f>MIN(0,B150-MAX($B$2:B150))</f>
         <v/>
       </c>
     </row>
     <row r="151">
-      <c r="E151" s="4">
-        <f>IF(OR(Trades!M140="WIN",Trades!M140="LOSS"),E150+Trades!N140,E150)</f>
-        <v/>
-      </c>
-      <c r="F151" s="15">
-        <f>MIN(0,E151-MAX($E$13:E151))</f>
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="4">
+        <f>IF(OR(Trades!M151="WIN",Trades!M151="LOSS"),B150+Trades!N151,B150)</f>
+        <v/>
+      </c>
+      <c r="C151" s="20">
+        <f>MIN(0,B151-MAX($B$2:B151))</f>
         <v/>
       </c>
     </row>
     <row r="152">
-      <c r="E152" s="4">
-        <f>IF(OR(Trades!M141="WIN",Trades!M141="LOSS"),E151+Trades!N141,E151)</f>
-        <v/>
-      </c>
-      <c r="F152" s="15">
-        <f>MIN(0,E152-MAX($E$13:E152))</f>
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="4">
+        <f>IF(OR(Trades!M152="WIN",Trades!M152="LOSS"),B151+Trades!N152,B151)</f>
+        <v/>
+      </c>
+      <c r="C152" s="20">
+        <f>MIN(0,B152-MAX($B$2:B152))</f>
         <v/>
       </c>
     </row>
     <row r="153">
-      <c r="E153" s="4">
-        <f>IF(OR(Trades!M142="WIN",Trades!M142="LOSS"),E152+Trades!N142,E152)</f>
-        <v/>
-      </c>
-      <c r="F153" s="15">
-        <f>MIN(0,E153-MAX($E$13:E153))</f>
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="4">
+        <f>IF(OR(Trades!M153="WIN",Trades!M153="LOSS"),B152+Trades!N153,B152)</f>
+        <v/>
+      </c>
+      <c r="C153" s="20">
+        <f>MIN(0,B153-MAX($B$2:B153))</f>
         <v/>
       </c>
     </row>
     <row r="154">
-      <c r="E154" s="4">
-        <f>IF(OR(Trades!M143="WIN",Trades!M143="LOSS"),E153+Trades!N143,E153)</f>
-        <v/>
-      </c>
-      <c r="F154" s="15">
-        <f>MIN(0,E154-MAX($E$13:E154))</f>
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="4">
+        <f>IF(OR(Trades!M154="WIN",Trades!M154="LOSS"),B153+Trades!N154,B153)</f>
+        <v/>
+      </c>
+      <c r="C154" s="20">
+        <f>MIN(0,B154-MAX($B$2:B154))</f>
         <v/>
       </c>
     </row>
     <row r="155">
-      <c r="E155" s="4">
-        <f>IF(OR(Trades!M144="WIN",Trades!M144="LOSS"),E154+Trades!N144,E154)</f>
-        <v/>
-      </c>
-      <c r="F155" s="15">
-        <f>MIN(0,E155-MAX($E$13:E155))</f>
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="4">
+        <f>IF(OR(Trades!M155="WIN",Trades!M155="LOSS"),B154+Trades!N155,B154)</f>
+        <v/>
+      </c>
+      <c r="C155" s="20">
+        <f>MIN(0,B155-MAX($B$2:B155))</f>
         <v/>
       </c>
     </row>
     <row r="156">
-      <c r="E156" s="4">
-        <f>IF(OR(Trades!M145="WIN",Trades!M145="LOSS"),E155+Trades!N145,E155)</f>
-        <v/>
-      </c>
-      <c r="F156" s="15">
-        <f>MIN(0,E156-MAX($E$13:E156))</f>
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="4">
+        <f>IF(OR(Trades!M156="WIN",Trades!M156="LOSS"),B155+Trades!N156,B155)</f>
+        <v/>
+      </c>
+      <c r="C156" s="20">
+        <f>MIN(0,B156-MAX($B$2:B156))</f>
         <v/>
       </c>
     </row>
     <row r="157">
-      <c r="E157" s="4">
-        <f>IF(OR(Trades!M146="WIN",Trades!M146="LOSS"),E156+Trades!N146,E156)</f>
-        <v/>
-      </c>
-      <c r="F157" s="15">
-        <f>MIN(0,E157-MAX($E$13:E157))</f>
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="4">
+        <f>IF(OR(Trades!M157="WIN",Trades!M157="LOSS"),B156+Trades!N157,B156)</f>
+        <v/>
+      </c>
+      <c r="C157" s="20">
+        <f>MIN(0,B157-MAX($B$2:B157))</f>
         <v/>
       </c>
     </row>
     <row r="158">
-      <c r="E158" s="4">
-        <f>IF(OR(Trades!M147="WIN",Trades!M147="LOSS"),E157+Trades!N147,E157)</f>
-        <v/>
-      </c>
-      <c r="F158" s="15">
-        <f>MIN(0,E158-MAX($E$13:E158))</f>
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="4">
+        <f>IF(OR(Trades!M158="WIN",Trades!M158="LOSS"),B157+Trades!N158,B157)</f>
+        <v/>
+      </c>
+      <c r="C158" s="20">
+        <f>MIN(0,B158-MAX($B$2:B158))</f>
         <v/>
       </c>
     </row>
     <row r="159">
-      <c r="E159" s="4">
-        <f>IF(OR(Trades!M148="WIN",Trades!M148="LOSS"),E158+Trades!N148,E158)</f>
-        <v/>
-      </c>
-      <c r="F159" s="15">
-        <f>MIN(0,E159-MAX($E$13:E159))</f>
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="4">
+        <f>IF(OR(Trades!M159="WIN",Trades!M159="LOSS"),B158+Trades!N159,B158)</f>
+        <v/>
+      </c>
+      <c r="C159" s="20">
+        <f>MIN(0,B159-MAX($B$2:B159))</f>
         <v/>
       </c>
     </row>
     <row r="160">
-      <c r="E160" s="4">
-        <f>IF(OR(Trades!M149="WIN",Trades!M149="LOSS"),E159+Trades!N149,E159)</f>
-        <v/>
-      </c>
-      <c r="F160" s="15">
-        <f>MIN(0,E160-MAX($E$13:E160))</f>
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="4">
+        <f>IF(OR(Trades!M160="WIN",Trades!M160="LOSS"),B159+Trades!N160,B159)</f>
+        <v/>
+      </c>
+      <c r="C160" s="20">
+        <f>MIN(0,B160-MAX($B$2:B160))</f>
         <v/>
       </c>
     </row>
     <row r="161">
-      <c r="E161" s="4">
-        <f>IF(OR(Trades!M150="WIN",Trades!M150="LOSS"),E160+Trades!N150,E160)</f>
-        <v/>
-      </c>
-      <c r="F161" s="15">
-        <f>MIN(0,E161-MAX($E$13:E161))</f>
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="4">
+        <f>IF(OR(Trades!M161="WIN",Trades!M161="LOSS"),B160+Trades!N161,B160)</f>
+        <v/>
+      </c>
+      <c r="C161" s="20">
+        <f>MIN(0,B161-MAX($B$2:B161))</f>
         <v/>
       </c>
     </row>
     <row r="162">
-      <c r="E162" s="4">
-        <f>IF(OR(Trades!M151="WIN",Trades!M151="LOSS"),E161+Trades!N151,E161)</f>
-        <v/>
-      </c>
-      <c r="F162" s="15">
-        <f>MIN(0,E162-MAX($E$13:E162))</f>
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="4">
+        <f>IF(OR(Trades!M162="WIN",Trades!M162="LOSS"),B161+Trades!N162,B161)</f>
+        <v/>
+      </c>
+      <c r="C162" s="20">
+        <f>MIN(0,B162-MAX($B$2:B162))</f>
         <v/>
       </c>
     </row>
     <row r="163">
-      <c r="E163" s="4">
-        <f>IF(OR(Trades!M152="WIN",Trades!M152="LOSS"),E162+Trades!N152,E162)</f>
-        <v/>
-      </c>
-      <c r="F163" s="15">
-        <f>MIN(0,E163-MAX($E$13:E163))</f>
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="4">
+        <f>IF(OR(Trades!M163="WIN",Trades!M163="LOSS"),B162+Trades!N163,B162)</f>
+        <v/>
+      </c>
+      <c r="C163" s="20">
+        <f>MIN(0,B163-MAX($B$2:B163))</f>
         <v/>
       </c>
     </row>
     <row r="164">
-      <c r="E164" s="4">
-        <f>IF(OR(Trades!M153="WIN",Trades!M153="LOSS"),E163+Trades!N153,E163)</f>
-        <v/>
-      </c>
-      <c r="F164" s="15">
-        <f>MIN(0,E164-MAX($E$13:E164))</f>
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="4">
+        <f>IF(OR(Trades!M164="WIN",Trades!M164="LOSS"),B163+Trades!N164,B163)</f>
+        <v/>
+      </c>
+      <c r="C164" s="20">
+        <f>MIN(0,B164-MAX($B$2:B164))</f>
         <v/>
       </c>
     </row>
     <row r="165">
-      <c r="E165" s="4">
-        <f>IF(OR(Trades!M154="WIN",Trades!M154="LOSS"),E164+Trades!N154,E164)</f>
-        <v/>
-      </c>
-      <c r="F165" s="15">
-        <f>MIN(0,E165-MAX($E$13:E165))</f>
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="4">
+        <f>IF(OR(Trades!M165="WIN",Trades!M165="LOSS"),B164+Trades!N165,B164)</f>
+        <v/>
+      </c>
+      <c r="C165" s="20">
+        <f>MIN(0,B165-MAX($B$2:B165))</f>
         <v/>
       </c>
     </row>
     <row r="166">
-      <c r="E166" s="4">
-        <f>IF(OR(Trades!M155="WIN",Trades!M155="LOSS"),E165+Trades!N155,E165)</f>
-        <v/>
-      </c>
-      <c r="F166" s="15">
-        <f>MIN(0,E166-MAX($E$13:E166))</f>
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="4">
+        <f>IF(OR(Trades!M166="WIN",Trades!M166="LOSS"),B165+Trades!N166,B165)</f>
+        <v/>
+      </c>
+      <c r="C166" s="20">
+        <f>MIN(0,B166-MAX($B$2:B166))</f>
         <v/>
       </c>
     </row>
     <row r="167">
-      <c r="E167" s="4">
-        <f>IF(OR(Trades!M156="WIN",Trades!M156="LOSS"),E166+Trades!N156,E166)</f>
-        <v/>
-      </c>
-      <c r="F167" s="15">
-        <f>MIN(0,E167-MAX($E$13:E167))</f>
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="4">
+        <f>IF(OR(Trades!M167="WIN",Trades!M167="LOSS"),B166+Trades!N167,B166)</f>
+        <v/>
+      </c>
+      <c r="C167" s="20">
+        <f>MIN(0,B167-MAX($B$2:B167))</f>
         <v/>
       </c>
     </row>
     <row r="168">
-      <c r="E168" s="4">
-        <f>IF(OR(Trades!M157="WIN",Trades!M157="LOSS"),E167+Trades!N157,E167)</f>
-        <v/>
-      </c>
-      <c r="F168" s="15">
-        <f>MIN(0,E168-MAX($E$13:E168))</f>
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="4">
+        <f>IF(OR(Trades!M168="WIN",Trades!M168="LOSS"),B167+Trades!N168,B167)</f>
+        <v/>
+      </c>
+      <c r="C168" s="20">
+        <f>MIN(0,B168-MAX($B$2:B168))</f>
         <v/>
       </c>
     </row>
     <row r="169">
-      <c r="E169" s="4">
-        <f>IF(OR(Trades!M158="WIN",Trades!M158="LOSS"),E168+Trades!N158,E168)</f>
-        <v/>
-      </c>
-      <c r="F169" s="15">
-        <f>MIN(0,E169-MAX($E$13:E169))</f>
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="4">
+        <f>IF(OR(Trades!M169="WIN",Trades!M169="LOSS"),B168+Trades!N169,B168)</f>
+        <v/>
+      </c>
+      <c r="C169" s="20">
+        <f>MIN(0,B169-MAX($B$2:B169))</f>
         <v/>
       </c>
     </row>
     <row r="170">
-      <c r="E170" s="4">
-        <f>IF(OR(Trades!M159="WIN",Trades!M159="LOSS"),E169+Trades!N159,E169)</f>
-        <v/>
-      </c>
-      <c r="F170" s="15">
-        <f>MIN(0,E170-MAX($E$13:E170))</f>
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="4">
+        <f>IF(OR(Trades!M170="WIN",Trades!M170="LOSS"),B169+Trades!N170,B169)</f>
+        <v/>
+      </c>
+      <c r="C170" s="20">
+        <f>MIN(0,B170-MAX($B$2:B170))</f>
         <v/>
       </c>
     </row>
     <row r="171">
-      <c r="E171" s="4">
-        <f>IF(OR(Trades!M160="WIN",Trades!M160="LOSS"),E170+Trades!N160,E170)</f>
-        <v/>
-      </c>
-      <c r="F171" s="15">
-        <f>MIN(0,E171-MAX($E$13:E171))</f>
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="4">
+        <f>IF(OR(Trades!M171="WIN",Trades!M171="LOSS"),B170+Trades!N171,B170)</f>
+        <v/>
+      </c>
+      <c r="C171" s="20">
+        <f>MIN(0,B171-MAX($B$2:B171))</f>
         <v/>
       </c>
     </row>
     <row r="172">
-      <c r="E172" s="4">
-        <f>IF(OR(Trades!M161="WIN",Trades!M161="LOSS"),E171+Trades!N161,E171)</f>
-        <v/>
-      </c>
-      <c r="F172" s="15">
-        <f>MIN(0,E172-MAX($E$13:E172))</f>
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="4">
+        <f>IF(OR(Trades!M172="WIN",Trades!M172="LOSS"),B171+Trades!N172,B171)</f>
+        <v/>
+      </c>
+      <c r="C172" s="20">
+        <f>MIN(0,B172-MAX($B$2:B172))</f>
         <v/>
       </c>
     </row>
     <row r="173">
-      <c r="E173" s="4">
-        <f>IF(OR(Trades!M162="WIN",Trades!M162="LOSS"),E172+Trades!N162,E172)</f>
-        <v/>
-      </c>
-      <c r="F173" s="15">
-        <f>MIN(0,E173-MAX($E$13:E173))</f>
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="4">
+        <f>IF(OR(Trades!M173="WIN",Trades!M173="LOSS"),B172+Trades!N173,B172)</f>
+        <v/>
+      </c>
+      <c r="C173" s="20">
+        <f>MIN(0,B173-MAX($B$2:B173))</f>
         <v/>
       </c>
     </row>
     <row r="174">
-      <c r="E174" s="4">
-        <f>IF(OR(Trades!M163="WIN",Trades!M163="LOSS"),E173+Trades!N163,E173)</f>
-        <v/>
-      </c>
-      <c r="F174" s="15">
-        <f>MIN(0,E174-MAX($E$13:E174))</f>
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="4">
+        <f>IF(OR(Trades!M174="WIN",Trades!M174="LOSS"),B173+Trades!N174,B173)</f>
+        <v/>
+      </c>
+      <c r="C174" s="20">
+        <f>MIN(0,B174-MAX($B$2:B174))</f>
         <v/>
       </c>
     </row>
     <row r="175">
-      <c r="E175" s="4">
-        <f>IF(OR(Trades!M164="WIN",Trades!M164="LOSS"),E174+Trades!N164,E174)</f>
-        <v/>
-      </c>
-      <c r="F175" s="15">
-        <f>MIN(0,E175-MAX($E$13:E175))</f>
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="4">
+        <f>IF(OR(Trades!M175="WIN",Trades!M175="LOSS"),B174+Trades!N175,B174)</f>
+        <v/>
+      </c>
+      <c r="C175" s="20">
+        <f>MIN(0,B175-MAX($B$2:B175))</f>
         <v/>
       </c>
     </row>
     <row r="176">
-      <c r="E176" s="4">
-        <f>IF(OR(Trades!M165="WIN",Trades!M165="LOSS"),E175+Trades!N165,E175)</f>
-        <v/>
-      </c>
-      <c r="F176" s="15">
-        <f>MIN(0,E176-MAX($E$13:E176))</f>
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="4">
+        <f>IF(OR(Trades!M176="WIN",Trades!M176="LOSS"),B175+Trades!N176,B175)</f>
+        <v/>
+      </c>
+      <c r="C176" s="20">
+        <f>MIN(0,B176-MAX($B$2:B176))</f>
         <v/>
       </c>
     </row>
     <row r="177">
-      <c r="E177" s="4">
-        <f>IF(OR(Trades!M166="WIN",Trades!M166="LOSS"),E176+Trades!N166,E176)</f>
-        <v/>
-      </c>
-      <c r="F177" s="15">
-        <f>MIN(0,E177-MAX($E$13:E177))</f>
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="4">
+        <f>IF(OR(Trades!M177="WIN",Trades!M177="LOSS"),B176+Trades!N177,B176)</f>
+        <v/>
+      </c>
+      <c r="C177" s="20">
+        <f>MIN(0,B177-MAX($B$2:B177))</f>
         <v/>
       </c>
     </row>
     <row r="178">
-      <c r="E178" s="4">
-        <f>IF(OR(Trades!M167="WIN",Trades!M167="LOSS"),E177+Trades!N167,E177)</f>
-        <v/>
-      </c>
-      <c r="F178" s="15">
-        <f>MIN(0,E178-MAX($E$13:E178))</f>
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="4">
+        <f>IF(OR(Trades!M178="WIN",Trades!M178="LOSS"),B177+Trades!N178,B177)</f>
+        <v/>
+      </c>
+      <c r="C178" s="20">
+        <f>MIN(0,B178-MAX($B$2:B178))</f>
         <v/>
       </c>
     </row>
     <row r="179">
-      <c r="E179" s="4">
-        <f>IF(OR(Trades!M168="WIN",Trades!M168="LOSS"),E178+Trades!N168,E178)</f>
-        <v/>
-      </c>
-      <c r="F179" s="15">
-        <f>MIN(0,E179-MAX($E$13:E179))</f>
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="4">
+        <f>IF(OR(Trades!M179="WIN",Trades!M179="LOSS"),B178+Trades!N179,B178)</f>
+        <v/>
+      </c>
+      <c r="C179" s="20">
+        <f>MIN(0,B179-MAX($B$2:B179))</f>
         <v/>
       </c>
     </row>
     <row r="180">
-      <c r="E180" s="4">
-        <f>IF(OR(Trades!M169="WIN",Trades!M169="LOSS"),E179+Trades!N169,E179)</f>
-        <v/>
-      </c>
-      <c r="F180" s="15">
-        <f>MIN(0,E180-MAX($E$13:E180))</f>
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="4">
+        <f>IF(OR(Trades!M180="WIN",Trades!M180="LOSS"),B179+Trades!N180,B179)</f>
+        <v/>
+      </c>
+      <c r="C180" s="20">
+        <f>MIN(0,B180-MAX($B$2:B180))</f>
         <v/>
       </c>
     </row>
     <row r="181">
-      <c r="E181" s="4">
-        <f>IF(OR(Trades!M170="WIN",Trades!M170="LOSS"),E180+Trades!N170,E180)</f>
-        <v/>
-      </c>
-      <c r="F181" s="15">
-        <f>MIN(0,E181-MAX($E$13:E181))</f>
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="4">
+        <f>IF(OR(Trades!M181="WIN",Trades!M181="LOSS"),B180+Trades!N181,B180)</f>
+        <v/>
+      </c>
+      <c r="C181" s="20">
+        <f>MIN(0,B181-MAX($B$2:B181))</f>
         <v/>
       </c>
     </row>
     <row r="182">
-      <c r="E182" s="4">
-        <f>IF(OR(Trades!M171="WIN",Trades!M171="LOSS"),E181+Trades!N171,E181)</f>
-        <v/>
-      </c>
-      <c r="F182" s="15">
-        <f>MIN(0,E182-MAX($E$13:E182))</f>
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="4">
+        <f>IF(OR(Trades!M182="WIN",Trades!M182="LOSS"),B181+Trades!N182,B181)</f>
+        <v/>
+      </c>
+      <c r="C182" s="20">
+        <f>MIN(0,B182-MAX($B$2:B182))</f>
         <v/>
       </c>
     </row>
     <row r="183">
-      <c r="E183" s="4">
-        <f>IF(OR(Trades!M172="WIN",Trades!M172="LOSS"),E182+Trades!N172,E182)</f>
-        <v/>
-      </c>
-      <c r="F183" s="15">
-        <f>MIN(0,E183-MAX($E$13:E183))</f>
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="4">
+        <f>IF(OR(Trades!M183="WIN",Trades!M183="LOSS"),B182+Trades!N183,B182)</f>
+        <v/>
+      </c>
+      <c r="C183" s="20">
+        <f>MIN(0,B183-MAX($B$2:B183))</f>
         <v/>
       </c>
     </row>
     <row r="184">
-      <c r="E184" s="4">
-        <f>IF(OR(Trades!M173="WIN",Trades!M173="LOSS"),E183+Trades!N173,E183)</f>
-        <v/>
-      </c>
-      <c r="F184" s="15">
-        <f>MIN(0,E184-MAX($E$13:E184))</f>
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="4">
+        <f>IF(OR(Trades!M184="WIN",Trades!M184="LOSS"),B183+Trades!N184,B183)</f>
+        <v/>
+      </c>
+      <c r="C184" s="20">
+        <f>MIN(0,B184-MAX($B$2:B184))</f>
         <v/>
       </c>
     </row>
     <row r="185">
-      <c r="E185" s="4">
-        <f>IF(OR(Trades!M174="WIN",Trades!M174="LOSS"),E184+Trades!N174,E184)</f>
-        <v/>
-      </c>
-      <c r="F185" s="15">
-        <f>MIN(0,E185-MAX($E$13:E185))</f>
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="4">
+        <f>IF(OR(Trades!M185="WIN",Trades!M185="LOSS"),B184+Trades!N185,B184)</f>
+        <v/>
+      </c>
+      <c r="C185" s="20">
+        <f>MIN(0,B185-MAX($B$2:B185))</f>
         <v/>
       </c>
     </row>
     <row r="186">
-      <c r="E186" s="4">
-        <f>IF(OR(Trades!M175="WIN",Trades!M175="LOSS"),E185+Trades!N175,E185)</f>
-        <v/>
-      </c>
-      <c r="F186" s="15">
-        <f>MIN(0,E186-MAX($E$13:E186))</f>
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="4">
+        <f>IF(OR(Trades!M186="WIN",Trades!M186="LOSS"),B185+Trades!N186,B185)</f>
+        <v/>
+      </c>
+      <c r="C186" s="20">
+        <f>MIN(0,B186-MAX($B$2:B186))</f>
         <v/>
       </c>
     </row>
     <row r="187">
-      <c r="E187" s="4">
-        <f>IF(OR(Trades!M176="WIN",Trades!M176="LOSS"),E186+Trades!N176,E186)</f>
-        <v/>
-      </c>
-      <c r="F187" s="15">
-        <f>MIN(0,E187-MAX($E$13:E187))</f>
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="4">
+        <f>IF(OR(Trades!M187="WIN",Trades!M187="LOSS"),B186+Trades!N187,B186)</f>
+        <v/>
+      </c>
+      <c r="C187" s="20">
+        <f>MIN(0,B187-MAX($B$2:B187))</f>
         <v/>
       </c>
     </row>
     <row r="188">
-      <c r="E188" s="4">
-        <f>IF(OR(Trades!M177="WIN",Trades!M177="LOSS"),E187+Trades!N177,E187)</f>
-        <v/>
-      </c>
-      <c r="F188" s="15">
-        <f>MIN(0,E188-MAX($E$13:E188))</f>
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="4">
+        <f>IF(OR(Trades!M188="WIN",Trades!M188="LOSS"),B187+Trades!N188,B187)</f>
+        <v/>
+      </c>
+      <c r="C188" s="20">
+        <f>MIN(0,B188-MAX($B$2:B188))</f>
         <v/>
       </c>
     </row>
     <row r="189">
-      <c r="E189" s="4">
-        <f>IF(OR(Trades!M178="WIN",Trades!M178="LOSS"),E188+Trades!N178,E188)</f>
-        <v/>
-      </c>
-      <c r="F189" s="15">
-        <f>MIN(0,E189-MAX($E$13:E189))</f>
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="4">
+        <f>IF(OR(Trades!M189="WIN",Trades!M189="LOSS"),B188+Trades!N189,B188)</f>
+        <v/>
+      </c>
+      <c r="C189" s="20">
+        <f>MIN(0,B189-MAX($B$2:B189))</f>
         <v/>
       </c>
     </row>
     <row r="190">
-      <c r="E190" s="4">
-        <f>IF(OR(Trades!M179="WIN",Trades!M179="LOSS"),E189+Trades!N179,E189)</f>
-        <v/>
-      </c>
-      <c r="F190" s="15">
-        <f>MIN(0,E190-MAX($E$13:E190))</f>
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="4">
+        <f>IF(OR(Trades!M190="WIN",Trades!M190="LOSS"),B189+Trades!N190,B189)</f>
+        <v/>
+      </c>
+      <c r="C190" s="20">
+        <f>MIN(0,B190-MAX($B$2:B190))</f>
         <v/>
       </c>
     </row>
     <row r="191">
-      <c r="E191" s="4">
-        <f>IF(OR(Trades!M180="WIN",Trades!M180="LOSS"),E190+Trades!N180,E190)</f>
-        <v/>
-      </c>
-      <c r="F191" s="15">
-        <f>MIN(0,E191-MAX($E$13:E191))</f>
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="4">
+        <f>IF(OR(Trades!M191="WIN",Trades!M191="LOSS"),B190+Trades!N191,B190)</f>
+        <v/>
+      </c>
+      <c r="C191" s="20">
+        <f>MIN(0,B191-MAX($B$2:B191))</f>
         <v/>
       </c>
     </row>
     <row r="192">
-      <c r="E192" s="4">
-        <f>IF(OR(Trades!M181="WIN",Trades!M181="LOSS"),E191+Trades!N181,E191)</f>
-        <v/>
-      </c>
-      <c r="F192" s="15">
-        <f>MIN(0,E192-MAX($E$13:E192))</f>
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="4">
+        <f>IF(OR(Trades!M192="WIN",Trades!M192="LOSS"),B191+Trades!N192,B191)</f>
+        <v/>
+      </c>
+      <c r="C192" s="20">
+        <f>MIN(0,B192-MAX($B$2:B192))</f>
         <v/>
       </c>
     </row>
     <row r="193">
-      <c r="E193" s="4">
-        <f>IF(OR(Trades!M182="WIN",Trades!M182="LOSS"),E192+Trades!N182,E192)</f>
-        <v/>
-      </c>
-      <c r="F193" s="15">
-        <f>MIN(0,E193-MAX($E$13:E193))</f>
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="4">
+        <f>IF(OR(Trades!M193="WIN",Trades!M193="LOSS"),B192+Trades!N193,B192)</f>
+        <v/>
+      </c>
+      <c r="C193" s="20">
+        <f>MIN(0,B193-MAX($B$2:B193))</f>
         <v/>
       </c>
     </row>
     <row r="194">
-      <c r="E194" s="4">
-        <f>IF(OR(Trades!M183="WIN",Trades!M183="LOSS"),E193+Trades!N183,E193)</f>
-        <v/>
-      </c>
-      <c r="F194" s="15">
-        <f>MIN(0,E194-MAX($E$13:E194))</f>
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="4">
+        <f>IF(OR(Trades!M194="WIN",Trades!M194="LOSS"),B193+Trades!N194,B193)</f>
+        <v/>
+      </c>
+      <c r="C194" s="20">
+        <f>MIN(0,B194-MAX($B$2:B194))</f>
         <v/>
       </c>
     </row>
     <row r="195">
-      <c r="E195" s="4">
-        <f>IF(OR(Trades!M184="WIN",Trades!M184="LOSS"),E194+Trades!N184,E194)</f>
-        <v/>
-      </c>
-      <c r="F195" s="15">
-        <f>MIN(0,E195-MAX($E$13:E195))</f>
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="4">
+        <f>IF(OR(Trades!M195="WIN",Trades!M195="LOSS"),B194+Trades!N195,B194)</f>
+        <v/>
+      </c>
+      <c r="C195" s="20">
+        <f>MIN(0,B195-MAX($B$2:B195))</f>
         <v/>
       </c>
     </row>
     <row r="196">
-      <c r="E196" s="4">
-        <f>IF(OR(Trades!M185="WIN",Trades!M185="LOSS"),E195+Trades!N185,E195)</f>
-        <v/>
-      </c>
-      <c r="F196" s="15">
-        <f>MIN(0,E196-MAX($E$13:E196))</f>
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="4">
+        <f>IF(OR(Trades!M196="WIN",Trades!M196="LOSS"),B195+Trades!N196,B195)</f>
+        <v/>
+      </c>
+      <c r="C196" s="20">
+        <f>MIN(0,B196-MAX($B$2:B196))</f>
         <v/>
       </c>
     </row>
     <row r="197">
-      <c r="E197" s="4">
-        <f>IF(OR(Trades!M186="WIN",Trades!M186="LOSS"),E196+Trades!N186,E196)</f>
-        <v/>
-      </c>
-      <c r="F197" s="15">
-        <f>MIN(0,E197-MAX($E$13:E197))</f>
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="4">
+        <f>IF(OR(Trades!M197="WIN",Trades!M197="LOSS"),B196+Trades!N197,B196)</f>
+        <v/>
+      </c>
+      <c r="C197" s="20">
+        <f>MIN(0,B197-MAX($B$2:B197))</f>
         <v/>
       </c>
     </row>
     <row r="198">
-      <c r="E198" s="4">
-        <f>IF(OR(Trades!M187="WIN",Trades!M187="LOSS"),E197+Trades!N187,E197)</f>
-        <v/>
-      </c>
-      <c r="F198" s="15">
-        <f>MIN(0,E198-MAX($E$13:E198))</f>
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="4">
+        <f>IF(OR(Trades!M198="WIN",Trades!M198="LOSS"),B197+Trades!N198,B197)</f>
+        <v/>
+      </c>
+      <c r="C198" s="20">
+        <f>MIN(0,B198-MAX($B$2:B198))</f>
         <v/>
       </c>
     </row>
     <row r="199">
-      <c r="E199" s="4">
-        <f>IF(OR(Trades!M188="WIN",Trades!M188="LOSS"),E198+Trades!N188,E198)</f>
-        <v/>
-      </c>
-      <c r="F199" s="15">
-        <f>MIN(0,E199-MAX($E$13:E199))</f>
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="4">
+        <f>IF(OR(Trades!M199="WIN",Trades!M199="LOSS"),B198+Trades!N199,B198)</f>
+        <v/>
+      </c>
+      <c r="C199" s="20">
+        <f>MIN(0,B199-MAX($B$2:B199))</f>
         <v/>
       </c>
     </row>
     <row r="200">
-      <c r="E200" s="4">
-        <f>IF(OR(Trades!M189="WIN",Trades!M189="LOSS"),E199+Trades!N189,E199)</f>
-        <v/>
-      </c>
-      <c r="F200" s="15">
-        <f>MIN(0,E200-MAX($E$13:E200))</f>
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="4">
+        <f>IF(OR(Trades!M200="WIN",Trades!M200="LOSS"),B199+Trades!N200,B199)</f>
+        <v/>
+      </c>
+      <c r="C200" s="20">
+        <f>MIN(0,B200-MAX($B$2:B200))</f>
         <v/>
       </c>
     </row>
     <row r="201">
-      <c r="E201" s="4">
-        <f>IF(OR(Trades!M190="WIN",Trades!M190="LOSS"),E200+Trades!N190,E200)</f>
-        <v/>
-      </c>
-      <c r="F201" s="15">
-        <f>MIN(0,E201-MAX($E$13:E201))</f>
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="4">
+        <f>IF(OR(Trades!M201="WIN",Trades!M201="LOSS"),B200+Trades!N201,B200)</f>
+        <v/>
+      </c>
+      <c r="C201" s="20">
+        <f>MIN(0,B201-MAX($B$2:B201))</f>
         <v/>
       </c>
     </row>
     <row r="202">
-      <c r="E202" s="4">
-        <f>IF(OR(Trades!M191="WIN",Trades!M191="LOSS"),E201+Trades!N191,E201)</f>
-        <v/>
-      </c>
-      <c r="F202" s="15">
-        <f>MIN(0,E202-MAX($E$13:E202))</f>
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="4">
+        <f>IF(OR(Trades!M202="WIN",Trades!M202="LOSS"),B201+Trades!N202,B201)</f>
+        <v/>
+      </c>
+      <c r="C202" s="20">
+        <f>MIN(0,B202-MAX($B$2:B202))</f>
         <v/>
       </c>
     </row>
     <row r="203">
-      <c r="E203" s="4">
-        <f>IF(OR(Trades!M192="WIN",Trades!M192="LOSS"),E202+Trades!N192,E202)</f>
-        <v/>
-      </c>
-      <c r="F203" s="15">
-        <f>MIN(0,E203-MAX($E$13:E203))</f>
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="4">
+        <f>IF(OR(Trades!M203="WIN",Trades!M203="LOSS"),B202+Trades!N203,B202)</f>
+        <v/>
+      </c>
+      <c r="C203" s="20">
+        <f>MIN(0,B203-MAX($B$2:B203))</f>
         <v/>
       </c>
     </row>
     <row r="204">
-      <c r="E204" s="4">
-        <f>IF(OR(Trades!M193="WIN",Trades!M193="LOSS"),E203+Trades!N193,E203)</f>
-        <v/>
-      </c>
-      <c r="F204" s="15">
-        <f>MIN(0,E204-MAX($E$13:E204))</f>
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="4">
+        <f>IF(OR(Trades!M204="WIN",Trades!M204="LOSS"),B203+Trades!N204,B203)</f>
+        <v/>
+      </c>
+      <c r="C204" s="20">
+        <f>MIN(0,B204-MAX($B$2:B204))</f>
         <v/>
       </c>
     </row>
     <row r="205">
-      <c r="E205" s="4">
-        <f>IF(OR(Trades!M194="WIN",Trades!M194="LOSS"),E204+Trades!N194,E204)</f>
-        <v/>
-      </c>
-      <c r="F205" s="15">
-        <f>MIN(0,E205-MAX($E$13:E205))</f>
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="4">
+        <f>IF(OR(Trades!M205="WIN",Trades!M205="LOSS"),B204+Trades!N205,B204)</f>
+        <v/>
+      </c>
+      <c r="C205" s="20">
+        <f>MIN(0,B205-MAX($B$2:B205))</f>
         <v/>
       </c>
     </row>
     <row r="206">
-      <c r="E206" s="4">
-        <f>IF(OR(Trades!M195="WIN",Trades!M195="LOSS"),E205+Trades!N195,E205)</f>
-        <v/>
-      </c>
-      <c r="F206" s="15">
-        <f>MIN(0,E206-MAX($E$13:E206))</f>
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="4">
+        <f>IF(OR(Trades!M206="WIN",Trades!M206="LOSS"),B205+Trades!N206,B205)</f>
+        <v/>
+      </c>
+      <c r="C206" s="20">
+        <f>MIN(0,B206-MAX($B$2:B206))</f>
         <v/>
       </c>
     </row>
     <row r="207">
-      <c r="E207" s="4">
-        <f>IF(OR(Trades!M196="WIN",Trades!M196="LOSS"),E206+Trades!N196,E206)</f>
-        <v/>
-      </c>
-      <c r="F207" s="15">
-        <f>MIN(0,E207-MAX($E$13:E207))</f>
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="4">
+        <f>IF(OR(Trades!M207="WIN",Trades!M207="LOSS"),B206+Trades!N207,B206)</f>
+        <v/>
+      </c>
+      <c r="C207" s="20">
+        <f>MIN(0,B207-MAX($B$2:B207))</f>
         <v/>
       </c>
     </row>
     <row r="208">
-      <c r="E208" s="4">
-        <f>IF(OR(Trades!M197="WIN",Trades!M197="LOSS"),E207+Trades!N197,E207)</f>
-        <v/>
-      </c>
-      <c r="F208" s="15">
-        <f>MIN(0,E208-MAX($E$13:E208))</f>
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="4">
+        <f>IF(OR(Trades!M208="WIN",Trades!M208="LOSS"),B207+Trades!N208,B207)</f>
+        <v/>
+      </c>
+      <c r="C208" s="20">
+        <f>MIN(0,B208-MAX($B$2:B208))</f>
         <v/>
       </c>
     </row>
     <row r="209">
-      <c r="E209" s="4">
-        <f>IF(OR(Trades!M198="WIN",Trades!M198="LOSS"),E208+Trades!N198,E208)</f>
-        <v/>
-      </c>
-      <c r="F209" s="15">
-        <f>MIN(0,E209-MAX($E$13:E209))</f>
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="4">
+        <f>IF(OR(Trades!M209="WIN",Trades!M209="LOSS"),B208+Trades!N209,B208)</f>
+        <v/>
+      </c>
+      <c r="C209" s="20">
+        <f>MIN(0,B209-MAX($B$2:B209))</f>
         <v/>
       </c>
     </row>
     <row r="210">
-      <c r="E210" s="4">
-        <f>IF(OR(Trades!M199="WIN",Trades!M199="LOSS"),E209+Trades!N199,E209)</f>
-        <v/>
-      </c>
-      <c r="F210" s="15">
-        <f>MIN(0,E210-MAX($E$13:E210))</f>
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="4">
+        <f>IF(OR(Trades!M210="WIN",Trades!M210="LOSS"),B209+Trades!N210,B209)</f>
+        <v/>
+      </c>
+      <c r="C210" s="20">
+        <f>MIN(0,B210-MAX($B$2:B210))</f>
         <v/>
       </c>
     </row>
     <row r="211">
-      <c r="E211" s="4">
-        <f>IF(OR(Trades!M200="WIN",Trades!M200="LOSS"),E210+Trades!N200,E210)</f>
-        <v/>
-      </c>
-      <c r="F211" s="15">
-        <f>MIN(0,E211-MAX($E$13:E211))</f>
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="4">
+        <f>IF(OR(Trades!M211="WIN",Trades!M211="LOSS"),B210+Trades!N211,B210)</f>
+        <v/>
+      </c>
+      <c r="C211" s="20">
+        <f>MIN(0,B211-MAX($B$2:B211))</f>
         <v/>
       </c>
     </row>
     <row r="212">
-      <c r="E212" s="4">
-        <f>IF(OR(Trades!M201="WIN",Trades!M201="LOSS"),E211+Trades!N201,E211)</f>
-        <v/>
-      </c>
-      <c r="F212" s="15">
-        <f>MIN(0,E212-MAX($E$13:E212))</f>
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="4">
+        <f>IF(OR(Trades!M212="WIN",Trades!M212="LOSS"),B211+Trades!N212,B211)</f>
+        <v/>
+      </c>
+      <c r="C212" s="20">
+        <f>MIN(0,B212-MAX($B$2:B212))</f>
         <v/>
       </c>
     </row>
     <row r="213">
-      <c r="E213" s="4">
-        <f>IF(OR(Trades!M202="WIN",Trades!M202="LOSS"),E212+Trades!N202,E212)</f>
-        <v/>
-      </c>
-      <c r="F213" s="15">
-        <f>MIN(0,E213-MAX($E$13:E213))</f>
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="4">
+        <f>IF(OR(Trades!M213="WIN",Trades!M213="LOSS"),B212+Trades!N213,B212)</f>
+        <v/>
+      </c>
+      <c r="C213" s="20">
+        <f>MIN(0,B213-MAX($B$2:B213))</f>
         <v/>
       </c>
     </row>
     <row r="214">
-      <c r="E214" s="4">
-        <f>IF(OR(Trades!M203="WIN",Trades!M203="LOSS"),E213+Trades!N203,E213)</f>
-        <v/>
-      </c>
-      <c r="F214" s="15">
-        <f>MIN(0,E214-MAX($E$13:E214))</f>
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="4">
+        <f>IF(OR(Trades!M214="WIN",Trades!M214="LOSS"),B213+Trades!N214,B213)</f>
+        <v/>
+      </c>
+      <c r="C214" s="20">
+        <f>MIN(0,B214-MAX($B$2:B214))</f>
         <v/>
       </c>
     </row>
     <row r="215">
-      <c r="E215" s="4">
-        <f>IF(OR(Trades!M204="WIN",Trades!M204="LOSS"),E214+Trades!N204,E214)</f>
-        <v/>
-      </c>
-      <c r="F215" s="15">
-        <f>MIN(0,E215-MAX($E$13:E215))</f>
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="4">
+        <f>IF(OR(Trades!M215="WIN",Trades!M215="LOSS"),B214+Trades!N215,B214)</f>
+        <v/>
+      </c>
+      <c r="C215" s="20">
+        <f>MIN(0,B215-MAX($B$2:B215))</f>
         <v/>
       </c>
     </row>
     <row r="216">
-      <c r="E216" s="4">
-        <f>IF(OR(Trades!M205="WIN",Trades!M205="LOSS"),E215+Trades!N205,E215)</f>
-        <v/>
-      </c>
-      <c r="F216" s="15">
-        <f>MIN(0,E216-MAX($E$13:E216))</f>
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="4">
+        <f>IF(OR(Trades!M216="WIN",Trades!M216="LOSS"),B215+Trades!N216,B215)</f>
+        <v/>
+      </c>
+      <c r="C216" s="20">
+        <f>MIN(0,B216-MAX($B$2:B216))</f>
         <v/>
       </c>
     </row>
     <row r="217">
-      <c r="E217" s="4">
-        <f>IF(OR(Trades!M206="WIN",Trades!M206="LOSS"),E216+Trades!N206,E216)</f>
-        <v/>
-      </c>
-      <c r="F217" s="15">
-        <f>MIN(0,E217-MAX($E$13:E217))</f>
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="4">
+        <f>IF(OR(Trades!M217="WIN",Trades!M217="LOSS"),B216+Trades!N217,B216)</f>
+        <v/>
+      </c>
+      <c r="C217" s="20">
+        <f>MIN(0,B217-MAX($B$2:B217))</f>
         <v/>
       </c>
     </row>
     <row r="218">
-      <c r="E218" s="4">
-        <f>IF(OR(Trades!M207="WIN",Trades!M207="LOSS"),E217+Trades!N207,E217)</f>
-        <v/>
-      </c>
-      <c r="F218" s="15">
-        <f>MIN(0,E218-MAX($E$13:E218))</f>
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="4">
+        <f>IF(OR(Trades!M218="WIN",Trades!M218="LOSS"),B217+Trades!N218,B217)</f>
+        <v/>
+      </c>
+      <c r="C218" s="20">
+        <f>MIN(0,B218-MAX($B$2:B218))</f>
         <v/>
       </c>
     </row>
     <row r="219">
-      <c r="E219" s="4">
-        <f>IF(OR(Trades!M208="WIN",Trades!M208="LOSS"),E218+Trades!N208,E218)</f>
-        <v/>
-      </c>
-      <c r="F219" s="15">
-        <f>MIN(0,E219-MAX($E$13:E219))</f>
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="4">
+        <f>IF(OR(Trades!M219="WIN",Trades!M219="LOSS"),B218+Trades!N219,B218)</f>
+        <v/>
+      </c>
+      <c r="C219" s="20">
+        <f>MIN(0,B219-MAX($B$2:B219))</f>
         <v/>
       </c>
     </row>
     <row r="220">
-      <c r="E220" s="4">
-        <f>IF(OR(Trades!M209="WIN",Trades!M209="LOSS"),E219+Trades!N209,E219)</f>
-        <v/>
-      </c>
-      <c r="F220" s="15">
-        <f>MIN(0,E220-MAX($E$13:E220))</f>
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="4">
+        <f>IF(OR(Trades!M220="WIN",Trades!M220="LOSS"),B219+Trades!N220,B219)</f>
+        <v/>
+      </c>
+      <c r="C220" s="20">
+        <f>MIN(0,B220-MAX($B$2:B220))</f>
         <v/>
       </c>
     </row>
     <row r="221">
-      <c r="E221" s="4">
-        <f>IF(OR(Trades!M210="WIN",Trades!M210="LOSS"),E220+Trades!N210,E220)</f>
-        <v/>
-      </c>
-      <c r="F221" s="15">
-        <f>MIN(0,E221-MAX($E$13:E221))</f>
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="4">
+        <f>IF(OR(Trades!M221="WIN",Trades!M221="LOSS"),B220+Trades!N221,B220)</f>
+        <v/>
+      </c>
+      <c r="C221" s="20">
+        <f>MIN(0,B221-MAX($B$2:B221))</f>
         <v/>
       </c>
     </row>
     <row r="222">
-      <c r="E222" s="4">
-        <f>IF(OR(Trades!M211="WIN",Trades!M211="LOSS"),E221+Trades!N211,E221)</f>
-        <v/>
-      </c>
-      <c r="F222" s="15">
-        <f>MIN(0,E222-MAX($E$13:E222))</f>
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="4">
+        <f>IF(OR(Trades!M222="WIN",Trades!M222="LOSS"),B221+Trades!N222,B221)</f>
+        <v/>
+      </c>
+      <c r="C222" s="20">
+        <f>MIN(0,B222-MAX($B$2:B222))</f>
         <v/>
       </c>
     </row>
     <row r="223">
-      <c r="E223" s="4">
-        <f>IF(OR(Trades!M212="WIN",Trades!M212="LOSS"),E222+Trades!N212,E222)</f>
-        <v/>
-      </c>
-      <c r="F223" s="15">
-        <f>MIN(0,E223-MAX($E$13:E223))</f>
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="4">
+        <f>IF(OR(Trades!M223="WIN",Trades!M223="LOSS"),B222+Trades!N223,B222)</f>
+        <v/>
+      </c>
+      <c r="C223" s="20">
+        <f>MIN(0,B223-MAX($B$2:B223))</f>
         <v/>
       </c>
     </row>
     <row r="224">
-      <c r="E224" s="4">
-        <f>IF(OR(Trades!M213="WIN",Trades!M213="LOSS"),E223+Trades!N213,E223)</f>
-        <v/>
-      </c>
-      <c r="F224" s="15">
-        <f>MIN(0,E224-MAX($E$13:E224))</f>
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="4">
+        <f>IF(OR(Trades!M224="WIN",Trades!M224="LOSS"),B223+Trades!N224,B223)</f>
+        <v/>
+      </c>
+      <c r="C224" s="20">
+        <f>MIN(0,B224-MAX($B$2:B224))</f>
         <v/>
       </c>
     </row>
     <row r="225">
-      <c r="E225" s="4">
-        <f>IF(OR(Trades!M214="WIN",Trades!M214="LOSS"),E224+Trades!N214,E224)</f>
-        <v/>
-      </c>
-      <c r="F225" s="15">
-        <f>MIN(0,E225-MAX($E$13:E225))</f>
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="4">
+        <f>IF(OR(Trades!M225="WIN",Trades!M225="LOSS"),B224+Trades!N225,B224)</f>
+        <v/>
+      </c>
+      <c r="C225" s="20">
+        <f>MIN(0,B225-MAX($B$2:B225))</f>
         <v/>
       </c>
     </row>
     <row r="226">
-      <c r="E226" s="4">
-        <f>IF(OR(Trades!M215="WIN",Trades!M215="LOSS"),E225+Trades!N215,E225)</f>
-        <v/>
-      </c>
-      <c r="F226" s="15">
-        <f>MIN(0,E226-MAX($E$13:E226))</f>
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="4">
+        <f>IF(OR(Trades!M226="WIN",Trades!M226="LOSS"),B225+Trades!N226,B225)</f>
+        <v/>
+      </c>
+      <c r="C226" s="20">
+        <f>MIN(0,B226-MAX($B$2:B226))</f>
         <v/>
       </c>
     </row>
     <row r="227">
-      <c r="E227" s="4">
-        <f>IF(OR(Trades!M216="WIN",Trades!M216="LOSS"),E226+Trades!N216,E226)</f>
-        <v/>
-      </c>
-      <c r="F227" s="15">
-        <f>MIN(0,E227-MAX($E$13:E227))</f>
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="4">
+        <f>IF(OR(Trades!M227="WIN",Trades!M227="LOSS"),B226+Trades!N227,B226)</f>
+        <v/>
+      </c>
+      <c r="C227" s="20">
+        <f>MIN(0,B227-MAX($B$2:B227))</f>
         <v/>
       </c>
     </row>
     <row r="228">
-      <c r="E228" s="4">
-        <f>IF(OR(Trades!M217="WIN",Trades!M217="LOSS"),E227+Trades!N217,E227)</f>
-        <v/>
-      </c>
-      <c r="F228" s="15">
-        <f>MIN(0,E228-MAX($E$13:E228))</f>
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="4">
+        <f>IF(OR(Trades!M228="WIN",Trades!M228="LOSS"),B227+Trades!N228,B227)</f>
+        <v/>
+      </c>
+      <c r="C228" s="20">
+        <f>MIN(0,B228-MAX($B$2:B228))</f>
         <v/>
       </c>
     </row>
     <row r="229">
-      <c r="E229" s="4">
-        <f>IF(OR(Trades!M218="WIN",Trades!M218="LOSS"),E228+Trades!N218,E228)</f>
-        <v/>
-      </c>
-      <c r="F229" s="15">
-        <f>MIN(0,E229-MAX($E$13:E229))</f>
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="4">
+        <f>IF(OR(Trades!M229="WIN",Trades!M229="LOSS"),B228+Trades!N229,B228)</f>
+        <v/>
+      </c>
+      <c r="C229" s="20">
+        <f>MIN(0,B229-MAX($B$2:B229))</f>
         <v/>
       </c>
     </row>
     <row r="230">
-      <c r="E230" s="4">
-        <f>IF(OR(Trades!M219="WIN",Trades!M219="LOSS"),E229+Trades!N219,E229)</f>
-        <v/>
-      </c>
-      <c r="F230" s="15">
-        <f>MIN(0,E230-MAX($E$13:E230))</f>
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="4">
+        <f>IF(OR(Trades!M230="WIN",Trades!M230="LOSS"),B229+Trades!N230,B229)</f>
+        <v/>
+      </c>
+      <c r="C230" s="20">
+        <f>MIN(0,B230-MAX($B$2:B230))</f>
         <v/>
       </c>
     </row>
     <row r="231">
-      <c r="E231" s="4">
-        <f>IF(OR(Trades!M220="WIN",Trades!M220="LOSS"),E230+Trades!N220,E230)</f>
-        <v/>
-      </c>
-      <c r="F231" s="15">
-        <f>MIN(0,E231-MAX($E$13:E231))</f>
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="4">
+        <f>IF(OR(Trades!M231="WIN",Trades!M231="LOSS"),B230+Trades!N231,B230)</f>
+        <v/>
+      </c>
+      <c r="C231" s="20">
+        <f>MIN(0,B231-MAX($B$2:B231))</f>
         <v/>
       </c>
     </row>
     <row r="232">
-      <c r="E232" s="4">
-        <f>IF(OR(Trades!M221="WIN",Trades!M221="LOSS"),E231+Trades!N221,E231)</f>
-        <v/>
-      </c>
-      <c r="F232" s="15">
-        <f>MIN(0,E232-MAX($E$13:E232))</f>
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="4">
+        <f>IF(OR(Trades!M232="WIN",Trades!M232="LOSS"),B231+Trades!N232,B231)</f>
+        <v/>
+      </c>
+      <c r="C232" s="20">
+        <f>MIN(0,B232-MAX($B$2:B232))</f>
         <v/>
       </c>
     </row>
     <row r="233">
-      <c r="E233" s="4">
-        <f>IF(OR(Trades!M222="WIN",Trades!M222="LOSS"),E232+Trades!N222,E232)</f>
-        <v/>
-      </c>
-      <c r="F233" s="15">
-        <f>MIN(0,E233-MAX($E$13:E233))</f>
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="4">
+        <f>IF(OR(Trades!M233="WIN",Trades!M233="LOSS"),B232+Trades!N233,B232)</f>
+        <v/>
+      </c>
+      <c r="C233" s="20">
+        <f>MIN(0,B233-MAX($B$2:B233))</f>
         <v/>
       </c>
     </row>
     <row r="234">
-      <c r="E234" s="4">
-        <f>IF(OR(Trades!M223="WIN",Trades!M223="LOSS"),E233+Trades!N223,E233)</f>
-        <v/>
-      </c>
-      <c r="F234" s="15">
-        <f>MIN(0,E234-MAX($E$13:E234))</f>
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="4">
+        <f>IF(OR(Trades!M234="WIN",Trades!M234="LOSS"),B233+Trades!N234,B233)</f>
+        <v/>
+      </c>
+      <c r="C234" s="20">
+        <f>MIN(0,B234-MAX($B$2:B234))</f>
         <v/>
       </c>
     </row>
     <row r="235">
-      <c r="E235" s="4">
-        <f>IF(OR(Trades!M224="WIN",Trades!M224="LOSS"),E234+Trades!N224,E234)</f>
-        <v/>
-      </c>
-      <c r="F235" s="15">
-        <f>MIN(0,E235-MAX($E$13:E235))</f>
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="4">
+        <f>IF(OR(Trades!M235="WIN",Trades!M235="LOSS"),B234+Trades!N235,B234)</f>
+        <v/>
+      </c>
+      <c r="C235" s="20">
+        <f>MIN(0,B235-MAX($B$2:B235))</f>
         <v/>
       </c>
     </row>
     <row r="236">
-      <c r="E236" s="4">
-        <f>IF(OR(Trades!M225="WIN",Trades!M225="LOSS"),E235+Trades!N225,E235)</f>
-        <v/>
-      </c>
-      <c r="F236" s="15">
-        <f>MIN(0,E236-MAX($E$13:E236))</f>
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="4">
+        <f>IF(OR(Trades!M236="WIN",Trades!M236="LOSS"),B235+Trades!N236,B235)</f>
+        <v/>
+      </c>
+      <c r="C236" s="20">
+        <f>MIN(0,B236-MAX($B$2:B236))</f>
         <v/>
       </c>
     </row>
     <row r="237">
-      <c r="E237" s="4">
-        <f>IF(OR(Trades!M226="WIN",Trades!M226="LOSS"),E236+Trades!N226,E236)</f>
-        <v/>
-      </c>
-      <c r="F237" s="15">
-        <f>MIN(0,E237-MAX($E$13:E237))</f>
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="4">
+        <f>IF(OR(Trades!M237="WIN",Trades!M237="LOSS"),B236+Trades!N237,B236)</f>
+        <v/>
+      </c>
+      <c r="C237" s="20">
+        <f>MIN(0,B237-MAX($B$2:B237))</f>
         <v/>
       </c>
     </row>
     <row r="238">
-      <c r="E238" s="4">
-        <f>IF(OR(Trades!M227="WIN",Trades!M227="LOSS"),E237+Trades!N227,E237)</f>
-        <v/>
-      </c>
-      <c r="F238" s="15">
-        <f>MIN(0,E238-MAX($E$13:E238))</f>
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="4">
+        <f>IF(OR(Trades!M238="WIN",Trades!M238="LOSS"),B237+Trades!N238,B237)</f>
+        <v/>
+      </c>
+      <c r="C238" s="20">
+        <f>MIN(0,B238-MAX($B$2:B238))</f>
         <v/>
       </c>
     </row>
     <row r="239">
-      <c r="E239" s="4">
-        <f>IF(OR(Trades!M228="WIN",Trades!M228="LOSS"),E238+Trades!N228,E238)</f>
-        <v/>
-      </c>
-      <c r="F239" s="15">
-        <f>MIN(0,E239-MAX($E$13:E239))</f>
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="4">
+        <f>IF(OR(Trades!M239="WIN",Trades!M239="LOSS"),B238+Trades!N239,B238)</f>
+        <v/>
+      </c>
+      <c r="C239" s="20">
+        <f>MIN(0,B239-MAX($B$2:B239))</f>
         <v/>
       </c>
     </row>
     <row r="240">
-      <c r="E240" s="4">
-        <f>IF(OR(Trades!M229="WIN",Trades!M229="LOSS"),E239+Trades!N229,E239)</f>
-        <v/>
-      </c>
-      <c r="F240" s="15">
-        <f>MIN(0,E240-MAX($E$13:E240))</f>
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="4">
+        <f>IF(OR(Trades!M240="WIN",Trades!M240="LOSS"),B239+Trades!N240,B239)</f>
+        <v/>
+      </c>
+      <c r="C240" s="20">
+        <f>MIN(0,B240-MAX($B$2:B240))</f>
         <v/>
       </c>
     </row>
     <row r="241">
-      <c r="E241" s="4">
-        <f>IF(OR(Trades!M230="WIN",Trades!M230="LOSS"),E240+Trades!N230,E240)</f>
-        <v/>
-      </c>
-      <c r="F241" s="15">
-        <f>MIN(0,E241-MAX($E$13:E241))</f>
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="4">
+        <f>IF(OR(Trades!M241="WIN",Trades!M241="LOSS"),B240+Trades!N241,B240)</f>
+        <v/>
+      </c>
+      <c r="C241" s="20">
+        <f>MIN(0,B241-MAX($B$2:B241))</f>
         <v/>
       </c>
     </row>
     <row r="242">
-      <c r="E242" s="4">
-        <f>IF(OR(Trades!M231="WIN",Trades!M231="LOSS"),E241+Trades!N231,E241)</f>
-        <v/>
-      </c>
-      <c r="F242" s="15">
-        <f>MIN(0,E242-MAX($E$13:E242))</f>
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="4">
+        <f>IF(OR(Trades!M242="WIN",Trades!M242="LOSS"),B241+Trades!N242,B241)</f>
+        <v/>
+      </c>
+      <c r="C242" s="20">
+        <f>MIN(0,B242-MAX($B$2:B242))</f>
         <v/>
       </c>
     </row>
     <row r="243">
-      <c r="E243" s="4">
-        <f>IF(OR(Trades!M232="WIN",Trades!M232="LOSS"),E242+Trades!N232,E242)</f>
-        <v/>
-      </c>
-      <c r="F243" s="15">
-        <f>MIN(0,E243-MAX($E$13:E243))</f>
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="4">
+        <f>IF(OR(Trades!M243="WIN",Trades!M243="LOSS"),B242+Trades!N243,B242)</f>
+        <v/>
+      </c>
+      <c r="C243" s="20">
+        <f>MIN(0,B243-MAX($B$2:B243))</f>
         <v/>
       </c>
     </row>
     <row r="244">
-      <c r="E244" s="4">
-        <f>IF(OR(Trades!M233="WIN",Trades!M233="LOSS"),E243+Trades!N233,E243)</f>
-        <v/>
-      </c>
-      <c r="F244" s="15">
-        <f>MIN(0,E244-MAX($E$13:E244))</f>
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="4">
+        <f>IF(OR(Trades!M244="WIN",Trades!M244="LOSS"),B243+Trades!N244,B243)</f>
+        <v/>
+      </c>
+      <c r="C244" s="20">
+        <f>MIN(0,B244-MAX($B$2:B244))</f>
         <v/>
       </c>
     </row>
     <row r="245">
-      <c r="E245" s="4">
-        <f>IF(OR(Trades!M234="WIN",Trades!M234="LOSS"),E244+Trades!N234,E244)</f>
-        <v/>
-      </c>
-      <c r="F245" s="15">
-        <f>MIN(0,E245-MAX($E$13:E245))</f>
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="4">
+        <f>IF(OR(Trades!M245="WIN",Trades!M245="LOSS"),B244+Trades!N245,B244)</f>
+        <v/>
+      </c>
+      <c r="C245" s="20">
+        <f>MIN(0,B245-MAX($B$2:B245))</f>
         <v/>
       </c>
     </row>
     <row r="246">
-      <c r="E246" s="4">
-        <f>IF(OR(Trades!M235="WIN",Trades!M235="LOSS"),E245+Trades!N235,E245)</f>
-        <v/>
-      </c>
-      <c r="F246" s="15">
-        <f>MIN(0,E246-MAX($E$13:E246))</f>
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="4">
+        <f>IF(OR(Trades!M246="WIN",Trades!M246="LOSS"),B245+Trades!N246,B245)</f>
+        <v/>
+      </c>
+      <c r="C246" s="20">
+        <f>MIN(0,B246-MAX($B$2:B246))</f>
         <v/>
       </c>
     </row>
     <row r="247">
-      <c r="E247" s="4">
-        <f>IF(OR(Trades!M236="WIN",Trades!M236="LOSS"),E246+Trades!N236,E246)</f>
-        <v/>
-      </c>
-      <c r="F247" s="15">
-        <f>MIN(0,E247-MAX($E$13:E247))</f>
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="4">
+        <f>IF(OR(Trades!M247="WIN",Trades!M247="LOSS"),B246+Trades!N247,B246)</f>
+        <v/>
+      </c>
+      <c r="C247" s="20">
+        <f>MIN(0,B247-MAX($B$2:B247))</f>
         <v/>
       </c>
     </row>
     <row r="248">
-      <c r="E248" s="4">
-        <f>IF(OR(Trades!M237="WIN",Trades!M237="LOSS"),E247+Trades!N237,E247)</f>
-        <v/>
-      </c>
-      <c r="F248" s="15">
-        <f>MIN(0,E248-MAX($E$13:E248))</f>
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="4">
+        <f>IF(OR(Trades!M248="WIN",Trades!M248="LOSS"),B247+Trades!N248,B247)</f>
+        <v/>
+      </c>
+      <c r="C248" s="20">
+        <f>MIN(0,B248-MAX($B$2:B248))</f>
         <v/>
       </c>
     </row>
     <row r="249">
-      <c r="E249" s="4">
-        <f>IF(OR(Trades!M238="WIN",Trades!M238="LOSS"),E248+Trades!N238,E248)</f>
-        <v/>
-      </c>
-      <c r="F249" s="15">
-        <f>MIN(0,E249-MAX($E$13:E249))</f>
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="4">
+        <f>IF(OR(Trades!M249="WIN",Trades!M249="LOSS"),B248+Trades!N249,B248)</f>
+        <v/>
+      </c>
+      <c r="C249" s="20">
+        <f>MIN(0,B249-MAX($B$2:B249))</f>
         <v/>
       </c>
     </row>
     <row r="250">
-      <c r="E250" s="4">
-        <f>IF(OR(Trades!M239="WIN",Trades!M239="LOSS"),E249+Trades!N239,E249)</f>
-        <v/>
-      </c>
-      <c r="F250" s="15">
-        <f>MIN(0,E250-MAX($E$13:E250))</f>
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="4">
+        <f>IF(OR(Trades!M250="WIN",Trades!M250="LOSS"),B249+Trades!N250,B249)</f>
+        <v/>
+      </c>
+      <c r="C250" s="20">
+        <f>MIN(0,B250-MAX($B$2:B250))</f>
         <v/>
       </c>
     </row>
     <row r="251">
-      <c r="E251" s="4">
-        <f>IF(OR(Trades!M240="WIN",Trades!M240="LOSS"),E250+Trades!N240,E250)</f>
-        <v/>
-      </c>
-      <c r="F251" s="15">
-        <f>MIN(0,E251-MAX($E$13:E251))</f>
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="4">
+        <f>IF(OR(Trades!M251="WIN",Trades!M251="LOSS"),B250+Trades!N251,B250)</f>
+        <v/>
+      </c>
+      <c r="C251" s="20">
+        <f>MIN(0,B251-MAX($B$2:B251))</f>
         <v/>
       </c>
     </row>
     <row r="252">
-      <c r="E252" s="4">
-        <f>IF(OR(Trades!M241="WIN",Trades!M241="LOSS"),E251+Trades!N241,E251)</f>
-        <v/>
-      </c>
-      <c r="F252" s="15">
-        <f>MIN(0,E252-MAX($E$13:E252))</f>
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="4">
+        <f>IF(OR(Trades!M252="WIN",Trades!M252="LOSS"),B251+Trades!N252,B251)</f>
+        <v/>
+      </c>
+      <c r="C252" s="20">
+        <f>MIN(0,B252-MAX($B$2:B252))</f>
         <v/>
       </c>
     </row>
     <row r="253">
-      <c r="E253" s="4">
-        <f>IF(OR(Trades!M242="WIN",Trades!M242="LOSS"),E252+Trades!N242,E252)</f>
-        <v/>
-      </c>
-      <c r="F253" s="15">
-        <f>MIN(0,E253-MAX($E$13:E253))</f>
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="4">
+        <f>IF(OR(Trades!M253="WIN",Trades!M253="LOSS"),B252+Trades!N253,B252)</f>
+        <v/>
+      </c>
+      <c r="C253" s="20">
+        <f>MIN(0,B253-MAX($B$2:B253))</f>
         <v/>
       </c>
     </row>
     <row r="254">
-      <c r="E254" s="4">
-        <f>IF(OR(Trades!M243="WIN",Trades!M243="LOSS"),E253+Trades!N243,E253)</f>
-        <v/>
-      </c>
-      <c r="F254" s="15">
-        <f>MIN(0,E254-MAX($E$13:E254))</f>
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="4">
+        <f>IF(OR(Trades!M254="WIN",Trades!M254="LOSS"),B253+Trades!N254,B253)</f>
+        <v/>
+      </c>
+      <c r="C254" s="20">
+        <f>MIN(0,B254-MAX($B$2:B254))</f>
         <v/>
       </c>
     </row>
     <row r="255">
-      <c r="E255" s="4">
-        <f>IF(OR(Trades!M244="WIN",Trades!M244="LOSS"),E254+Trades!N244,E254)</f>
-        <v/>
-      </c>
-      <c r="F255" s="15">
-        <f>MIN(0,E255-MAX($E$13:E255))</f>
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="4">
+        <f>IF(OR(Trades!M255="WIN",Trades!M255="LOSS"),B254+Trades!N255,B254)</f>
+        <v/>
+      </c>
+      <c r="C255" s="20">
+        <f>MIN(0,B255-MAX($B$2:B255))</f>
         <v/>
       </c>
     </row>
     <row r="256">
-      <c r="E256" s="4">
-        <f>IF(OR(Trades!M245="WIN",Trades!M245="LOSS"),E255+Trades!N245,E255)</f>
-        <v/>
-      </c>
-      <c r="F256" s="15">
-        <f>MIN(0,E256-MAX($E$13:E256))</f>
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="4">
+        <f>IF(OR(Trades!M256="WIN",Trades!M256="LOSS"),B255+Trades!N256,B255)</f>
+        <v/>
+      </c>
+      <c r="C256" s="20">
+        <f>MIN(0,B256-MAX($B$2:B256))</f>
         <v/>
       </c>
     </row>
     <row r="257">
-      <c r="E257" s="4">
-        <f>IF(OR(Trades!M246="WIN",Trades!M246="LOSS"),E256+Trades!N246,E256)</f>
-        <v/>
-      </c>
-      <c r="F257" s="15">
-        <f>MIN(0,E257-MAX($E$13:E257))</f>
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="4">
+        <f>IF(OR(Trades!M257="WIN",Trades!M257="LOSS"),B256+Trades!N257,B256)</f>
+        <v/>
+      </c>
+      <c r="C257" s="20">
+        <f>MIN(0,B257-MAX($B$2:B257))</f>
         <v/>
       </c>
     </row>
     <row r="258">
-      <c r="E258" s="4">
-        <f>IF(OR(Trades!M247="WIN",Trades!M247="LOSS"),E257+Trades!N247,E257)</f>
-        <v/>
-      </c>
-      <c r="F258" s="15">
-        <f>MIN(0,E258-MAX($E$13:E258))</f>
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="4">
+        <f>IF(OR(Trades!M258="WIN",Trades!M258="LOSS"),B257+Trades!N258,B257)</f>
+        <v/>
+      </c>
+      <c r="C258" s="20">
+        <f>MIN(0,B258-MAX($B$2:B258))</f>
         <v/>
       </c>
     </row>
     <row r="259">
-      <c r="E259" s="4">
-        <f>IF(OR(Trades!M248="WIN",Trades!M248="LOSS"),E258+Trades!N248,E258)</f>
-        <v/>
-      </c>
-      <c r="F259" s="15">
-        <f>MIN(0,E259-MAX($E$13:E259))</f>
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="4">
+        <f>IF(OR(Trades!M259="WIN",Trades!M259="LOSS"),B258+Trades!N259,B258)</f>
+        <v/>
+      </c>
+      <c r="C259" s="20">
+        <f>MIN(0,B259-MAX($B$2:B259))</f>
         <v/>
       </c>
     </row>
     <row r="260">
-      <c r="E260" s="4">
-        <f>IF(OR(Trades!M249="WIN",Trades!M249="LOSS"),E259+Trades!N249,E259)</f>
-        <v/>
-      </c>
-      <c r="F260" s="15">
-        <f>MIN(0,E260-MAX($E$13:E260))</f>
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="4">
+        <f>IF(OR(Trades!M260="WIN",Trades!M260="LOSS"),B259+Trades!N260,B259)</f>
+        <v/>
+      </c>
+      <c r="C260" s="20">
+        <f>MIN(0,B260-MAX($B$2:B260))</f>
         <v/>
       </c>
     </row>
     <row r="261">
-      <c r="E261" s="4">
-        <f>IF(OR(Trades!M250="WIN",Trades!M250="LOSS"),E260+Trades!N250,E260)</f>
-        <v/>
-      </c>
-      <c r="F261" s="15">
-        <f>MIN(0,E261-MAX($E$13:E261))</f>
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="4">
+        <f>IF(OR(Trades!M261="WIN",Trades!M261="LOSS"),B260+Trades!N261,B260)</f>
+        <v/>
+      </c>
+      <c r="C261" s="20">
+        <f>MIN(0,B261-MAX($B$2:B261))</f>
         <v/>
       </c>
     </row>
     <row r="262">
-      <c r="E262" s="4">
-        <f>IF(OR(Trades!M251="WIN",Trades!M251="LOSS"),E261+Trades!N251,E261)</f>
-        <v/>
-      </c>
-      <c r="F262" s="15">
-        <f>MIN(0,E262-MAX($E$13:E262))</f>
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="4">
+        <f>IF(OR(Trades!M262="WIN",Trades!M262="LOSS"),B261+Trades!N262,B261)</f>
+        <v/>
+      </c>
+      <c r="C262" s="20">
+        <f>MIN(0,B262-MAX($B$2:B262))</f>
         <v/>
       </c>
     </row>
     <row r="263">
-      <c r="E263" s="4">
-        <f>IF(OR(Trades!M252="WIN",Trades!M252="LOSS"),E262+Trades!N252,E262)</f>
-        <v/>
-      </c>
-      <c r="F263" s="15">
-        <f>MIN(0,E263-MAX($E$13:E263))</f>
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="4">
+        <f>IF(OR(Trades!M263="WIN",Trades!M263="LOSS"),B262+Trades!N263,B262)</f>
+        <v/>
+      </c>
+      <c r="C263" s="20">
+        <f>MIN(0,B263-MAX($B$2:B263))</f>
         <v/>
       </c>
     </row>
     <row r="264">
-      <c r="E264" s="4">
-        <f>IF(OR(Trades!M253="WIN",Trades!M253="LOSS"),E263+Trades!N253,E263)</f>
-        <v/>
-      </c>
-      <c r="F264" s="15">
-        <f>MIN(0,E264-MAX($E$13:E264))</f>
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="4">
+        <f>IF(OR(Trades!M264="WIN",Trades!M264="LOSS"),B263+Trades!N264,B263)</f>
+        <v/>
+      </c>
+      <c r="C264" s="20">
+        <f>MIN(0,B264-MAX($B$2:B264))</f>
         <v/>
       </c>
     </row>
     <row r="265">
-      <c r="E265" s="4">
-        <f>IF(OR(Trades!M254="WIN",Trades!M254="LOSS"),E264+Trades!N254,E264)</f>
-        <v/>
-      </c>
-      <c r="F265" s="15">
-        <f>MIN(0,E265-MAX($E$13:E265))</f>
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="4">
+        <f>IF(OR(Trades!M265="WIN",Trades!M265="LOSS"),B264+Trades!N265,B264)</f>
+        <v/>
+      </c>
+      <c r="C265" s="20">
+        <f>MIN(0,B265-MAX($B$2:B265))</f>
         <v/>
       </c>
     </row>
     <row r="266">
-      <c r="E266" s="4">
-        <f>IF(OR(Trades!M255="WIN",Trades!M255="LOSS"),E265+Trades!N255,E265)</f>
-        <v/>
-      </c>
-      <c r="F266" s="15">
-        <f>MIN(0,E266-MAX($E$13:E266))</f>
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="4">
+        <f>IF(OR(Trades!M266="WIN",Trades!M266="LOSS"),B265+Trades!N266,B265)</f>
+        <v/>
+      </c>
+      <c r="C266" s="20">
+        <f>MIN(0,B266-MAX($B$2:B266))</f>
         <v/>
       </c>
     </row>
     <row r="267">
-      <c r="E267" s="4">
-        <f>IF(OR(Trades!M256="WIN",Trades!M256="LOSS"),E266+Trades!N256,E266)</f>
-        <v/>
-      </c>
-      <c r="F267" s="15">
-        <f>MIN(0,E267-MAX($E$13:E267))</f>
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="4">
+        <f>IF(OR(Trades!M267="WIN",Trades!M267="LOSS"),B266+Trades!N267,B266)</f>
+        <v/>
+      </c>
+      <c r="C267" s="20">
+        <f>MIN(0,B267-MAX($B$2:B267))</f>
         <v/>
       </c>
     </row>
     <row r="268">
-      <c r="E268" s="4">
-        <f>IF(OR(Trades!M257="WIN",Trades!M257="LOSS"),E267+Trades!N257,E267)</f>
-        <v/>
-      </c>
-      <c r="F268" s="15">
-        <f>MIN(0,E268-MAX($E$13:E268))</f>
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="4">
+        <f>IF(OR(Trades!M268="WIN",Trades!M268="LOSS"),B267+Trades!N268,B267)</f>
+        <v/>
+      </c>
+      <c r="C268" s="20">
+        <f>MIN(0,B268-MAX($B$2:B268))</f>
         <v/>
       </c>
     </row>
     <row r="269">
-      <c r="E269" s="4">
-        <f>IF(OR(Trades!M258="WIN",Trades!M258="LOSS"),E268+Trades!N258,E268)</f>
-        <v/>
-      </c>
-      <c r="F269" s="15">
-        <f>MIN(0,E269-MAX($E$13:E269))</f>
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="4">
+        <f>IF(OR(Trades!M269="WIN",Trades!M269="LOSS"),B268+Trades!N269,B268)</f>
+        <v/>
+      </c>
+      <c r="C269" s="20">
+        <f>MIN(0,B269-MAX($B$2:B269))</f>
         <v/>
       </c>
     </row>
     <row r="270">
-      <c r="E270" s="4">
-        <f>IF(OR(Trades!M259="WIN",Trades!M259="LOSS"),E269+Trades!N259,E269)</f>
-        <v/>
-      </c>
-      <c r="F270" s="15">
-        <f>MIN(0,E270-MAX($E$13:E270))</f>
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="4">
+        <f>IF(OR(Trades!M270="WIN",Trades!M270="LOSS"),B269+Trades!N270,B269)</f>
+        <v/>
+      </c>
+      <c r="C270" s="20">
+        <f>MIN(0,B270-MAX($B$2:B270))</f>
         <v/>
       </c>
     </row>
     <row r="271">
-      <c r="E271" s="4">
-        <f>IF(OR(Trades!M260="WIN",Trades!M260="LOSS"),E270+Trades!N260,E270)</f>
-        <v/>
-      </c>
-      <c r="F271" s="15">
-        <f>MIN(0,E271-MAX($E$13:E271))</f>
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" s="4">
+        <f>IF(OR(Trades!M271="WIN",Trades!M271="LOSS"),B270+Trades!N271,B270)</f>
+        <v/>
+      </c>
+      <c r="C271" s="20">
+        <f>MIN(0,B271-MAX($B$2:B271))</f>
         <v/>
       </c>
     </row>
     <row r="272">
-      <c r="E272" s="4">
-        <f>IF(OR(Trades!M261="WIN",Trades!M261="LOSS"),E271+Trades!N261,E271)</f>
-        <v/>
-      </c>
-      <c r="F272" s="15">
-        <f>MIN(0,E272-MAX($E$13:E272))</f>
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" s="4">
+        <f>IF(OR(Trades!M272="WIN",Trades!M272="LOSS"),B271+Trades!N272,B271)</f>
+        <v/>
+      </c>
+      <c r="C272" s="20">
+        <f>MIN(0,B272-MAX($B$2:B272))</f>
         <v/>
       </c>
     </row>
     <row r="273">
-      <c r="E273" s="4">
-        <f>IF(OR(Trades!M262="WIN",Trades!M262="LOSS"),E272+Trades!N262,E272)</f>
-        <v/>
-      </c>
-      <c r="F273" s="15">
-        <f>MIN(0,E273-MAX($E$13:E273))</f>
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" s="4">
+        <f>IF(OR(Trades!M273="WIN",Trades!M273="LOSS"),B272+Trades!N273,B272)</f>
+        <v/>
+      </c>
+      <c r="C273" s="20">
+        <f>MIN(0,B273-MAX($B$2:B273))</f>
         <v/>
       </c>
     </row>
     <row r="274">
-      <c r="E274" s="4">
-        <f>IF(OR(Trades!M263="WIN",Trades!M263="LOSS"),E273+Trades!N263,E273)</f>
-        <v/>
-      </c>
-      <c r="F274" s="15">
-        <f>MIN(0,E274-MAX($E$13:E274))</f>
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" s="4">
+        <f>IF(OR(Trades!M274="WIN",Trades!M274="LOSS"),B273+Trades!N274,B273)</f>
+        <v/>
+      </c>
+      <c r="C274" s="20">
+        <f>MIN(0,B274-MAX($B$2:B274))</f>
         <v/>
       </c>
     </row>
     <row r="275">
-      <c r="E275" s="4">
-        <f>IF(OR(Trades!M264="WIN",Trades!M264="LOSS"),E274+Trades!N264,E274)</f>
-        <v/>
-      </c>
-      <c r="F275" s="15">
-        <f>MIN(0,E275-MAX($E$13:E275))</f>
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" s="4">
+        <f>IF(OR(Trades!M275="WIN",Trades!M275="LOSS"),B274+Trades!N275,B274)</f>
+        <v/>
+      </c>
+      <c r="C275" s="20">
+        <f>MIN(0,B275-MAX($B$2:B275))</f>
         <v/>
       </c>
     </row>
     <row r="276">
-      <c r="E276" s="4">
-        <f>IF(OR(Trades!M265="WIN",Trades!M265="LOSS"),E275+Trades!N265,E275)</f>
-        <v/>
-      </c>
-      <c r="F276" s="15">
-        <f>MIN(0,E276-MAX($E$13:E276))</f>
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" s="4">
+        <f>IF(OR(Trades!M276="WIN",Trades!M276="LOSS"),B275+Trades!N276,B275)</f>
+        <v/>
+      </c>
+      <c r="C276" s="20">
+        <f>MIN(0,B276-MAX($B$2:B276))</f>
         <v/>
       </c>
     </row>
     <row r="277">
-      <c r="E277" s="4">
-        <f>IF(OR(Trades!M266="WIN",Trades!M266="LOSS"),E276+Trades!N266,E276)</f>
-        <v/>
-      </c>
-      <c r="F277" s="15">
-        <f>MIN(0,E277-MAX($E$13:E277))</f>
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" s="4">
+        <f>IF(OR(Trades!M277="WIN",Trades!M277="LOSS"),B276+Trades!N277,B276)</f>
+        <v/>
+      </c>
+      <c r="C277" s="20">
+        <f>MIN(0,B277-MAX($B$2:B277))</f>
         <v/>
       </c>
     </row>
     <row r="278">
-      <c r="E278" s="4">
-        <f>IF(OR(Trades!M267="WIN",Trades!M267="LOSS"),E277+Trades!N267,E277)</f>
-        <v/>
-      </c>
-      <c r="F278" s="15">
-        <f>MIN(0,E278-MAX($E$13:E278))</f>
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" s="4">
+        <f>IF(OR(Trades!M278="WIN",Trades!M278="LOSS"),B277+Trades!N278,B277)</f>
+        <v/>
+      </c>
+      <c r="C278" s="20">
+        <f>MIN(0,B278-MAX($B$2:B278))</f>
         <v/>
       </c>
     </row>
     <row r="279">
-      <c r="E279" s="4">
-        <f>IF(OR(Trades!M268="WIN",Trades!M268="LOSS"),E278+Trades!N268,E278)</f>
-        <v/>
-      </c>
-      <c r="F279" s="15">
-        <f>MIN(0,E279-MAX($E$13:E279))</f>
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" s="4">
+        <f>IF(OR(Trades!M279="WIN",Trades!M279="LOSS"),B278+Trades!N279,B278)</f>
+        <v/>
+      </c>
+      <c r="C279" s="20">
+        <f>MIN(0,B279-MAX($B$2:B279))</f>
         <v/>
       </c>
     </row>
     <row r="280">
-      <c r="E280" s="4">
-        <f>IF(OR(Trades!M269="WIN",Trades!M269="LOSS"),E279+Trades!N269,E279)</f>
-        <v/>
-      </c>
-      <c r="F280" s="15">
-        <f>MIN(0,E280-MAX($E$13:E280))</f>
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="4">
+        <f>IF(OR(Trades!M280="WIN",Trades!M280="LOSS"),B279+Trades!N280,B279)</f>
+        <v/>
+      </c>
+      <c r="C280" s="20">
+        <f>MIN(0,B280-MAX($B$2:B280))</f>
         <v/>
       </c>
     </row>
     <row r="281">
-      <c r="E281" s="4">
-        <f>IF(OR(Trades!M270="WIN",Trades!M270="LOSS"),E280+Trades!N270,E280)</f>
-        <v/>
-      </c>
-      <c r="F281" s="15">
-        <f>MIN(0,E281-MAX($E$13:E281))</f>
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="4">
+        <f>IF(OR(Trades!M281="WIN",Trades!M281="LOSS"),B280+Trades!N281,B280)</f>
+        <v/>
+      </c>
+      <c r="C281" s="20">
+        <f>MIN(0,B281-MAX($B$2:B281))</f>
         <v/>
       </c>
     </row>
     <row r="282">
-      <c r="E282" s="4">
-        <f>IF(OR(Trades!M271="WIN",Trades!M271="LOSS"),E281+Trades!N271,E281)</f>
-        <v/>
-      </c>
-      <c r="F282" s="15">
-        <f>MIN(0,E282-MAX($E$13:E282))</f>
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="4">
+        <f>IF(OR(Trades!M282="WIN",Trades!M282="LOSS"),B281+Trades!N282,B281)</f>
+        <v/>
+      </c>
+      <c r="C282" s="20">
+        <f>MIN(0,B282-MAX($B$2:B282))</f>
         <v/>
       </c>
     </row>
     <row r="283">
-      <c r="E283" s="4">
-        <f>IF(OR(Trades!M272="WIN",Trades!M272="LOSS"),E282+Trades!N272,E282)</f>
-        <v/>
-      </c>
-      <c r="F283" s="15">
-        <f>MIN(0,E283-MAX($E$13:E283))</f>
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="4">
+        <f>IF(OR(Trades!M283="WIN",Trades!M283="LOSS"),B282+Trades!N283,B282)</f>
+        <v/>
+      </c>
+      <c r="C283" s="20">
+        <f>MIN(0,B283-MAX($B$2:B283))</f>
         <v/>
       </c>
     </row>
     <row r="284">
-      <c r="E284" s="4">
-        <f>IF(OR(Trades!M273="WIN",Trades!M273="LOSS"),E283+Trades!N273,E283)</f>
-        <v/>
-      </c>
-      <c r="F284" s="15">
-        <f>MIN(0,E284-MAX($E$13:E284))</f>
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" s="4">
+        <f>IF(OR(Trades!M284="WIN",Trades!M284="LOSS"),B283+Trades!N284,B283)</f>
+        <v/>
+      </c>
+      <c r="C284" s="20">
+        <f>MIN(0,B284-MAX($B$2:B284))</f>
         <v/>
       </c>
     </row>
     <row r="285">
-      <c r="E285" s="4">
-        <f>IF(OR(Trades!M274="WIN",Trades!M274="LOSS"),E284+Trades!N274,E284)</f>
-        <v/>
-      </c>
-      <c r="F285" s="15">
-        <f>MIN(0,E285-MAX($E$13:E285))</f>
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" s="4">
+        <f>IF(OR(Trades!M285="WIN",Trades!M285="LOSS"),B284+Trades!N285,B284)</f>
+        <v/>
+      </c>
+      <c r="C285" s="20">
+        <f>MIN(0,B285-MAX($B$2:B285))</f>
         <v/>
       </c>
     </row>
     <row r="286">
-      <c r="E286" s="4">
-        <f>IF(OR(Trades!M275="WIN",Trades!M275="LOSS"),E285+Trades!N275,E285)</f>
-        <v/>
-      </c>
-      <c r="F286" s="15">
-        <f>MIN(0,E286-MAX($E$13:E286))</f>
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" s="4">
+        <f>IF(OR(Trades!M286="WIN",Trades!M286="LOSS"),B285+Trades!N286,B285)</f>
+        <v/>
+      </c>
+      <c r="C286" s="20">
+        <f>MIN(0,B286-MAX($B$2:B286))</f>
         <v/>
       </c>
     </row>
     <row r="287">
-      <c r="E287" s="4">
-        <f>IF(OR(Trades!M276="WIN",Trades!M276="LOSS"),E286+Trades!N276,E286)</f>
-        <v/>
-      </c>
-      <c r="F287" s="15">
-        <f>MIN(0,E287-MAX($E$13:E287))</f>
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" s="4">
+        <f>IF(OR(Trades!M287="WIN",Trades!M287="LOSS"),B286+Trades!N287,B286)</f>
+        <v/>
+      </c>
+      <c r="C287" s="20">
+        <f>MIN(0,B287-MAX($B$2:B287))</f>
         <v/>
       </c>
     </row>
     <row r="288">
-      <c r="E288" s="4">
-        <f>IF(OR(Trades!M277="WIN",Trades!M277="LOSS"),E287+Trades!N277,E287)</f>
-        <v/>
-      </c>
-      <c r="F288" s="15">
-        <f>MIN(0,E288-MAX($E$13:E288))</f>
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="4">
+        <f>IF(OR(Trades!M288="WIN",Trades!M288="LOSS"),B287+Trades!N288,B287)</f>
+        <v/>
+      </c>
+      <c r="C288" s="20">
+        <f>MIN(0,B288-MAX($B$2:B288))</f>
         <v/>
       </c>
     </row>
     <row r="289">
-      <c r="E289" s="4">
-        <f>IF(OR(Trades!M278="WIN",Trades!M278="LOSS"),E288+Trades!N278,E288)</f>
-        <v/>
-      </c>
-      <c r="F289" s="15">
-        <f>MIN(0,E289-MAX($E$13:E289))</f>
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="4">
+        <f>IF(OR(Trades!M289="WIN",Trades!M289="LOSS"),B288+Trades!N289,B288)</f>
+        <v/>
+      </c>
+      <c r="C289" s="20">
+        <f>MIN(0,B289-MAX($B$2:B289))</f>
         <v/>
       </c>
     </row>
     <row r="290">
-      <c r="E290" s="4">
-        <f>IF(OR(Trades!M279="WIN",Trades!M279="LOSS"),E289+Trades!N279,E289)</f>
-        <v/>
-      </c>
-      <c r="F290" s="15">
-        <f>MIN(0,E290-MAX($E$13:E290))</f>
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="4">
+        <f>IF(OR(Trades!M290="WIN",Trades!M290="LOSS"),B289+Trades!N290,B289)</f>
+        <v/>
+      </c>
+      <c r="C290" s="20">
+        <f>MIN(0,B290-MAX($B$2:B290))</f>
         <v/>
       </c>
     </row>
     <row r="291">
-      <c r="E291" s="4">
-        <f>IF(OR(Trades!M280="WIN",Trades!M280="LOSS"),E290+Trades!N280,E290)</f>
-        <v/>
-      </c>
-      <c r="F291" s="15">
-        <f>MIN(0,E291-MAX($E$13:E291))</f>
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" s="4">
+        <f>IF(OR(Trades!M291="WIN",Trades!M291="LOSS"),B290+Trades!N291,B290)</f>
+        <v/>
+      </c>
+      <c r="C291" s="20">
+        <f>MIN(0,B291-MAX($B$2:B291))</f>
         <v/>
       </c>
     </row>
     <row r="292">
-      <c r="E292" s="4">
-        <f>IF(OR(Trades!M281="WIN",Trades!M281="LOSS"),E291+Trades!N281,E291)</f>
-        <v/>
-      </c>
-      <c r="F292" s="15">
-        <f>MIN(0,E292-MAX($E$13:E292))</f>
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" s="4">
+        <f>IF(OR(Trades!M292="WIN",Trades!M292="LOSS"),B291+Trades!N292,B291)</f>
+        <v/>
+      </c>
+      <c r="C292" s="20">
+        <f>MIN(0,B292-MAX($B$2:B292))</f>
         <v/>
       </c>
     </row>
     <row r="293">
-      <c r="E293" s="4">
-        <f>IF(OR(Trades!M282="WIN",Trades!M282="LOSS"),E292+Trades!N282,E292)</f>
-        <v/>
-      </c>
-      <c r="F293" s="15">
-        <f>MIN(0,E293-MAX($E$13:E293))</f>
+      <c r="A293" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" s="4">
+        <f>IF(OR(Trades!M293="WIN",Trades!M293="LOSS"),B292+Trades!N293,B292)</f>
+        <v/>
+      </c>
+      <c r="C293" s="20">
+        <f>MIN(0,B293-MAX($B$2:B293))</f>
         <v/>
       </c>
     </row>
     <row r="294">
-      <c r="E294" s="4">
-        <f>IF(OR(Trades!M283="WIN",Trades!M283="LOSS"),E293+Trades!N283,E293)</f>
-        <v/>
-      </c>
-      <c r="F294" s="15">
-        <f>MIN(0,E294-MAX($E$13:E294))</f>
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" s="4">
+        <f>IF(OR(Trades!M294="WIN",Trades!M294="LOSS"),B293+Trades!N294,B293)</f>
+        <v/>
+      </c>
+      <c r="C294" s="20">
+        <f>MIN(0,B294-MAX($B$2:B294))</f>
         <v/>
       </c>
     </row>
     <row r="295">
-      <c r="E295" s="4">
-        <f>IF(OR(Trades!M284="WIN",Trades!M284="LOSS"),E294+Trades!N284,E294)</f>
-        <v/>
-      </c>
-      <c r="F295" s="15">
-        <f>MIN(0,E295-MAX($E$13:E295))</f>
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" s="4">
+        <f>IF(OR(Trades!M295="WIN",Trades!M295="LOSS"),B294+Trades!N295,B294)</f>
+        <v/>
+      </c>
+      <c r="C295" s="20">
+        <f>MIN(0,B295-MAX($B$2:B295))</f>
         <v/>
       </c>
     </row>
     <row r="296">
-      <c r="E296" s="4">
-        <f>IF(OR(Trades!M285="WIN",Trades!M285="LOSS"),E295+Trades!N285,E295)</f>
-        <v/>
-      </c>
-      <c r="F296" s="15">
-        <f>MIN(0,E296-MAX($E$13:E296))</f>
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" s="4">
+        <f>IF(OR(Trades!M296="WIN",Trades!M296="LOSS"),B295+Trades!N296,B295)</f>
+        <v/>
+      </c>
+      <c r="C296" s="20">
+        <f>MIN(0,B296-MAX($B$2:B296))</f>
         <v/>
       </c>
     </row>
     <row r="297">
-      <c r="E297" s="4">
-        <f>IF(OR(Trades!M286="WIN",Trades!M286="LOSS"),E296+Trades!N286,E296)</f>
-        <v/>
-      </c>
-      <c r="F297" s="15">
-        <f>MIN(0,E297-MAX($E$13:E297))</f>
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" s="4">
+        <f>IF(OR(Trades!M297="WIN",Trades!M297="LOSS"),B296+Trades!N297,B296)</f>
+        <v/>
+      </c>
+      <c r="C297" s="20">
+        <f>MIN(0,B297-MAX($B$2:B297))</f>
         <v/>
       </c>
     </row>
     <row r="298">
-      <c r="E298" s="4">
-        <f>IF(OR(Trades!M287="WIN",Trades!M287="LOSS"),E297+Trades!N287,E297)</f>
-        <v/>
-      </c>
-      <c r="F298" s="15">
-        <f>MIN(0,E298-MAX($E$13:E298))</f>
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" s="4">
+        <f>IF(OR(Trades!M298="WIN",Trades!M298="LOSS"),B297+Trades!N298,B297)</f>
+        <v/>
+      </c>
+      <c r="C298" s="20">
+        <f>MIN(0,B298-MAX($B$2:B298))</f>
         <v/>
       </c>
     </row>
     <row r="299">
-      <c r="E299" s="4">
-        <f>IF(OR(Trades!M288="WIN",Trades!M288="LOSS"),E298+Trades!N288,E298)</f>
-        <v/>
-      </c>
-      <c r="F299" s="15">
-        <f>MIN(0,E299-MAX($E$13:E299))</f>
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" s="4">
+        <f>IF(OR(Trades!M299="WIN",Trades!M299="LOSS"),B298+Trades!N299,B298)</f>
+        <v/>
+      </c>
+      <c r="C299" s="20">
+        <f>MIN(0,B299-MAX($B$2:B299))</f>
         <v/>
       </c>
     </row>
     <row r="300">
-      <c r="E300" s="4">
-        <f>IF(OR(Trades!M289="WIN",Trades!M289="LOSS"),E299+Trades!N289,E299)</f>
-        <v/>
-      </c>
-      <c r="F300" s="15">
-        <f>MIN(0,E300-MAX($E$13:E300))</f>
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" s="4">
+        <f>IF(OR(Trades!M300="WIN",Trades!M300="LOSS"),B299+Trades!N300,B299)</f>
+        <v/>
+      </c>
+      <c r="C300" s="20">
+        <f>MIN(0,B300-MAX($B$2:B300))</f>
         <v/>
       </c>
     </row>
     <row r="301">
-      <c r="E301" s="4">
-        <f>IF(OR(Trades!M290="WIN",Trades!M290="LOSS"),E300+Trades!N290,E300)</f>
-        <v/>
-      </c>
-      <c r="F301" s="15">
-        <f>MIN(0,E301-MAX($E$13:E301))</f>
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" s="4">
+        <f>IF(OR(Trades!M301="WIN",Trades!M301="LOSS"),B300+Trades!N301,B300)</f>
+        <v/>
+      </c>
+      <c r="C301" s="20">
+        <f>MIN(0,B301-MAX($B$2:B301))</f>
         <v/>
       </c>
     </row>
     <row r="302">
-      <c r="E302" s="4">
-        <f>IF(OR(Trades!M291="WIN",Trades!M291="LOSS"),E301+Trades!N291,E301)</f>
-        <v/>
-      </c>
-      <c r="F302" s="15">
-        <f>MIN(0,E302-MAX($E$13:E302))</f>
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" s="4">
+        <f>IF(OR(Trades!M302="WIN",Trades!M302="LOSS"),B301+Trades!N302,B301)</f>
+        <v/>
+      </c>
+      <c r="C302" s="20">
+        <f>MIN(0,B302-MAX($B$2:B302))</f>
         <v/>
       </c>
     </row>
     <row r="303">
-      <c r="E303" s="4">
-        <f>IF(OR(Trades!M292="WIN",Trades!M292="LOSS"),E302+Trades!N292,E302)</f>
-        <v/>
-      </c>
-      <c r="F303" s="15">
-        <f>MIN(0,E303-MAX($E$13:E303))</f>
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" s="4">
+        <f>IF(OR(Trades!M303="WIN",Trades!M303="LOSS"),B302+Trades!N303,B302)</f>
+        <v/>
+      </c>
+      <c r="C303" s="20">
+        <f>MIN(0,B303-MAX($B$2:B303))</f>
         <v/>
       </c>
     </row>
     <row r="304">
-      <c r="E304" s="4">
-        <f>IF(OR(Trades!M293="WIN",Trades!M293="LOSS"),E303+Trades!N293,E303)</f>
-        <v/>
-      </c>
-      <c r="F304" s="15">
-        <f>MIN(0,E304-MAX($E$13:E304))</f>
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" s="4">
+        <f>IF(OR(Trades!M304="WIN",Trades!M304="LOSS"),B303+Trades!N304,B303)</f>
+        <v/>
+      </c>
+      <c r="C304" s="20">
+        <f>MIN(0,B304-MAX($B$2:B304))</f>
         <v/>
       </c>
     </row>
     <row r="305">
-      <c r="E305" s="4">
-        <f>IF(OR(Trades!M294="WIN",Trades!M294="LOSS"),E304+Trades!N294,E304)</f>
-        <v/>
-      </c>
-      <c r="F305" s="15">
-        <f>MIN(0,E305-MAX($E$13:E305))</f>
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" s="4">
+        <f>IF(OR(Trades!M305="WIN",Trades!M305="LOSS"),B304+Trades!N305,B304)</f>
+        <v/>
+      </c>
+      <c r="C305" s="20">
+        <f>MIN(0,B305-MAX($B$2:B305))</f>
         <v/>
       </c>
     </row>
     <row r="306">
-      <c r="E306" s="4">
-        <f>IF(OR(Trades!M295="WIN",Trades!M295="LOSS"),E305+Trades!N295,E305)</f>
-        <v/>
-      </c>
-      <c r="F306" s="15">
-        <f>MIN(0,E306-MAX($E$13:E306))</f>
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" s="4">
+        <f>IF(OR(Trades!M306="WIN",Trades!M306="LOSS"),B305+Trades!N306,B305)</f>
+        <v/>
+      </c>
+      <c r="C306" s="20">
+        <f>MIN(0,B306-MAX($B$2:B306))</f>
         <v/>
       </c>
     </row>
     <row r="307">
-      <c r="E307" s="4">
-        <f>IF(OR(Trades!M296="WIN",Trades!M296="LOSS"),E306+Trades!N296,E306)</f>
-        <v/>
-      </c>
-      <c r="F307" s="15">
-        <f>MIN(0,E307-MAX($E$13:E307))</f>
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" s="4">
+        <f>IF(OR(Trades!M307="WIN",Trades!M307="LOSS"),B306+Trades!N307,B306)</f>
+        <v/>
+      </c>
+      <c r="C307" s="20">
+        <f>MIN(0,B307-MAX($B$2:B307))</f>
         <v/>
       </c>
     </row>
     <row r="308">
-      <c r="E308" s="4">
-        <f>IF(OR(Trades!M297="WIN",Trades!M297="LOSS"),E307+Trades!N297,E307)</f>
-        <v/>
-      </c>
-      <c r="F308" s="15">
-        <f>MIN(0,E308-MAX($E$13:E308))</f>
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" s="4">
+        <f>IF(OR(Trades!M308="WIN",Trades!M308="LOSS"),B307+Trades!N308,B307)</f>
+        <v/>
+      </c>
+      <c r="C308" s="20">
+        <f>MIN(0,B308-MAX($B$2:B308))</f>
         <v/>
       </c>
     </row>
     <row r="309">
-      <c r="E309" s="4">
-        <f>IF(OR(Trades!M298="WIN",Trades!M298="LOSS"),E308+Trades!N298,E308)</f>
-        <v/>
-      </c>
-      <c r="F309" s="15">
-        <f>MIN(0,E309-MAX($E$13:E309))</f>
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" s="4">
+        <f>IF(OR(Trades!M309="WIN",Trades!M309="LOSS"),B308+Trades!N309,B308)</f>
+        <v/>
+      </c>
+      <c r="C309" s="20">
+        <f>MIN(0,B309-MAX($B$2:B309))</f>
         <v/>
       </c>
     </row>
     <row r="310">
-      <c r="E310" s="4">
-        <f>IF(OR(Trades!M299="WIN",Trades!M299="LOSS"),E309+Trades!N299,E309)</f>
-        <v/>
-      </c>
-      <c r="F310" s="15">
-        <f>MIN(0,E310-MAX($E$13:E310))</f>
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" s="4">
+        <f>IF(OR(Trades!M310="WIN",Trades!M310="LOSS"),B309+Trades!N310,B309)</f>
+        <v/>
+      </c>
+      <c r="C310" s="20">
+        <f>MIN(0,B310-MAX($B$2:B310))</f>
         <v/>
       </c>
     </row>
     <row r="311">
-      <c r="E311" s="4">
-        <f>IF(OR(Trades!M300="WIN",Trades!M300="LOSS"),E310+Trades!N300,E310)</f>
-        <v/>
-      </c>
-      <c r="F311" s="15">
-        <f>MIN(0,E311-MAX($E$13:E311))</f>
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" s="4">
+        <f>IF(OR(Trades!M311="WIN",Trades!M311="LOSS"),B310+Trades!N311,B310)</f>
+        <v/>
+      </c>
+      <c r="C311" s="20">
+        <f>MIN(0,B311-MAX($B$2:B311))</f>
         <v/>
       </c>
     </row>
     <row r="312">
-      <c r="E312" s="4">
-        <f>IF(OR(Trades!M301="WIN",Trades!M301="LOSS"),E311+Trades!N301,E311)</f>
-        <v/>
-      </c>
-      <c r="F312" s="15">
-        <f>MIN(0,E312-MAX($E$13:E312))</f>
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" s="4">
+        <f>IF(OR(Trades!M312="WIN",Trades!M312="LOSS"),B311+Trades!N312,B311)</f>
+        <v/>
+      </c>
+      <c r="C312" s="20">
+        <f>MIN(0,B312-MAX($B$2:B312))</f>
         <v/>
       </c>
     </row>
     <row r="313">
-      <c r="E313" s="4">
-        <f>IF(OR(Trades!M302="WIN",Trades!M302="LOSS"),E312+Trades!N302,E312)</f>
-        <v/>
-      </c>
-      <c r="F313" s="15">
-        <f>MIN(0,E313-MAX($E$13:E313))</f>
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" s="4">
+        <f>IF(OR(Trades!M313="WIN",Trades!M313="LOSS"),B312+Trades!N313,B312)</f>
+        <v/>
+      </c>
+      <c r="C313" s="20">
+        <f>MIN(0,B313-MAX($B$2:B313))</f>
         <v/>
       </c>
     </row>
     <row r="314">
-      <c r="E314" s="4">
-        <f>IF(OR(Trades!M303="WIN",Trades!M303="LOSS"),E313+Trades!N303,E313)</f>
-        <v/>
-      </c>
-      <c r="F314" s="15">
-        <f>MIN(0,E314-MAX($E$13:E314))</f>
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" s="4">
+        <f>IF(OR(Trades!M314="WIN",Trades!M314="LOSS"),B313+Trades!N314,B313)</f>
+        <v/>
+      </c>
+      <c r="C314" s="20">
+        <f>MIN(0,B314-MAX($B$2:B314))</f>
         <v/>
       </c>
     </row>
     <row r="315">
-      <c r="E315" s="4">
-        <f>IF(OR(Trades!M304="WIN",Trades!M304="LOSS"),E314+Trades!N304,E314)</f>
-        <v/>
-      </c>
-      <c r="F315" s="15">
-        <f>MIN(0,E315-MAX($E$13:E315))</f>
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" s="4">
+        <f>IF(OR(Trades!M315="WIN",Trades!M315="LOSS"),B314+Trades!N315,B314)</f>
+        <v/>
+      </c>
+      <c r="C315" s="20">
+        <f>MIN(0,B315-MAX($B$2:B315))</f>
         <v/>
       </c>
     </row>
     <row r="316">
-      <c r="E316" s="4">
-        <f>IF(OR(Trades!M305="WIN",Trades!M305="LOSS"),E315+Trades!N305,E315)</f>
-        <v/>
-      </c>
-      <c r="F316" s="15">
-        <f>MIN(0,E316-MAX($E$13:E316))</f>
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" s="4">
+        <f>IF(OR(Trades!M316="WIN",Trades!M316="LOSS"),B315+Trades!N316,B315)</f>
+        <v/>
+      </c>
+      <c r="C316" s="20">
+        <f>MIN(0,B316-MAX($B$2:B316))</f>
         <v/>
       </c>
     </row>
     <row r="317">
-      <c r="E317" s="4">
-        <f>IF(OR(Trades!M306="WIN",Trades!M306="LOSS"),E316+Trades!N306,E316)</f>
-        <v/>
-      </c>
-      <c r="F317" s="15">
-        <f>MIN(0,E317-MAX($E$13:E317))</f>
+      <c r="A317" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" s="4">
+        <f>IF(OR(Trades!M317="WIN",Trades!M317="LOSS"),B316+Trades!N317,B316)</f>
+        <v/>
+      </c>
+      <c r="C317" s="20">
+        <f>MIN(0,B317-MAX($B$2:B317))</f>
         <v/>
       </c>
     </row>
     <row r="318">
-      <c r="E318" s="4">
-        <f>IF(OR(Trades!M307="WIN",Trades!M307="LOSS"),E317+Trades!N307,E317)</f>
-        <v/>
-      </c>
-      <c r="F318" s="15">
-        <f>MIN(0,E318-MAX($E$13:E318))</f>
+      <c r="A318" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" s="4">
+        <f>IF(OR(Trades!M318="WIN",Trades!M318="LOSS"),B317+Trades!N318,B317)</f>
+        <v/>
+      </c>
+      <c r="C318" s="20">
+        <f>MIN(0,B318-MAX($B$2:B318))</f>
         <v/>
       </c>
     </row>
     <row r="319">
-      <c r="E319" s="4">
-        <f>IF(OR(Trades!M308="WIN",Trades!M308="LOSS"),E318+Trades!N308,E318)</f>
-        <v/>
-      </c>
-      <c r="F319" s="15">
-        <f>MIN(0,E319-MAX($E$13:E319))</f>
+      <c r="A319" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" s="4">
+        <f>IF(OR(Trades!M319="WIN",Trades!M319="LOSS"),B318+Trades!N319,B318)</f>
+        <v/>
+      </c>
+      <c r="C319" s="20">
+        <f>MIN(0,B319-MAX($B$2:B319))</f>
         <v/>
       </c>
     </row>
     <row r="320">
-      <c r="E320" s="4">
-        <f>IF(OR(Trades!M309="WIN",Trades!M309="LOSS"),E319+Trades!N309,E319)</f>
-        <v/>
-      </c>
-      <c r="F320" s="15">
-        <f>MIN(0,E320-MAX($E$13:E320))</f>
+      <c r="A320" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" s="4">
+        <f>IF(OR(Trades!M320="WIN",Trades!M320="LOSS"),B319+Trades!N320,B319)</f>
+        <v/>
+      </c>
+      <c r="C320" s="20">
+        <f>MIN(0,B320-MAX($B$2:B320))</f>
         <v/>
       </c>
     </row>
     <row r="321">
-      <c r="E321" s="4">
-        <f>IF(OR(Trades!M310="WIN",Trades!M310="LOSS"),E320+Trades!N310,E320)</f>
-        <v/>
-      </c>
-      <c r="F321" s="15">
-        <f>MIN(0,E321-MAX($E$13:E321))</f>
+      <c r="A321" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" s="4">
+        <f>IF(OR(Trades!M321="WIN",Trades!M321="LOSS"),B320+Trades!N321,B320)</f>
+        <v/>
+      </c>
+      <c r="C321" s="20">
+        <f>MIN(0,B321-MAX($B$2:B321))</f>
         <v/>
       </c>
     </row>
     <row r="322">
-      <c r="E322" s="4">
-        <f>IF(OR(Trades!M311="WIN",Trades!M311="LOSS"),E321+Trades!N311,E321)</f>
-        <v/>
-      </c>
-      <c r="F322" s="15">
-        <f>MIN(0,E322-MAX($E$13:E322))</f>
+      <c r="A322" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" s="4">
+        <f>IF(OR(Trades!M322="WIN",Trades!M322="LOSS"),B321+Trades!N322,B321)</f>
+        <v/>
+      </c>
+      <c r="C322" s="20">
+        <f>MIN(0,B322-MAX($B$2:B322))</f>
         <v/>
       </c>
     </row>
     <row r="323">
-      <c r="E323" s="4">
-        <f>IF(OR(Trades!M312="WIN",Trades!M312="LOSS"),E322+Trades!N312,E322)</f>
-        <v/>
-      </c>
-      <c r="F323" s="15">
-        <f>MIN(0,E323-MAX($E$13:E323))</f>
+      <c r="A323" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" s="4">
+        <f>IF(OR(Trades!M323="WIN",Trades!M323="LOSS"),B322+Trades!N323,B322)</f>
+        <v/>
+      </c>
+      <c r="C323" s="20">
+        <f>MIN(0,B323-MAX($B$2:B323))</f>
         <v/>
       </c>
     </row>
     <row r="324">
-      <c r="E324" s="4">
-        <f>IF(OR(Trades!M313="WIN",Trades!M313="LOSS"),E323+Trades!N313,E323)</f>
-        <v/>
-      </c>
-      <c r="F324" s="15">
-        <f>MIN(0,E324-MAX($E$13:E324))</f>
+      <c r="A324" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" s="4">
+        <f>IF(OR(Trades!M324="WIN",Trades!M324="LOSS"),B323+Trades!N324,B323)</f>
+        <v/>
+      </c>
+      <c r="C324" s="20">
+        <f>MIN(0,B324-MAX($B$2:B324))</f>
         <v/>
       </c>
     </row>
     <row r="325">
-      <c r="E325" s="4">
-        <f>IF(OR(Trades!M314="WIN",Trades!M314="LOSS"),E324+Trades!N314,E324)</f>
-        <v/>
-      </c>
-      <c r="F325" s="15">
-        <f>MIN(0,E325-MAX($E$13:E325))</f>
+      <c r="A325" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" s="4">
+        <f>IF(OR(Trades!M325="WIN",Trades!M325="LOSS"),B324+Trades!N325,B324)</f>
+        <v/>
+      </c>
+      <c r="C325" s="20">
+        <f>MIN(0,B325-MAX($B$2:B325))</f>
         <v/>
       </c>
     </row>
     <row r="326">
-      <c r="E326" s="4">
-        <f>IF(OR(Trades!M315="WIN",Trades!M315="LOSS"),E325+Trades!N315,E325)</f>
-        <v/>
-      </c>
-      <c r="F326" s="15">
-        <f>MIN(0,E326-MAX($E$13:E326))</f>
+      <c r="A326" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" s="4">
+        <f>IF(OR(Trades!M326="WIN",Trades!M326="LOSS"),B325+Trades!N326,B325)</f>
+        <v/>
+      </c>
+      <c r="C326" s="20">
+        <f>MIN(0,B326-MAX($B$2:B326))</f>
         <v/>
       </c>
     </row>
     <row r="327">
-      <c r="E327" s="4">
-        <f>IF(OR(Trades!M316="WIN",Trades!M316="LOSS"),E326+Trades!N316,E326)</f>
-        <v/>
-      </c>
-      <c r="F327" s="15">
-        <f>MIN(0,E327-MAX($E$13:E327))</f>
+      <c r="A327" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" s="4">
+        <f>IF(OR(Trades!M327="WIN",Trades!M327="LOSS"),B326+Trades!N327,B326)</f>
+        <v/>
+      </c>
+      <c r="C327" s="20">
+        <f>MIN(0,B327-MAX($B$2:B327))</f>
         <v/>
       </c>
     </row>
     <row r="328">
-      <c r="E328" s="4">
-        <f>IF(OR(Trades!M317="WIN",Trades!M317="LOSS"),E327+Trades!N317,E327)</f>
-        <v/>
-      </c>
-      <c r="F328" s="15">
-        <f>MIN(0,E328-MAX($E$13:E328))</f>
+      <c r="A328" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" s="4">
+        <f>IF(OR(Trades!M328="WIN",Trades!M328="LOSS"),B327+Trades!N328,B327)</f>
+        <v/>
+      </c>
+      <c r="C328" s="20">
+        <f>MIN(0,B328-MAX($B$2:B328))</f>
         <v/>
       </c>
     </row>
     <row r="329">
-      <c r="E329" s="4">
-        <f>IF(OR(Trades!M318="WIN",Trades!M318="LOSS"),E328+Trades!N318,E328)</f>
-        <v/>
-      </c>
-      <c r="F329" s="15">
-        <f>MIN(0,E329-MAX($E$13:E329))</f>
+      <c r="A329" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" s="4">
+        <f>IF(OR(Trades!M329="WIN",Trades!M329="LOSS"),B328+Trades!N329,B328)</f>
+        <v/>
+      </c>
+      <c r="C329" s="20">
+        <f>MIN(0,B329-MAX($B$2:B329))</f>
         <v/>
       </c>
     </row>
     <row r="330">
-      <c r="E330" s="4">
-        <f>IF(OR(Trades!M319="WIN",Trades!M319="LOSS"),E329+Trades!N319,E329)</f>
-        <v/>
-      </c>
-      <c r="F330" s="15">
-        <f>MIN(0,E330-MAX($E$13:E330))</f>
+      <c r="A330" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" s="4">
+        <f>IF(OR(Trades!M330="WIN",Trades!M330="LOSS"),B329+Trades!N330,B329)</f>
+        <v/>
+      </c>
+      <c r="C330" s="20">
+        <f>MIN(0,B330-MAX($B$2:B330))</f>
         <v/>
       </c>
     </row>
     <row r="331">
-      <c r="E331" s="4">
-        <f>IF(OR(Trades!M320="WIN",Trades!M320="LOSS"),E330+Trades!N320,E330)</f>
-        <v/>
-      </c>
-      <c r="F331" s="15">
-        <f>MIN(0,E331-MAX($E$13:E331))</f>
+      <c r="A331" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" s="4">
+        <f>IF(OR(Trades!M331="WIN",Trades!M331="LOSS"),B330+Trades!N331,B330)</f>
+        <v/>
+      </c>
+      <c r="C331" s="20">
+        <f>MIN(0,B331-MAX($B$2:B331))</f>
         <v/>
       </c>
     </row>
     <row r="332">
-      <c r="E332" s="4">
-        <f>IF(OR(Trades!M321="WIN",Trades!M321="LOSS"),E331+Trades!N321,E331)</f>
-        <v/>
-      </c>
-      <c r="F332" s="15">
-        <f>MIN(0,E332-MAX($E$13:E332))</f>
+      <c r="A332" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" s="4">
+        <f>IF(OR(Trades!M332="WIN",Trades!M332="LOSS"),B331+Trades!N332,B331)</f>
+        <v/>
+      </c>
+      <c r="C332" s="20">
+        <f>MIN(0,B332-MAX($B$2:B332))</f>
         <v/>
       </c>
     </row>
     <row r="333">
-      <c r="E333" s="4">
-        <f>IF(OR(Trades!M322="WIN",Trades!M322="LOSS"),E332+Trades!N322,E332)</f>
-        <v/>
-      </c>
-      <c r="F333" s="15">
-        <f>MIN(0,E333-MAX($E$13:E333))</f>
+      <c r="A333" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" s="4">
+        <f>IF(OR(Trades!M333="WIN",Trades!M333="LOSS"),B332+Trades!N333,B332)</f>
+        <v/>
+      </c>
+      <c r="C333" s="20">
+        <f>MIN(0,B333-MAX($B$2:B333))</f>
         <v/>
       </c>
     </row>
     <row r="334">
-      <c r="E334" s="4">
-        <f>IF(OR(Trades!M323="WIN",Trades!M323="LOSS"),E333+Trades!N323,E333)</f>
-        <v/>
-      </c>
-      <c r="F334" s="15">
-        <f>MIN(0,E334-MAX($E$13:E334))</f>
+      <c r="A334" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" s="4">
+        <f>IF(OR(Trades!M334="WIN",Trades!M334="LOSS"),B333+Trades!N334,B333)</f>
+        <v/>
+      </c>
+      <c r="C334" s="20">
+        <f>MIN(0,B334-MAX($B$2:B334))</f>
         <v/>
       </c>
     </row>
     <row r="335">
-      <c r="E335" s="4">
-        <f>IF(OR(Trades!M324="WIN",Trades!M324="LOSS"),E334+Trades!N324,E334)</f>
-        <v/>
-      </c>
-      <c r="F335" s="15">
-        <f>MIN(0,E335-MAX($E$13:E335))</f>
+      <c r="A335" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" s="4">
+        <f>IF(OR(Trades!M335="WIN",Trades!M335="LOSS"),B334+Trades!N335,B334)</f>
+        <v/>
+      </c>
+      <c r="C335" s="20">
+        <f>MIN(0,B335-MAX($B$2:B335))</f>
         <v/>
       </c>
     </row>
     <row r="336">
-      <c r="E336" s="4">
-        <f>IF(OR(Trades!M325="WIN",Trades!M325="LOSS"),E335+Trades!N325,E335)</f>
-        <v/>
-      </c>
-      <c r="F336" s="15">
-        <f>MIN(0,E336-MAX($E$13:E336))</f>
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" s="4">
+        <f>IF(OR(Trades!M336="WIN",Trades!M336="LOSS"),B335+Trades!N336,B335)</f>
+        <v/>
+      </c>
+      <c r="C336" s="20">
+        <f>MIN(0,B336-MAX($B$2:B336))</f>
         <v/>
       </c>
     </row>
     <row r="337">
-      <c r="E337" s="4">
-        <f>IF(OR(Trades!M326="WIN",Trades!M326="LOSS"),E336+Trades!N326,E336)</f>
-        <v/>
-      </c>
-      <c r="F337" s="15">
-        <f>MIN(0,E337-MAX($E$13:E337))</f>
+      <c r="A337" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" s="4">
+        <f>IF(OR(Trades!M337="WIN",Trades!M337="LOSS"),B336+Trades!N337,B336)</f>
+        <v/>
+      </c>
+      <c r="C337" s="20">
+        <f>MIN(0,B337-MAX($B$2:B337))</f>
         <v/>
       </c>
     </row>
     <row r="338">
-      <c r="E338" s="4">
-        <f>IF(OR(Trades!M327="WIN",Trades!M327="LOSS"),E337+Trades!N327,E337)</f>
-        <v/>
-      </c>
-      <c r="F338" s="15">
-        <f>MIN(0,E338-MAX($E$13:E338))</f>
+      <c r="A338" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" s="4">
+        <f>IF(OR(Trades!M338="WIN",Trades!M338="LOSS"),B337+Trades!N338,B337)</f>
+        <v/>
+      </c>
+      <c r="C338" s="20">
+        <f>MIN(0,B338-MAX($B$2:B338))</f>
         <v/>
       </c>
     </row>
     <row r="339">
-      <c r="E339" s="4">
-        <f>IF(OR(Trades!M328="WIN",Trades!M328="LOSS"),E338+Trades!N328,E338)</f>
-        <v/>
-      </c>
-      <c r="F339" s="15">
-        <f>MIN(0,E339-MAX($E$13:E339))</f>
+      <c r="A339" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" s="4">
+        <f>IF(OR(Trades!M339="WIN",Trades!M339="LOSS"),B338+Trades!N339,B338)</f>
+        <v/>
+      </c>
+      <c r="C339" s="20">
+        <f>MIN(0,B339-MAX($B$2:B339))</f>
         <v/>
       </c>
     </row>
     <row r="340">
-      <c r="E340" s="4">
-        <f>IF(OR(Trades!M329="WIN",Trades!M329="LOSS"),E339+Trades!N329,E339)</f>
-        <v/>
-      </c>
-      <c r="F340" s="15">
-        <f>MIN(0,E340-MAX($E$13:E340))</f>
+      <c r="A340" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" s="4">
+        <f>IF(OR(Trades!M340="WIN",Trades!M340="LOSS"),B339+Trades!N340,B339)</f>
+        <v/>
+      </c>
+      <c r="C340" s="20">
+        <f>MIN(0,B340-MAX($B$2:B340))</f>
         <v/>
       </c>
     </row>
     <row r="341">
-      <c r="E341" s="4">
-        <f>IF(OR(Trades!M330="WIN",Trades!M330="LOSS"),E340+Trades!N330,E340)</f>
-        <v/>
-      </c>
-      <c r="F341" s="15">
-        <f>MIN(0,E341-MAX($E$13:E341))</f>
+      <c r="A341" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" s="4">
+        <f>IF(OR(Trades!M341="WIN",Trades!M341="LOSS"),B340+Trades!N341,B340)</f>
+        <v/>
+      </c>
+      <c r="C341" s="20">
+        <f>MIN(0,B341-MAX($B$2:B341))</f>
         <v/>
       </c>
     </row>
     <row r="342">
-      <c r="E342" s="4">
-        <f>IF(OR(Trades!M331="WIN",Trades!M331="LOSS"),E341+Trades!N331,E341)</f>
-        <v/>
-      </c>
-      <c r="F342" s="15">
-        <f>MIN(0,E342-MAX($E$13:E342))</f>
+      <c r="A342" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" s="4">
+        <f>IF(OR(Trades!M342="WIN",Trades!M342="LOSS"),B341+Trades!N342,B341)</f>
+        <v/>
+      </c>
+      <c r="C342" s="20">
+        <f>MIN(0,B342-MAX($B$2:B342))</f>
         <v/>
       </c>
     </row>
     <row r="343">
-      <c r="E343" s="4">
-        <f>IF(OR(Trades!M332="WIN",Trades!M332="LOSS"),E342+Trades!N332,E342)</f>
-        <v/>
-      </c>
-      <c r="F343" s="15">
-        <f>MIN(0,E343-MAX($E$13:E343))</f>
+      <c r="A343" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" s="4">
+        <f>IF(OR(Trades!M343="WIN",Trades!M343="LOSS"),B342+Trades!N343,B342)</f>
+        <v/>
+      </c>
+      <c r="C343" s="20">
+        <f>MIN(0,B343-MAX($B$2:B343))</f>
         <v/>
       </c>
     </row>
     <row r="344">
-      <c r="E344" s="4">
-        <f>IF(OR(Trades!M333="WIN",Trades!M333="LOSS"),E343+Trades!N333,E343)</f>
-        <v/>
-      </c>
-      <c r="F344" s="15">
-        <f>MIN(0,E344-MAX($E$13:E344))</f>
+      <c r="A344" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" s="4">
+        <f>IF(OR(Trades!M344="WIN",Trades!M344="LOSS"),B343+Trades!N344,B343)</f>
+        <v/>
+      </c>
+      <c r="C344" s="20">
+        <f>MIN(0,B344-MAX($B$2:B344))</f>
         <v/>
       </c>
     </row>
     <row r="345">
-      <c r="E345" s="4">
-        <f>IF(OR(Trades!M334="WIN",Trades!M334="LOSS"),E344+Trades!N334,E344)</f>
-        <v/>
-      </c>
-      <c r="F345" s="15">
-        <f>MIN(0,E345-MAX($E$13:E345))</f>
+      <c r="A345" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" s="4">
+        <f>IF(OR(Trades!M345="WIN",Trades!M345="LOSS"),B344+Trades!N345,B344)</f>
+        <v/>
+      </c>
+      <c r="C345" s="20">
+        <f>MIN(0,B345-MAX($B$2:B345))</f>
         <v/>
       </c>
     </row>
     <row r="346">
-      <c r="E346" s="4">
-        <f>IF(OR(Trades!M335="WIN",Trades!M335="LOSS"),E345+Trades!N335,E345)</f>
-        <v/>
-      </c>
-      <c r="F346" s="15">
-        <f>MIN(0,E346-MAX($E$13:E346))</f>
+      <c r="A346" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" s="4">
+        <f>IF(OR(Trades!M346="WIN",Trades!M346="LOSS"),B345+Trades!N346,B345)</f>
+        <v/>
+      </c>
+      <c r="C346" s="20">
+        <f>MIN(0,B346-MAX($B$2:B346))</f>
         <v/>
       </c>
     </row>
     <row r="347">
-      <c r="E347" s="4">
-        <f>IF(OR(Trades!M336="WIN",Trades!M336="LOSS"),E346+Trades!N336,E346)</f>
-        <v/>
-      </c>
-      <c r="F347" s="15">
-        <f>MIN(0,E347-MAX($E$13:E347))</f>
+      <c r="A347" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" s="4">
+        <f>IF(OR(Trades!M347="WIN",Trades!M347="LOSS"),B346+Trades!N347,B346)</f>
+        <v/>
+      </c>
+      <c r="C347" s="20">
+        <f>MIN(0,B347-MAX($B$2:B347))</f>
         <v/>
       </c>
     </row>
     <row r="348">
-      <c r="E348" s="4">
-        <f>IF(OR(Trades!M337="WIN",Trades!M337="LOSS"),E347+Trades!N337,E347)</f>
-        <v/>
-      </c>
-      <c r="F348" s="15">
-        <f>MIN(0,E348-MAX($E$13:E348))</f>
+      <c r="A348" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" s="4">
+        <f>IF(OR(Trades!M348="WIN",Trades!M348="LOSS"),B347+Trades!N348,B347)</f>
+        <v/>
+      </c>
+      <c r="C348" s="20">
+        <f>MIN(0,B348-MAX($B$2:B348))</f>
         <v/>
       </c>
     </row>
     <row r="349">
-      <c r="E349" s="4">
-        <f>IF(OR(Trades!M338="WIN",Trades!M338="LOSS"),E348+Trades!N338,E348)</f>
-        <v/>
-      </c>
-      <c r="F349" s="15">
-        <f>MIN(0,E349-MAX($E$13:E349))</f>
+      <c r="A349" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" s="4">
+        <f>IF(OR(Trades!M349="WIN",Trades!M349="LOSS"),B348+Trades!N349,B348)</f>
+        <v/>
+      </c>
+      <c r="C349" s="20">
+        <f>MIN(0,B349-MAX($B$2:B349))</f>
         <v/>
       </c>
     </row>
     <row r="350">
-      <c r="E350" s="4">
-        <f>IF(OR(Trades!M339="WIN",Trades!M339="LOSS"),E349+Trades!N339,E349)</f>
-        <v/>
-      </c>
-      <c r="F350" s="15">
-        <f>MIN(0,E350-MAX($E$13:E350))</f>
+      <c r="A350" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" s="4">
+        <f>IF(OR(Trades!M350="WIN",Trades!M350="LOSS"),B349+Trades!N350,B349)</f>
+        <v/>
+      </c>
+      <c r="C350" s="20">
+        <f>MIN(0,B350-MAX($B$2:B350))</f>
         <v/>
       </c>
     </row>
     <row r="351">
-      <c r="E351" s="4">
-        <f>IF(OR(Trades!M340="WIN",Trades!M340="LOSS"),E350+Trades!N340,E350)</f>
-        <v/>
-      </c>
-      <c r="F351" s="15">
-        <f>MIN(0,E351-MAX($E$13:E351))</f>
+      <c r="A351" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" s="4">
+        <f>IF(OR(Trades!M351="WIN",Trades!M351="LOSS"),B350+Trades!N351,B350)</f>
+        <v/>
+      </c>
+      <c r="C351" s="20">
+        <f>MIN(0,B351-MAX($B$2:B351))</f>
         <v/>
       </c>
     </row>
     <row r="352">
-      <c r="E352" s="4">
-        <f>IF(OR(Trades!M341="WIN",Trades!M341="LOSS"),E351+Trades!N341,E351)</f>
-        <v/>
-      </c>
-      <c r="F352" s="15">
-        <f>MIN(0,E352-MAX($E$13:E352))</f>
+      <c r="A352" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" s="4">
+        <f>IF(OR(Trades!M352="WIN",Trades!M352="LOSS"),B351+Trades!N352,B351)</f>
+        <v/>
+      </c>
+      <c r="C352" s="20">
+        <f>MIN(0,B352-MAX($B$2:B352))</f>
         <v/>
       </c>
     </row>
     <row r="353">
-      <c r="E353" s="4">
-        <f>IF(OR(Trades!M342="WIN",Trades!M342="LOSS"),E352+Trades!N342,E352)</f>
-        <v/>
-      </c>
-      <c r="F353" s="15">
-        <f>MIN(0,E353-MAX($E$13:E353))</f>
+      <c r="A353" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" s="4">
+        <f>IF(OR(Trades!M353="WIN",Trades!M353="LOSS"),B352+Trades!N353,B352)</f>
+        <v/>
+      </c>
+      <c r="C353" s="20">
+        <f>MIN(0,B353-MAX($B$2:B353))</f>
         <v/>
       </c>
     </row>
     <row r="354">
-      <c r="E354" s="4">
-        <f>IF(OR(Trades!M343="WIN",Trades!M343="LOSS"),E353+Trades!N343,E353)</f>
-        <v/>
-      </c>
-      <c r="F354" s="15">
-        <f>MIN(0,E354-MAX($E$13:E354))</f>
+      <c r="A354" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" s="4">
+        <f>IF(OR(Trades!M354="WIN",Trades!M354="LOSS"),B353+Trades!N354,B353)</f>
+        <v/>
+      </c>
+      <c r="C354" s="20">
+        <f>MIN(0,B354-MAX($B$2:B354))</f>
         <v/>
       </c>
     </row>
     <row r="355">
-      <c r="E355" s="4">
-        <f>IF(OR(Trades!M344="WIN",Trades!M344="LOSS"),E354+Trades!N344,E354)</f>
-        <v/>
-      </c>
-      <c r="F355" s="15">
-        <f>MIN(0,E355-MAX($E$13:E355))</f>
+      <c r="A355" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" s="4">
+        <f>IF(OR(Trades!M355="WIN",Trades!M355="LOSS"),B354+Trades!N355,B354)</f>
+        <v/>
+      </c>
+      <c r="C355" s="20">
+        <f>MIN(0,B355-MAX($B$2:B355))</f>
         <v/>
       </c>
     </row>
     <row r="356">
-      <c r="E356" s="4">
-        <f>IF(OR(Trades!M345="WIN",Trades!M345="LOSS"),E355+Trades!N345,E355)</f>
-        <v/>
-      </c>
-      <c r="F356" s="15">
-        <f>MIN(0,E356-MAX($E$13:E356))</f>
+      <c r="A356" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" s="4">
+        <f>IF(OR(Trades!M356="WIN",Trades!M356="LOSS"),B355+Trades!N356,B355)</f>
+        <v/>
+      </c>
+      <c r="C356" s="20">
+        <f>MIN(0,B356-MAX($B$2:B356))</f>
         <v/>
       </c>
     </row>
     <row r="357">
-      <c r="E357" s="4">
-        <f>IF(OR(Trades!M346="WIN",Trades!M346="LOSS"),E356+Trades!N346,E356)</f>
-        <v/>
-      </c>
-      <c r="F357" s="15">
-        <f>MIN(0,E357-MAX($E$13:E357))</f>
+      <c r="A357" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" s="4">
+        <f>IF(OR(Trades!M357="WIN",Trades!M357="LOSS"),B356+Trades!N357,B356)</f>
+        <v/>
+      </c>
+      <c r="C357" s="20">
+        <f>MIN(0,B357-MAX($B$2:B357))</f>
         <v/>
       </c>
     </row>
     <row r="358">
-      <c r="E358" s="4">
-        <f>IF(OR(Trades!M347="WIN",Trades!M347="LOSS"),E357+Trades!N347,E357)</f>
-        <v/>
-      </c>
-      <c r="F358" s="15">
-        <f>MIN(0,E358-MAX($E$13:E358))</f>
+      <c r="A358" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" s="4">
+        <f>IF(OR(Trades!M358="WIN",Trades!M358="LOSS"),B357+Trades!N358,B357)</f>
+        <v/>
+      </c>
+      <c r="C358" s="20">
+        <f>MIN(0,B358-MAX($B$2:B358))</f>
         <v/>
       </c>
     </row>
     <row r="359">
-      <c r="E359" s="4">
-        <f>IF(OR(Trades!M348="WIN",Trades!M348="LOSS"),E358+Trades!N348,E358)</f>
-        <v/>
-      </c>
-      <c r="F359" s="15">
-        <f>MIN(0,E359-MAX($E$13:E359))</f>
+      <c r="A359" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" s="4">
+        <f>IF(OR(Trades!M359="WIN",Trades!M359="LOSS"),B358+Trades!N359,B358)</f>
+        <v/>
+      </c>
+      <c r="C359" s="20">
+        <f>MIN(0,B359-MAX($B$2:B359))</f>
         <v/>
       </c>
     </row>
     <row r="360">
-      <c r="E360" s="4">
-        <f>IF(OR(Trades!M349="WIN",Trades!M349="LOSS"),E359+Trades!N349,E359)</f>
-        <v/>
-      </c>
-      <c r="F360" s="15">
-        <f>MIN(0,E360-MAX($E$13:E360))</f>
+      <c r="A360" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" s="4">
+        <f>IF(OR(Trades!M360="WIN",Trades!M360="LOSS"),B359+Trades!N360,B359)</f>
+        <v/>
+      </c>
+      <c r="C360" s="20">
+        <f>MIN(0,B360-MAX($B$2:B360))</f>
         <v/>
       </c>
     </row>
     <row r="361">
-      <c r="E361" s="4">
-        <f>IF(OR(Trades!M350="WIN",Trades!M350="LOSS"),E360+Trades!N350,E360)</f>
-        <v/>
-      </c>
-      <c r="F361" s="15">
-        <f>MIN(0,E361-MAX($E$13:E361))</f>
+      <c r="A361" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" s="4">
+        <f>IF(OR(Trades!M361="WIN",Trades!M361="LOSS"),B360+Trades!N361,B360)</f>
+        <v/>
+      </c>
+      <c r="C361" s="20">
+        <f>MIN(0,B361-MAX($B$2:B361))</f>
         <v/>
       </c>
     </row>
     <row r="362">
-      <c r="E362" s="4">
-        <f>IF(OR(Trades!M351="WIN",Trades!M351="LOSS"),E361+Trades!N351,E361)</f>
-        <v/>
-      </c>
-      <c r="F362" s="15">
-        <f>MIN(0,E362-MAX($E$13:E362))</f>
+      <c r="A362" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" s="4">
+        <f>IF(OR(Trades!M362="WIN",Trades!M362="LOSS"),B361+Trades!N362,B361)</f>
+        <v/>
+      </c>
+      <c r="C362" s="20">
+        <f>MIN(0,B362-MAX($B$2:B362))</f>
         <v/>
       </c>
     </row>
     <row r="363">
-      <c r="E363" s="4">
-        <f>IF(OR(Trades!M352="WIN",Trades!M352="LOSS"),E362+Trades!N352,E362)</f>
-        <v/>
-      </c>
-      <c r="F363" s="15">
-        <f>MIN(0,E363-MAX($E$13:E363))</f>
+      <c r="A363" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" s="4">
+        <f>IF(OR(Trades!M363="WIN",Trades!M363="LOSS"),B362+Trades!N363,B362)</f>
+        <v/>
+      </c>
+      <c r="C363" s="20">
+        <f>MIN(0,B363-MAX($B$2:B363))</f>
         <v/>
       </c>
     </row>
     <row r="364">
-      <c r="E364" s="4">
-        <f>IF(OR(Trades!M353="WIN",Trades!M353="LOSS"),E363+Trades!N353,E363)</f>
-        <v/>
-      </c>
-      <c r="F364" s="15">
-        <f>MIN(0,E364-MAX($E$13:E364))</f>
+      <c r="A364" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" s="4">
+        <f>IF(OR(Trades!M364="WIN",Trades!M364="LOSS"),B363+Trades!N364,B363)</f>
+        <v/>
+      </c>
+      <c r="C364" s="20">
+        <f>MIN(0,B364-MAX($B$2:B364))</f>
         <v/>
       </c>
     </row>
     <row r="365">
-      <c r="E365" s="4">
-        <f>IF(OR(Trades!M354="WIN",Trades!M354="LOSS"),E364+Trades!N354,E364)</f>
-        <v/>
-      </c>
-      <c r="F365" s="15">
-        <f>MIN(0,E365-MAX($E$13:E365))</f>
+      <c r="A365" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" s="4">
+        <f>IF(OR(Trades!M365="WIN",Trades!M365="LOSS"),B364+Trades!N365,B364)</f>
+        <v/>
+      </c>
+      <c r="C365" s="20">
+        <f>MIN(0,B365-MAX($B$2:B365))</f>
         <v/>
       </c>
     </row>
     <row r="366">
-      <c r="E366" s="4">
-        <f>IF(OR(Trades!M355="WIN",Trades!M355="LOSS"),E365+Trades!N355,E365)</f>
-        <v/>
-      </c>
-      <c r="F366" s="15">
-        <f>MIN(0,E366-MAX($E$13:E366))</f>
+      <c r="A366" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" s="4">
+        <f>IF(OR(Trades!M366="WIN",Trades!M366="LOSS"),B365+Trades!N366,B365)</f>
+        <v/>
+      </c>
+      <c r="C366" s="20">
+        <f>MIN(0,B366-MAX($B$2:B366))</f>
         <v/>
       </c>
     </row>
     <row r="367">
-      <c r="E367" s="4">
-        <f>IF(OR(Trades!M356="WIN",Trades!M356="LOSS"),E366+Trades!N356,E366)</f>
-        <v/>
-      </c>
-      <c r="F367" s="15">
-        <f>MIN(0,E367-MAX($E$13:E367))</f>
+      <c r="A367" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" s="4">
+        <f>IF(OR(Trades!M367="WIN",Trades!M367="LOSS"),B366+Trades!N367,B366)</f>
+        <v/>
+      </c>
+      <c r="C367" s="20">
+        <f>MIN(0,B367-MAX($B$2:B367))</f>
         <v/>
       </c>
     </row>
     <row r="368">
-      <c r="E368" s="4">
-        <f>IF(OR(Trades!M357="WIN",Trades!M357="LOSS"),E367+Trades!N357,E367)</f>
-        <v/>
-      </c>
-      <c r="F368" s="15">
-        <f>MIN(0,E368-MAX($E$13:E368))</f>
+      <c r="A368" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" s="4">
+        <f>IF(OR(Trades!M368="WIN",Trades!M368="LOSS"),B367+Trades!N368,B367)</f>
+        <v/>
+      </c>
+      <c r="C368" s="20">
+        <f>MIN(0,B368-MAX($B$2:B368))</f>
         <v/>
       </c>
     </row>
     <row r="369">
-      <c r="E369" s="4">
-        <f>IF(OR(Trades!M358="WIN",Trades!M358="LOSS"),E368+Trades!N358,E368)</f>
-        <v/>
-      </c>
-      <c r="F369" s="15">
-        <f>MIN(0,E369-MAX($E$13:E369))</f>
+      <c r="A369" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" s="4">
+        <f>IF(OR(Trades!M369="WIN",Trades!M369="LOSS"),B368+Trades!N369,B368)</f>
+        <v/>
+      </c>
+      <c r="C369" s="20">
+        <f>MIN(0,B369-MAX($B$2:B369))</f>
         <v/>
       </c>
     </row>
     <row r="370">
-      <c r="E370" s="4">
-        <f>IF(OR(Trades!M359="WIN",Trades!M359="LOSS"),E369+Trades!N359,E369)</f>
-        <v/>
-      </c>
-      <c r="F370" s="15">
-        <f>MIN(0,E370-MAX($E$13:E370))</f>
+      <c r="A370" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" s="4">
+        <f>IF(OR(Trades!M370="WIN",Trades!M370="LOSS"),B369+Trades!N370,B369)</f>
+        <v/>
+      </c>
+      <c r="C370" s="20">
+        <f>MIN(0,B370-MAX($B$2:B370))</f>
         <v/>
       </c>
     </row>
     <row r="371">
-      <c r="E371" s="4">
-        <f>IF(OR(Trades!M360="WIN",Trades!M360="LOSS"),E370+Trades!N360,E370)</f>
-        <v/>
-      </c>
-      <c r="F371" s="15">
-        <f>MIN(0,E371-MAX($E$13:E371))</f>
+      <c r="A371" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" s="4">
+        <f>IF(OR(Trades!M371="WIN",Trades!M371="LOSS"),B370+Trades!N371,B370)</f>
+        <v/>
+      </c>
+      <c r="C371" s="20">
+        <f>MIN(0,B371-MAX($B$2:B371))</f>
         <v/>
       </c>
     </row>
     <row r="372">
-      <c r="E372" s="4">
-        <f>IF(OR(Trades!M361="WIN",Trades!M361="LOSS"),E371+Trades!N361,E371)</f>
-        <v/>
-      </c>
-      <c r="F372" s="15">
-        <f>MIN(0,E372-MAX($E$13:E372))</f>
+      <c r="A372" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" s="4">
+        <f>IF(OR(Trades!M372="WIN",Trades!M372="LOSS"),B371+Trades!N372,B371)</f>
+        <v/>
+      </c>
+      <c r="C372" s="20">
+        <f>MIN(0,B372-MAX($B$2:B372))</f>
         <v/>
       </c>
     </row>
     <row r="373">
-      <c r="E373" s="4">
-        <f>IF(OR(Trades!M362="WIN",Trades!M362="LOSS"),E372+Trades!N362,E372)</f>
-        <v/>
-      </c>
-      <c r="F373" s="15">
-        <f>MIN(0,E373-MAX($E$13:E373))</f>
+      <c r="A373" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" s="4">
+        <f>IF(OR(Trades!M373="WIN",Trades!M373="LOSS"),B372+Trades!N373,B372)</f>
+        <v/>
+      </c>
+      <c r="C373" s="20">
+        <f>MIN(0,B373-MAX($B$2:B373))</f>
         <v/>
       </c>
     </row>
     <row r="374">
-      <c r="E374" s="4">
-        <f>IF(OR(Trades!M363="WIN",Trades!M363="LOSS"),E373+Trades!N363,E373)</f>
-        <v/>
-      </c>
-      <c r="F374" s="15">
-        <f>MIN(0,E374-MAX($E$13:E374))</f>
+      <c r="A374" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" s="4">
+        <f>IF(OR(Trades!M374="WIN",Trades!M374="LOSS"),B373+Trades!N374,B373)</f>
+        <v/>
+      </c>
+      <c r="C374" s="20">
+        <f>MIN(0,B374-MAX($B$2:B374))</f>
         <v/>
       </c>
     </row>
     <row r="375">
-      <c r="E375" s="4">
-        <f>IF(OR(Trades!M364="WIN",Trades!M364="LOSS"),E374+Trades!N364,E374)</f>
-        <v/>
-      </c>
-      <c r="F375" s="15">
-        <f>MIN(0,E375-MAX($E$13:E375))</f>
+      <c r="A375" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" s="4">
+        <f>IF(OR(Trades!M375="WIN",Trades!M375="LOSS"),B374+Trades!N375,B374)</f>
+        <v/>
+      </c>
+      <c r="C375" s="20">
+        <f>MIN(0,B375-MAX($B$2:B375))</f>
         <v/>
       </c>
     </row>
     <row r="376">
-      <c r="E376" s="4">
-        <f>IF(OR(Trades!M365="WIN",Trades!M365="LOSS"),E375+Trades!N365,E375)</f>
-        <v/>
-      </c>
-      <c r="F376" s="15">
-        <f>MIN(0,E376-MAX($E$13:E376))</f>
+      <c r="A376" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" s="4">
+        <f>IF(OR(Trades!M376="WIN",Trades!M376="LOSS"),B375+Trades!N376,B375)</f>
+        <v/>
+      </c>
+      <c r="C376" s="20">
+        <f>MIN(0,B376-MAX($B$2:B376))</f>
         <v/>
       </c>
     </row>
     <row r="377">
-      <c r="E377" s="4">
-        <f>IF(OR(Trades!M366="WIN",Trades!M366="LOSS"),E376+Trades!N366,E376)</f>
-        <v/>
-      </c>
-      <c r="F377" s="15">
-        <f>MIN(0,E377-MAX($E$13:E377))</f>
+      <c r="A377" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" s="4">
+        <f>IF(OR(Trades!M377="WIN",Trades!M377="LOSS"),B376+Trades!N377,B376)</f>
+        <v/>
+      </c>
+      <c r="C377" s="20">
+        <f>MIN(0,B377-MAX($B$2:B377))</f>
         <v/>
       </c>
     </row>
     <row r="378">
-      <c r="E378" s="4">
-        <f>IF(OR(Trades!M367="WIN",Trades!M367="LOSS"),E377+Trades!N367,E377)</f>
-        <v/>
-      </c>
-      <c r="F378" s="15">
-        <f>MIN(0,E378-MAX($E$13:E378))</f>
+      <c r="A378" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" s="4">
+        <f>IF(OR(Trades!M378="WIN",Trades!M378="LOSS"),B377+Trades!N378,B377)</f>
+        <v/>
+      </c>
+      <c r="C378" s="20">
+        <f>MIN(0,B378-MAX($B$2:B378))</f>
         <v/>
       </c>
     </row>
     <row r="379">
-      <c r="E379" s="4">
-        <f>IF(OR(Trades!M368="WIN",Trades!M368="LOSS"),E378+Trades!N368,E378)</f>
-        <v/>
-      </c>
-      <c r="F379" s="15">
-        <f>MIN(0,E379-MAX($E$13:E379))</f>
+      <c r="A379" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" s="4">
+        <f>IF(OR(Trades!M379="WIN",Trades!M379="LOSS"),B378+Trades!N379,B378)</f>
+        <v/>
+      </c>
+      <c r="C379" s="20">
+        <f>MIN(0,B379-MAX($B$2:B379))</f>
         <v/>
       </c>
     </row>
     <row r="380">
-      <c r="E380" s="4">
-        <f>IF(OR(Trades!M369="WIN",Trades!M369="LOSS"),E379+Trades!N369,E379)</f>
-        <v/>
-      </c>
-      <c r="F380" s="15">
-        <f>MIN(0,E380-MAX($E$13:E380))</f>
+      <c r="A380" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" s="4">
+        <f>IF(OR(Trades!M380="WIN",Trades!M380="LOSS"),B379+Trades!N380,B379)</f>
+        <v/>
+      </c>
+      <c r="C380" s="20">
+        <f>MIN(0,B380-MAX($B$2:B380))</f>
         <v/>
       </c>
     </row>
     <row r="381">
-      <c r="E381" s="4">
-        <f>IF(OR(Trades!M370="WIN",Trades!M370="LOSS"),E380+Trades!N370,E380)</f>
-        <v/>
-      </c>
-      <c r="F381" s="15">
-        <f>MIN(0,E381-MAX($E$13:E381))</f>
+      <c r="A381" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" s="4">
+        <f>IF(OR(Trades!M381="WIN",Trades!M381="LOSS"),B380+Trades!N381,B380)</f>
+        <v/>
+      </c>
+      <c r="C381" s="20">
+        <f>MIN(0,B381-MAX($B$2:B381))</f>
         <v/>
       </c>
     </row>
     <row r="382">
-      <c r="E382" s="4">
-        <f>IF(OR(Trades!M371="WIN",Trades!M371="LOSS"),E381+Trades!N371,E381)</f>
-        <v/>
-      </c>
-      <c r="F382" s="15">
-        <f>MIN(0,E382-MAX($E$13:E382))</f>
+      <c r="A382" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" s="4">
+        <f>IF(OR(Trades!M382="WIN",Trades!M382="LOSS"),B381+Trades!N382,B381)</f>
+        <v/>
+      </c>
+      <c r="C382" s="20">
+        <f>MIN(0,B382-MAX($B$2:B382))</f>
         <v/>
       </c>
     </row>
     <row r="383">
-      <c r="E383" s="4">
-        <f>IF(OR(Trades!M372="WIN",Trades!M372="LOSS"),E382+Trades!N372,E382)</f>
-        <v/>
-      </c>
-      <c r="F383" s="15">
-        <f>MIN(0,E383-MAX($E$13:E383))</f>
+      <c r="A383" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" s="4">
+        <f>IF(OR(Trades!M383="WIN",Trades!M383="LOSS"),B382+Trades!N383,B382)</f>
+        <v/>
+      </c>
+      <c r="C383" s="20">
+        <f>MIN(0,B383-MAX($B$2:B383))</f>
         <v/>
       </c>
     </row>
     <row r="384">
-      <c r="E384" s="4">
-        <f>IF(OR(Trades!M373="WIN",Trades!M373="LOSS"),E383+Trades!N373,E383)</f>
-        <v/>
-      </c>
-      <c r="F384" s="15">
-        <f>MIN(0,E384-MAX($E$13:E384))</f>
+      <c r="A384" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" s="4">
+        <f>IF(OR(Trades!M384="WIN",Trades!M384="LOSS"),B383+Trades!N384,B383)</f>
+        <v/>
+      </c>
+      <c r="C384" s="20">
+        <f>MIN(0,B384-MAX($B$2:B384))</f>
         <v/>
       </c>
     </row>
     <row r="385">
-      <c r="E385" s="4">
-        <f>IF(OR(Trades!M374="WIN",Trades!M374="LOSS"),E384+Trades!N374,E384)</f>
-        <v/>
-      </c>
-      <c r="F385" s="15">
-        <f>MIN(0,E385-MAX($E$13:E385))</f>
+      <c r="A385" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" s="4">
+        <f>IF(OR(Trades!M385="WIN",Trades!M385="LOSS"),B384+Trades!N385,B384)</f>
+        <v/>
+      </c>
+      <c r="C385" s="20">
+        <f>MIN(0,B385-MAX($B$2:B385))</f>
         <v/>
       </c>
     </row>
     <row r="386">
-      <c r="E386" s="4">
-        <f>IF(OR(Trades!M375="WIN",Trades!M375="LOSS"),E385+Trades!N375,E385)</f>
-        <v/>
-      </c>
-      <c r="F386" s="15">
-        <f>MIN(0,E386-MAX($E$13:E386))</f>
+      <c r="A386" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" s="4">
+        <f>IF(OR(Trades!M386="WIN",Trades!M386="LOSS"),B385+Trades!N386,B385)</f>
+        <v/>
+      </c>
+      <c r="C386" s="20">
+        <f>MIN(0,B386-MAX($B$2:B386))</f>
         <v/>
       </c>
     </row>
     <row r="387">
-      <c r="E387" s="4">
-        <f>IF(OR(Trades!M376="WIN",Trades!M376="LOSS"),E386+Trades!N376,E386)</f>
-        <v/>
-      </c>
-      <c r="F387" s="15">
-        <f>MIN(0,E387-MAX($E$13:E387))</f>
+      <c r="A387" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" s="4">
+        <f>IF(OR(Trades!M387="WIN",Trades!M387="LOSS"),B386+Trades!N387,B386)</f>
+        <v/>
+      </c>
+      <c r="C387" s="20">
+        <f>MIN(0,B387-MAX($B$2:B387))</f>
         <v/>
       </c>
     </row>
     <row r="388">
-      <c r="E388" s="4">
-        <f>IF(OR(Trades!M377="WIN",Trades!M377="LOSS"),E387+Trades!N377,E387)</f>
-        <v/>
-      </c>
-      <c r="F388" s="15">
-        <f>MIN(0,E388-MAX($E$13:E388))</f>
+      <c r="A388" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" s="4">
+        <f>IF(OR(Trades!M388="WIN",Trades!M388="LOSS"),B387+Trades!N388,B387)</f>
+        <v/>
+      </c>
+      <c r="C388" s="20">
+        <f>MIN(0,B388-MAX($B$2:B388))</f>
         <v/>
       </c>
     </row>
     <row r="389">
-      <c r="E389" s="4">
-        <f>IF(OR(Trades!M378="WIN",Trades!M378="LOSS"),E388+Trades!N378,E388)</f>
-        <v/>
-      </c>
-      <c r="F389" s="15">
-        <f>MIN(0,E389-MAX($E$13:E389))</f>
+      <c r="A389" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" s="4">
+        <f>IF(OR(Trades!M389="WIN",Trades!M389="LOSS"),B388+Trades!N389,B388)</f>
+        <v/>
+      </c>
+      <c r="C389" s="20">
+        <f>MIN(0,B389-MAX($B$2:B389))</f>
         <v/>
       </c>
     </row>
     <row r="390">
-      <c r="E390" s="4">
-        <f>IF(OR(Trades!M379="WIN",Trades!M379="LOSS"),E389+Trades!N379,E389)</f>
-        <v/>
-      </c>
-      <c r="F390" s="15">
-        <f>MIN(0,E390-MAX($E$13:E390))</f>
+      <c r="A390" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" s="4">
+        <f>IF(OR(Trades!M390="WIN",Trades!M390="LOSS"),B389+Trades!N390,B389)</f>
+        <v/>
+      </c>
+      <c r="C390" s="20">
+        <f>MIN(0,B390-MAX($B$2:B390))</f>
         <v/>
       </c>
     </row>
     <row r="391">
-      <c r="E391" s="4">
-        <f>IF(OR(Trades!M380="WIN",Trades!M380="LOSS"),E390+Trades!N380,E390)</f>
-        <v/>
-      </c>
-      <c r="F391" s="15">
-        <f>MIN(0,E391-MAX($E$13:E391))</f>
+      <c r="A391" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" s="4">
+        <f>IF(OR(Trades!M391="WIN",Trades!M391="LOSS"),B390+Trades!N391,B390)</f>
+        <v/>
+      </c>
+      <c r="C391" s="20">
+        <f>MIN(0,B391-MAX($B$2:B391))</f>
         <v/>
       </c>
     </row>
     <row r="392">
-      <c r="E392" s="4">
-        <f>IF(OR(Trades!M381="WIN",Trades!M381="LOSS"),E391+Trades!N381,E391)</f>
-        <v/>
-      </c>
-      <c r="F392" s="15">
-        <f>MIN(0,E392-MAX($E$13:E392))</f>
+      <c r="A392" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" s="4">
+        <f>IF(OR(Trades!M392="WIN",Trades!M392="LOSS"),B391+Trades!N392,B391)</f>
+        <v/>
+      </c>
+      <c r="C392" s="20">
+        <f>MIN(0,B392-MAX($B$2:B392))</f>
         <v/>
       </c>
     </row>
     <row r="393">
-      <c r="E393" s="4">
-        <f>IF(OR(Trades!M382="WIN",Trades!M382="LOSS"),E392+Trades!N382,E392)</f>
-        <v/>
-      </c>
-      <c r="F393" s="15">
-        <f>MIN(0,E393-MAX($E$13:E393))</f>
+      <c r="A393" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" s="4">
+        <f>IF(OR(Trades!M393="WIN",Trades!M393="LOSS"),B392+Trades!N393,B392)</f>
+        <v/>
+      </c>
+      <c r="C393" s="20">
+        <f>MIN(0,B393-MAX($B$2:B393))</f>
         <v/>
       </c>
     </row>
     <row r="394">
-      <c r="E394" s="4">
-        <f>IF(OR(Trades!M383="WIN",Trades!M383="LOSS"),E393+Trades!N383,E393)</f>
-        <v/>
-      </c>
-      <c r="F394" s="15">
-        <f>MIN(0,E394-MAX($E$13:E394))</f>
+      <c r="A394" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" s="4">
+        <f>IF(OR(Trades!M394="WIN",Trades!M394="LOSS"),B393+Trades!N394,B393)</f>
+        <v/>
+      </c>
+      <c r="C394" s="20">
+        <f>MIN(0,B394-MAX($B$2:B394))</f>
         <v/>
       </c>
     </row>
     <row r="395">
-      <c r="E395" s="4">
-        <f>IF(OR(Trades!M384="WIN",Trades!M384="LOSS"),E394+Trades!N384,E394)</f>
-        <v/>
-      </c>
-      <c r="F395" s="15">
-        <f>MIN(0,E395-MAX($E$13:E395))</f>
+      <c r="A395" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" s="4">
+        <f>IF(OR(Trades!M395="WIN",Trades!M395="LOSS"),B394+Trades!N395,B394)</f>
+        <v/>
+      </c>
+      <c r="C395" s="20">
+        <f>MIN(0,B395-MAX($B$2:B395))</f>
         <v/>
       </c>
     </row>
     <row r="396">
-      <c r="E396" s="4">
-        <f>IF(OR(Trades!M385="WIN",Trades!M385="LOSS"),E395+Trades!N385,E395)</f>
-        <v/>
-      </c>
-      <c r="F396" s="15">
-        <f>MIN(0,E396-MAX($E$13:E396))</f>
+      <c r="A396" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" s="4">
+        <f>IF(OR(Trades!M396="WIN",Trades!M396="LOSS"),B395+Trades!N396,B395)</f>
+        <v/>
+      </c>
+      <c r="C396" s="20">
+        <f>MIN(0,B396-MAX($B$2:B396))</f>
         <v/>
       </c>
     </row>
     <row r="397">
-      <c r="E397" s="4">
-        <f>IF(OR(Trades!M386="WIN",Trades!M386="LOSS"),E396+Trades!N386,E396)</f>
-        <v/>
-      </c>
-      <c r="F397" s="15">
-        <f>MIN(0,E397-MAX($E$13:E397))</f>
+      <c r="A397" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" s="4">
+        <f>IF(OR(Trades!M397="WIN",Trades!M397="LOSS"),B396+Trades!N397,B396)</f>
+        <v/>
+      </c>
+      <c r="C397" s="20">
+        <f>MIN(0,B397-MAX($B$2:B397))</f>
         <v/>
       </c>
     </row>
     <row r="398">
-      <c r="E398" s="4">
-        <f>IF(OR(Trades!M387="WIN",Trades!M387="LOSS"),E397+Trades!N387,E397)</f>
-        <v/>
-      </c>
-      <c r="F398" s="15">
-        <f>MIN(0,E398-MAX($E$13:E398))</f>
+      <c r="A398" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" s="4">
+        <f>IF(OR(Trades!M398="WIN",Trades!M398="LOSS"),B397+Trades!N398,B397)</f>
+        <v/>
+      </c>
+      <c r="C398" s="20">
+        <f>MIN(0,B398-MAX($B$2:B398))</f>
         <v/>
       </c>
     </row>
     <row r="399">
-      <c r="E399" s="4">
-        <f>IF(OR(Trades!M388="WIN",Trades!M388="LOSS"),E398+Trades!N388,E398)</f>
-        <v/>
-      </c>
-      <c r="F399" s="15">
-        <f>MIN(0,E399-MAX($E$13:E399))</f>
+      <c r="A399" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" s="4">
+        <f>IF(OR(Trades!M399="WIN",Trades!M399="LOSS"),B398+Trades!N399,B398)</f>
+        <v/>
+      </c>
+      <c r="C399" s="20">
+        <f>MIN(0,B399-MAX($B$2:B399))</f>
         <v/>
       </c>
     </row>
     <row r="400">
-      <c r="E400" s="4">
-        <f>IF(OR(Trades!M389="WIN",Trades!M389="LOSS"),E399+Trades!N389,E399)</f>
-        <v/>
-      </c>
-      <c r="F400" s="15">
-        <f>MIN(0,E400-MAX($E$13:E400))</f>
+      <c r="A400" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" s="4">
+        <f>IF(OR(Trades!M400="WIN",Trades!M400="LOSS"),B399+Trades!N400,B399)</f>
+        <v/>
+      </c>
+      <c r="C400" s="20">
+        <f>MIN(0,B400-MAX($B$2:B400))</f>
         <v/>
       </c>
     </row>
     <row r="401">
-      <c r="E401" s="4">
-        <f>IF(OR(Trades!M390="WIN",Trades!M390="LOSS"),E400+Trades!N390,E400)</f>
-        <v/>
-      </c>
-      <c r="F401" s="15">
-        <f>MIN(0,E401-MAX($E$13:E401))</f>
+      <c r="A401" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" s="4">
+        <f>IF(OR(Trades!M401="WIN",Trades!M401="LOSS"),B400+Trades!N401,B400)</f>
+        <v/>
+      </c>
+      <c r="C401" s="20">
+        <f>MIN(0,B401-MAX($B$2:B401))</f>
         <v/>
       </c>
     </row>
     <row r="402">
-      <c r="E402" s="4">
-        <f>IF(OR(Trades!M391="WIN",Trades!M391="LOSS"),E401+Trades!N391,E401)</f>
-        <v/>
-      </c>
-      <c r="F402" s="15">
-        <f>MIN(0,E402-MAX($E$13:E402))</f>
+      <c r="A402" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" s="4">
+        <f>IF(OR(Trades!M402="WIN",Trades!M402="LOSS"),B401+Trades!N402,B401)</f>
+        <v/>
+      </c>
+      <c r="C402" s="20">
+        <f>MIN(0,B402-MAX($B$2:B402))</f>
         <v/>
       </c>
     </row>
     <row r="403">
-      <c r="E403" s="4">
-        <f>IF(OR(Trades!M392="WIN",Trades!M392="LOSS"),E402+Trades!N392,E402)</f>
-        <v/>
-      </c>
-      <c r="F403" s="15">
-        <f>MIN(0,E403-MAX($E$13:E403))</f>
+      <c r="A403" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" s="4">
+        <f>IF(OR(Trades!M403="WIN",Trades!M403="LOSS"),B402+Trades!N403,B402)</f>
+        <v/>
+      </c>
+      <c r="C403" s="20">
+        <f>MIN(0,B403-MAX($B$2:B403))</f>
         <v/>
       </c>
     </row>
     <row r="404">
-      <c r="E404" s="4">
-        <f>IF(OR(Trades!M393="WIN",Trades!M393="LOSS"),E403+Trades!N393,E403)</f>
-        <v/>
-      </c>
-      <c r="F404" s="15">
-        <f>MIN(0,E404-MAX($E$13:E404))</f>
+      <c r="A404" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" s="4">
+        <f>IF(OR(Trades!M404="WIN",Trades!M404="LOSS"),B403+Trades!N404,B403)</f>
+        <v/>
+      </c>
+      <c r="C404" s="20">
+        <f>MIN(0,B404-MAX($B$2:B404))</f>
         <v/>
       </c>
     </row>
     <row r="405">
-      <c r="E405" s="4">
-        <f>IF(OR(Trades!M394="WIN",Trades!M394="LOSS"),E404+Trades!N394,E404)</f>
-        <v/>
-      </c>
-      <c r="F405" s="15">
-        <f>MIN(0,E405-MAX($E$13:E405))</f>
+      <c r="A405" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" s="4">
+        <f>IF(OR(Trades!M405="WIN",Trades!M405="LOSS"),B404+Trades!N405,B404)</f>
+        <v/>
+      </c>
+      <c r="C405" s="20">
+        <f>MIN(0,B405-MAX($B$2:B405))</f>
         <v/>
       </c>
     </row>
     <row r="406">
-      <c r="E406" s="4">
-        <f>IF(OR(Trades!M395="WIN",Trades!M395="LOSS"),E405+Trades!N395,E405)</f>
-        <v/>
-      </c>
-      <c r="F406" s="15">
-        <f>MIN(0,E406-MAX($E$13:E406))</f>
+      <c r="A406" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" s="4">
+        <f>IF(OR(Trades!M406="WIN",Trades!M406="LOSS"),B405+Trades!N406,B405)</f>
+        <v/>
+      </c>
+      <c r="C406" s="20">
+        <f>MIN(0,B406-MAX($B$2:B406))</f>
         <v/>
       </c>
     </row>
     <row r="407">
-      <c r="E407" s="4">
-        <f>IF(OR(Trades!M396="WIN",Trades!M396="LOSS"),E406+Trades!N396,E406)</f>
-        <v/>
-      </c>
-      <c r="F407" s="15">
-        <f>MIN(0,E407-MAX($E$13:E407))</f>
+      <c r="A407" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" s="4">
+        <f>IF(OR(Trades!M407="WIN",Trades!M407="LOSS"),B406+Trades!N407,B406)</f>
+        <v/>
+      </c>
+      <c r="C407" s="20">
+        <f>MIN(0,B407-MAX($B$2:B407))</f>
         <v/>
       </c>
     </row>
     <row r="408">
-      <c r="E408" s="4">
-        <f>IF(OR(Trades!M397="WIN",Trades!M397="LOSS"),E407+Trades!N397,E407)</f>
-        <v/>
-      </c>
-      <c r="F408" s="15">
-        <f>MIN(0,E408-MAX($E$13:E408))</f>
+      <c r="A408" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" s="4">
+        <f>IF(OR(Trades!M408="WIN",Trades!M408="LOSS"),B407+Trades!N408,B407)</f>
+        <v/>
+      </c>
+      <c r="C408" s="20">
+        <f>MIN(0,B408-MAX($B$2:B408))</f>
         <v/>
       </c>
     </row>
     <row r="409">
-      <c r="E409" s="4">
-        <f>IF(OR(Trades!M398="WIN",Trades!M398="LOSS"),E408+Trades!N398,E408)</f>
-        <v/>
-      </c>
-      <c r="F409" s="15">
-        <f>MIN(0,E409-MAX($E$13:E409))</f>
+      <c r="A409" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" s="4">
+        <f>IF(OR(Trades!M409="WIN",Trades!M409="LOSS"),B408+Trades!N409,B408)</f>
+        <v/>
+      </c>
+      <c r="C409" s="20">
+        <f>MIN(0,B409-MAX($B$2:B409))</f>
         <v/>
       </c>
     </row>
     <row r="410">
-      <c r="E410" s="4">
-        <f>IF(OR(Trades!M399="WIN",Trades!M399="LOSS"),E409+Trades!N399,E409)</f>
-        <v/>
-      </c>
-      <c r="F410" s="15">
-        <f>MIN(0,E410-MAX($E$13:E410))</f>
+      <c r="A410" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" s="4">
+        <f>IF(OR(Trades!M410="WIN",Trades!M410="LOSS"),B409+Trades!N410,B409)</f>
+        <v/>
+      </c>
+      <c r="C410" s="20">
+        <f>MIN(0,B410-MAX($B$2:B410))</f>
         <v/>
       </c>
     </row>
     <row r="411">
-      <c r="E411" s="4">
-        <f>IF(OR(Trades!M400="WIN",Trades!M400="LOSS"),E410+Trades!N400,E410)</f>
-        <v/>
-      </c>
-      <c r="F411" s="15">
-        <f>MIN(0,E411-MAX($E$13:E411))</f>
+      <c r="A411" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" s="4">
+        <f>IF(OR(Trades!M411="WIN",Trades!M411="LOSS"),B410+Trades!N411,B410)</f>
+        <v/>
+      </c>
+      <c r="C411" s="20">
+        <f>MIN(0,B411-MAX($B$2:B411))</f>
         <v/>
       </c>
     </row>
     <row r="412">
-      <c r="E412" s="4">
-        <f>IF(OR(Trades!M401="WIN",Trades!M401="LOSS"),E411+Trades!N401,E411)</f>
-        <v/>
-      </c>
-      <c r="F412" s="15">
-        <f>MIN(0,E412-MAX($E$13:E412))</f>
+      <c r="A412" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" s="4">
+        <f>IF(OR(Trades!M412="WIN",Trades!M412="LOSS"),B411+Trades!N412,B411)</f>
+        <v/>
+      </c>
+      <c r="C412" s="20">
+        <f>MIN(0,B412-MAX($B$2:B412))</f>
         <v/>
       </c>
     </row>
     <row r="413">
-      <c r="E413" s="4">
-        <f>IF(OR(Trades!M402="WIN",Trades!M402="LOSS"),E412+Trades!N402,E412)</f>
-        <v/>
-      </c>
-      <c r="F413" s="15">
-        <f>MIN(0,E413-MAX($E$13:E413))</f>
+      <c r="A413" t="n">
+        <v>412</v>
+      </c>
+      <c r="B413" s="4">
+        <f>IF(OR(Trades!M413="WIN",Trades!M413="LOSS"),B412+Trades!N413,B412)</f>
+        <v/>
+      </c>
+      <c r="C413" s="20">
+        <f>MIN(0,B413-MAX($B$2:B413))</f>
         <v/>
       </c>
     </row>
     <row r="414">
-      <c r="E414" s="4">
-        <f>IF(OR(Trades!M403="WIN",Trades!M403="LOSS"),E413+Trades!N403,E413)</f>
-        <v/>
-      </c>
-      <c r="F414" s="15">
-        <f>MIN(0,E414-MAX($E$13:E414))</f>
+      <c r="A414" t="n">
+        <v>413</v>
+      </c>
+      <c r="B414" s="4">
+        <f>IF(OR(Trades!M414="WIN",Trades!M414="LOSS"),B413+Trades!N414,B413)</f>
+        <v/>
+      </c>
+      <c r="C414" s="20">
+        <f>MIN(0,B414-MAX($B$2:B414))</f>
         <v/>
       </c>
     </row>
     <row r="415">
-      <c r="E415" s="4">
-        <f>IF(OR(Trades!M404="WIN",Trades!M404="LOSS"),E414+Trades!N404,E414)</f>
-        <v/>
-      </c>
-      <c r="F415" s="15">
-        <f>MIN(0,E415-MAX($E$13:E415))</f>
+      <c r="A415" t="n">
+        <v>414</v>
+      </c>
+      <c r="B415" s="4">
+        <f>IF(OR(Trades!M415="WIN",Trades!M415="LOSS"),B414+Trades!N415,B414)</f>
+        <v/>
+      </c>
+      <c r="C415" s="20">
+        <f>MIN(0,B415-MAX($B$2:B415))</f>
         <v/>
       </c>
     </row>
     <row r="416">
-      <c r="E416" s="4">
-        <f>IF(OR(Trades!M405="WIN",Trades!M405="LOSS"),E415+Trades!N405,E415)</f>
-        <v/>
-      </c>
-      <c r="F416" s="15">
-        <f>MIN(0,E416-MAX($E$13:E416))</f>
+      <c r="A416" t="n">
+        <v>415</v>
+      </c>
+      <c r="B416" s="4">
+        <f>IF(OR(Trades!M416="WIN",Trades!M416="LOSS"),B415+Trades!N416,B415)</f>
+        <v/>
+      </c>
+      <c r="C416" s="20">
+        <f>MIN(0,B416-MAX($B$2:B416))</f>
         <v/>
       </c>
     </row>
     <row r="417">
-      <c r="E417" s="4">
-        <f>IF(OR(Trades!M406="WIN",Trades!M406="LOSS"),E416+Trades!N406,E416)</f>
-        <v/>
-      </c>
-      <c r="F417" s="15">
-        <f>MIN(0,E417-MAX($E$13:E417))</f>
+      <c r="A417" t="n">
+        <v>416</v>
+      </c>
+      <c r="B417" s="4">
+        <f>IF(OR(Trades!M417="WIN",Trades!M417="LOSS"),B416+Trades!N417,B416)</f>
+        <v/>
+      </c>
+      <c r="C417" s="20">
+        <f>MIN(0,B417-MAX($B$2:B417))</f>
         <v/>
       </c>
     </row>
     <row r="418">
-      <c r="E418" s="4">
-        <f>IF(OR(Trades!M407="WIN",Trades!M407="LOSS"),E417+Trades!N407,E417)</f>
-        <v/>
-      </c>
-      <c r="F418" s="15">
-        <f>MIN(0,E418-MAX($E$13:E418))</f>
+      <c r="A418" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" s="4">
+        <f>IF(OR(Trades!M418="WIN",Trades!M418="LOSS"),B417+Trades!N418,B417)</f>
+        <v/>
+      </c>
+      <c r="C418" s="20">
+        <f>MIN(0,B418-MAX($B$2:B418))</f>
         <v/>
       </c>
     </row>
     <row r="419">
-      <c r="E419" s="4">
-        <f>IF(OR(Trades!M408="WIN",Trades!M408="LOSS"),E418+Trades!N408,E418)</f>
-        <v/>
-      </c>
-      <c r="F419" s="15">
-        <f>MIN(0,E419-MAX($E$13:E419))</f>
+      <c r="A419" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" s="4">
+        <f>IF(OR(Trades!M419="WIN",Trades!M419="LOSS"),B418+Trades!N419,B418)</f>
+        <v/>
+      </c>
+      <c r="C419" s="20">
+        <f>MIN(0,B419-MAX($B$2:B419))</f>
         <v/>
       </c>
     </row>
     <row r="420">
-      <c r="E420" s="4">
-        <f>IF(OR(Trades!M409="WIN",Trades!M409="LOSS"),E419+Trades!N409,E419)</f>
-        <v/>
-      </c>
-      <c r="F420" s="15">
-        <f>MIN(0,E420-MAX($E$13:E420))</f>
+      <c r="A420" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" s="4">
+        <f>IF(OR(Trades!M420="WIN",Trades!M420="LOSS"),B419+Trades!N420,B419)</f>
+        <v/>
+      </c>
+      <c r="C420" s="20">
+        <f>MIN(0,B420-MAX($B$2:B420))</f>
         <v/>
       </c>
     </row>
     <row r="421">
-      <c r="E421" s="4">
-        <f>IF(OR(Trades!M410="WIN",Trades!M410="LOSS"),E420+Trades!N410,E420)</f>
-        <v/>
-      </c>
-      <c r="F421" s="15">
-        <f>MIN(0,E421-MAX($E$13:E421))</f>
+      <c r="A421" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" s="4">
+        <f>IF(OR(Trades!M421="WIN",Trades!M421="LOSS"),B420+Trades!N421,B420)</f>
+        <v/>
+      </c>
+      <c r="C421" s="20">
+        <f>MIN(0,B421-MAX($B$2:B421))</f>
         <v/>
       </c>
     </row>
     <row r="422">
-      <c r="E422" s="4">
-        <f>IF(OR(Trades!M411="WIN",Trades!M411="LOSS"),E421+Trades!N411,E421)</f>
-        <v/>
-      </c>
-      <c r="F422" s="15">
-        <f>MIN(0,E422-MAX($E$13:E422))</f>
+      <c r="A422" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" s="4">
+        <f>IF(OR(Trades!M422="WIN",Trades!M422="LOSS"),B421+Trades!N422,B421)</f>
+        <v/>
+      </c>
+      <c r="C422" s="20">
+        <f>MIN(0,B422-MAX($B$2:B422))</f>
         <v/>
       </c>
     </row>
     <row r="423">
-      <c r="E423" s="4">
-        <f>IF(OR(Trades!M412="WIN",Trades!M412="LOSS"),E422+Trades!N412,E422)</f>
-        <v/>
-      </c>
-      <c r="F423" s="15">
-        <f>MIN(0,E423-MAX($E$13:E423))</f>
+      <c r="A423" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" s="4">
+        <f>IF(OR(Trades!M423="WIN",Trades!M423="LOSS"),B422+Trades!N423,B422)</f>
+        <v/>
+      </c>
+      <c r="C423" s="20">
+        <f>MIN(0,B423-MAX($B$2:B423))</f>
         <v/>
       </c>
     </row>
     <row r="424">
-      <c r="E424" s="4">
-        <f>IF(OR(Trades!M413="WIN",Trades!M413="LOSS"),E423+Trades!N413,E423)</f>
-        <v/>
-      </c>
-      <c r="F424" s="15">
-        <f>MIN(0,E424-MAX($E$13:E424))</f>
+      <c r="A424" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" s="4">
+        <f>IF(OR(Trades!M424="WIN",Trades!M424="LOSS"),B423+Trades!N424,B423)</f>
+        <v/>
+      </c>
+      <c r="C424" s="20">
+        <f>MIN(0,B424-MAX($B$2:B424))</f>
         <v/>
       </c>
     </row>
     <row r="425">
-      <c r="E425" s="4">
-        <f>IF(OR(Trades!M414="WIN",Trades!M414="LOSS"),E424+Trades!N414,E424)</f>
-        <v/>
-      </c>
-      <c r="F425" s="15">
-        <f>MIN(0,E425-MAX($E$13:E425))</f>
+      <c r="A425" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" s="4">
+        <f>IF(OR(Trades!M425="WIN",Trades!M425="LOSS"),B424+Trades!N425,B424)</f>
+        <v/>
+      </c>
+      <c r="C425" s="20">
+        <f>MIN(0,B425-MAX($B$2:B425))</f>
         <v/>
       </c>
     </row>
     <row r="426">
-      <c r="E426" s="4">
-        <f>IF(OR(Trades!M415="WIN",Trades!M415="LOSS"),E425+Trades!N415,E425)</f>
-        <v/>
-      </c>
-      <c r="F426" s="15">
-        <f>MIN(0,E426-MAX($E$13:E426))</f>
+      <c r="A426" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" s="4">
+        <f>IF(OR(Trades!M426="WIN",Trades!M426="LOSS"),B425+Trades!N426,B425)</f>
+        <v/>
+      </c>
+      <c r="C426" s="20">
+        <f>MIN(0,B426-MAX($B$2:B426))</f>
         <v/>
       </c>
     </row>
     <row r="427">
-      <c r="E427" s="4">
-        <f>IF(OR(Trades!M416="WIN",Trades!M416="LOSS"),E426+Trades!N416,E426)</f>
-        <v/>
-      </c>
-      <c r="F427" s="15">
-        <f>MIN(0,E427-MAX($E$13:E427))</f>
+      <c r="A427" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" s="4">
+        <f>IF(OR(Trades!M427="WIN",Trades!M427="LOSS"),B426+Trades!N427,B426)</f>
+        <v/>
+      </c>
+      <c r="C427" s="20">
+        <f>MIN(0,B427-MAX($B$2:B427))</f>
         <v/>
       </c>
     </row>
     <row r="428">
-      <c r="E428" s="4">
-        <f>IF(OR(Trades!M417="WIN",Trades!M417="LOSS"),E427+Trades!N417,E427)</f>
-        <v/>
-      </c>
-      <c r="F428" s="15">
-        <f>MIN(0,E428-MAX($E$13:E428))</f>
+      <c r="A428" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" s="4">
+        <f>IF(OR(Trades!M428="WIN",Trades!M428="LOSS"),B427+Trades!N428,B427)</f>
+        <v/>
+      </c>
+      <c r="C428" s="20">
+        <f>MIN(0,B428-MAX($B$2:B428))</f>
         <v/>
       </c>
     </row>
     <row r="429">
-      <c r="E429" s="4">
-        <f>IF(OR(Trades!M418="WIN",Trades!M418="LOSS"),E428+Trades!N418,E428)</f>
-        <v/>
-      </c>
-      <c r="F429" s="15">
-        <f>MIN(0,E429-MAX($E$13:E429))</f>
+      <c r="A429" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" s="4">
+        <f>IF(OR(Trades!M429="WIN",Trades!M429="LOSS"),B428+Trades!N429,B428)</f>
+        <v/>
+      </c>
+      <c r="C429" s="20">
+        <f>MIN(0,B429-MAX($B$2:B429))</f>
         <v/>
       </c>
     </row>
     <row r="430">
-      <c r="E430" s="4">
-        <f>IF(OR(Trades!M419="WIN",Trades!M419="LOSS"),E429+Trades!N419,E429)</f>
-        <v/>
-      </c>
-      <c r="F430" s="15">
-        <f>MIN(0,E430-MAX($E$13:E430))</f>
+      <c r="A430" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" s="4">
+        <f>IF(OR(Trades!M430="WIN",Trades!M430="LOSS"),B429+Trades!N430,B429)</f>
+        <v/>
+      </c>
+      <c r="C430" s="20">
+        <f>MIN(0,B430-MAX($B$2:B430))</f>
         <v/>
       </c>
     </row>
     <row r="431">
-      <c r="E431" s="4">
-        <f>IF(OR(Trades!M420="WIN",Trades!M420="LOSS"),E430+Trades!N420,E430)</f>
-        <v/>
-      </c>
-      <c r="F431" s="15">
-        <f>MIN(0,E431-MAX($E$13:E431))</f>
+      <c r="A431" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" s="4">
+        <f>IF(OR(Trades!M431="WIN",Trades!M431="LOSS"),B430+Trades!N431,B430)</f>
+        <v/>
+      </c>
+      <c r="C431" s="20">
+        <f>MIN(0,B431-MAX($B$2:B431))</f>
         <v/>
       </c>
     </row>
     <row r="432">
-      <c r="E432" s="4">
-        <f>IF(OR(Trades!M421="WIN",Trades!M421="LOSS"),E431+Trades!N421,E431)</f>
-        <v/>
-      </c>
-      <c r="F432" s="15">
-        <f>MIN(0,E432-MAX($E$13:E432))</f>
+      <c r="A432" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" s="4">
+        <f>IF(OR(Trades!M432="WIN",Trades!M432="LOSS"),B431+Trades!N432,B431)</f>
+        <v/>
+      </c>
+      <c r="C432" s="20">
+        <f>MIN(0,B432-MAX($B$2:B432))</f>
         <v/>
       </c>
     </row>
     <row r="433">
-      <c r="E433" s="4">
-        <f>IF(OR(Trades!M422="WIN",Trades!M422="LOSS"),E432+Trades!N422,E432)</f>
-        <v/>
-      </c>
-      <c r="F433" s="15">
-        <f>MIN(0,E433-MAX($E$13:E433))</f>
+      <c r="A433" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" s="4">
+        <f>IF(OR(Trades!M433="WIN",Trades!M433="LOSS"),B432+Trades!N433,B432)</f>
+        <v/>
+      </c>
+      <c r="C433" s="20">
+        <f>MIN(0,B433-MAX($B$2:B433))</f>
         <v/>
       </c>
     </row>
     <row r="434">
-      <c r="E434" s="4">
-        <f>IF(OR(Trades!M423="WIN",Trades!M423="LOSS"),E433+Trades!N423,E433)</f>
-        <v/>
-      </c>
-      <c r="F434" s="15">
-        <f>MIN(0,E434-MAX($E$13:E434))</f>
+      <c r="A434" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" s="4">
+        <f>IF(OR(Trades!M434="WIN",Trades!M434="LOSS"),B433+Trades!N434,B433)</f>
+        <v/>
+      </c>
+      <c r="C434" s="20">
+        <f>MIN(0,B434-MAX($B$2:B434))</f>
         <v/>
       </c>
     </row>
     <row r="435">
-      <c r="E435" s="4">
-        <f>IF(OR(Trades!M424="WIN",Trades!M424="LOSS"),E434+Trades!N424,E434)</f>
-        <v/>
-      </c>
-      <c r="F435" s="15">
-        <f>MIN(0,E435-MAX($E$13:E435))</f>
+      <c r="A435" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" s="4">
+        <f>IF(OR(Trades!M435="WIN",Trades!M435="LOSS"),B434+Trades!N435,B434)</f>
+        <v/>
+      </c>
+      <c r="C435" s="20">
+        <f>MIN(0,B435-MAX($B$2:B435))</f>
         <v/>
       </c>
     </row>
     <row r="436">
-      <c r="E436" s="4">
-        <f>IF(OR(Trades!M425="WIN",Trades!M425="LOSS"),E435+Trades!N425,E435)</f>
-        <v/>
-      </c>
-      <c r="F436" s="15">
-        <f>MIN(0,E436-MAX($E$13:E436))</f>
+      <c r="A436" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" s="4">
+        <f>IF(OR(Trades!M436="WIN",Trades!M436="LOSS"),B435+Trades!N436,B435)</f>
+        <v/>
+      </c>
+      <c r="C436" s="20">
+        <f>MIN(0,B436-MAX($B$2:B436))</f>
         <v/>
       </c>
     </row>
     <row r="437">
-      <c r="E437" s="4">
-        <f>IF(OR(Trades!M426="WIN",Trades!M426="LOSS"),E436+Trades!N426,E436)</f>
-        <v/>
-      </c>
-      <c r="F437" s="15">
-        <f>MIN(0,E437-MAX($E$13:E437))</f>
+      <c r="A437" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" s="4">
+        <f>IF(OR(Trades!M437="WIN",Trades!M437="LOSS"),B436+Trades!N437,B436)</f>
+        <v/>
+      </c>
+      <c r="C437" s="20">
+        <f>MIN(0,B437-MAX($B$2:B437))</f>
         <v/>
       </c>
     </row>
     <row r="438">
-      <c r="E438" s="4">
-        <f>IF(OR(Trades!M427="WIN",Trades!M427="LOSS"),E437+Trades!N427,E437)</f>
-        <v/>
-      </c>
-      <c r="F438" s="15">
-        <f>MIN(0,E438-MAX($E$13:E438))</f>
+      <c r="A438" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" s="4">
+        <f>IF(OR(Trades!M438="WIN",Trades!M438="LOSS"),B437+Trades!N438,B437)</f>
+        <v/>
+      </c>
+      <c r="C438" s="20">
+        <f>MIN(0,B438-MAX($B$2:B438))</f>
         <v/>
       </c>
     </row>
     <row r="439">
-      <c r="E439" s="4">
-        <f>IF(OR(Trades!M428="WIN",Trades!M428="LOSS"),E438+Trades!N428,E438)</f>
-        <v/>
-      </c>
-      <c r="F439" s="15">
-        <f>MIN(0,E439-MAX($E$13:E439))</f>
+      <c r="A439" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" s="4">
+        <f>IF(OR(Trades!M439="WIN",Trades!M439="LOSS"),B438+Trades!N439,B438)</f>
+        <v/>
+      </c>
+      <c r="C439" s="20">
+        <f>MIN(0,B439-MAX($B$2:B439))</f>
         <v/>
       </c>
     </row>
     <row r="440">
-      <c r="E440" s="4">
-        <f>IF(OR(Trades!M429="WIN",Trades!M429="LOSS"),E439+Trades!N429,E439)</f>
-        <v/>
-      </c>
-      <c r="F440" s="15">
-        <f>MIN(0,E440-MAX($E$13:E440))</f>
+      <c r="A440" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" s="4">
+        <f>IF(OR(Trades!M440="WIN",Trades!M440="LOSS"),B439+Trades!N440,B439)</f>
+        <v/>
+      </c>
+      <c r="C440" s="20">
+        <f>MIN(0,B440-MAX($B$2:B440))</f>
         <v/>
       </c>
     </row>
     <row r="441">
-      <c r="E441" s="4">
-        <f>IF(OR(Trades!M430="WIN",Trades!M430="LOSS"),E440+Trades!N430,E440)</f>
-        <v/>
-      </c>
-      <c r="F441" s="15">
-        <f>MIN(0,E441-MAX($E$13:E441))</f>
+      <c r="A441" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" s="4">
+        <f>IF(OR(Trades!M441="WIN",Trades!M441="LOSS"),B440+Trades!N441,B440)</f>
+        <v/>
+      </c>
+      <c r="C441" s="20">
+        <f>MIN(0,B441-MAX($B$2:B441))</f>
         <v/>
       </c>
     </row>
     <row r="442">
-      <c r="E442" s="4">
-        <f>IF(OR(Trades!M431="WIN",Trades!M431="LOSS"),E441+Trades!N431,E441)</f>
-        <v/>
-      </c>
-      <c r="F442" s="15">
-        <f>MIN(0,E442-MAX($E$13:E442))</f>
+      <c r="A442" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" s="4">
+        <f>IF(OR(Trades!M442="WIN",Trades!M442="LOSS"),B441+Trades!N442,B441)</f>
+        <v/>
+      </c>
+      <c r="C442" s="20">
+        <f>MIN(0,B442-MAX($B$2:B442))</f>
         <v/>
       </c>
     </row>
     <row r="443">
-      <c r="E443" s="4">
-        <f>IF(OR(Trades!M432="WIN",Trades!M432="LOSS"),E442+Trades!N432,E442)</f>
-        <v/>
-      </c>
-      <c r="F443" s="15">
-        <f>MIN(0,E443-MAX($E$13:E443))</f>
+      <c r="A443" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" s="4">
+        <f>IF(OR(Trades!M443="WIN",Trades!M443="LOSS"),B442+Trades!N443,B442)</f>
+        <v/>
+      </c>
+      <c r="C443" s="20">
+        <f>MIN(0,B443-MAX($B$2:B443))</f>
         <v/>
       </c>
     </row>
     <row r="444">
-      <c r="E444" s="4">
-        <f>IF(OR(Trades!M433="WIN",Trades!M433="LOSS"),E443+Trades!N433,E443)</f>
-        <v/>
-      </c>
-      <c r="F444" s="15">
-        <f>MIN(0,E444-MAX($E$13:E444))</f>
+      <c r="A444" t="n">
+        <v>443</v>
+      </c>
+      <c r="B444" s="4">
+        <f>IF(OR(Trades!M444="WIN",Trades!M444="LOSS"),B443+Trades!N444,B443)</f>
+        <v/>
+      </c>
+      <c r="C444" s="20">
+        <f>MIN(0,B444-MAX($B$2:B444))</f>
         <v/>
       </c>
     </row>
     <row r="445">
-      <c r="E445" s="4">
-        <f>IF(OR(Trades!M434="WIN",Trades!M434="LOSS"),E444+Trades!N434,E444)</f>
-        <v/>
-      </c>
-      <c r="F445" s="15">
-        <f>MIN(0,E445-MAX($E$13:E445))</f>
+      <c r="A445" t="n">
+        <v>444</v>
+      </c>
+      <c r="B445" s="4">
+        <f>IF(OR(Trades!M445="WIN",Trades!M445="LOSS"),B444+Trades!N445,B444)</f>
+        <v/>
+      </c>
+      <c r="C445" s="20">
+        <f>MIN(0,B445-MAX($B$2:B445))</f>
         <v/>
       </c>
     </row>
     <row r="446">
-      <c r="E446" s="4">
-        <f>IF(OR(Trades!M435="WIN",Trades!M435="LOSS"),E445+Trades!N435,E445)</f>
-        <v/>
-      </c>
-      <c r="F446" s="15">
-        <f>MIN(0,E446-MAX($E$13:E446))</f>
+      <c r="A446" t="n">
+        <v>445</v>
+      </c>
+      <c r="B446" s="4">
+        <f>IF(OR(Trades!M446="WIN",Trades!M446="LOSS"),B445+Trades!N446,B445)</f>
+        <v/>
+      </c>
+      <c r="C446" s="20">
+        <f>MIN(0,B446-MAX($B$2:B446))</f>
         <v/>
       </c>
     </row>
     <row r="447">
-      <c r="E447" s="4">
-        <f>IF(OR(Trades!M436="WIN",Trades!M436="LOSS"),E446+Trades!N436,E446)</f>
-        <v/>
-      </c>
-      <c r="F447" s="15">
-        <f>MIN(0,E447-MAX($E$13:E447))</f>
+      <c r="A447" t="n">
+        <v>446</v>
+      </c>
+      <c r="B447" s="4">
+        <f>IF(OR(Trades!M447="WIN",Trades!M447="LOSS"),B446+Trades!N447,B446)</f>
+        <v/>
+      </c>
+      <c r="C447" s="20">
+        <f>MIN(0,B447-MAX($B$2:B447))</f>
         <v/>
       </c>
     </row>
     <row r="448">
-      <c r="E448" s="4">
-        <f>IF(OR(Trades!M437="WIN",Trades!M437="LOSS"),E447+Trades!N437,E447)</f>
-        <v/>
-      </c>
-      <c r="F448" s="15">
-        <f>MIN(0,E448-MAX($E$13:E448))</f>
+      <c r="A448" t="n">
+        <v>447</v>
+      </c>
+      <c r="B448" s="4">
+        <f>IF(OR(Trades!M448="WIN",Trades!M448="LOSS"),B447+Trades!N448,B447)</f>
+        <v/>
+      </c>
+      <c r="C448" s="20">
+        <f>MIN(0,B448-MAX($B$2:B448))</f>
         <v/>
       </c>
     </row>
     <row r="449">
-      <c r="E449" s="4">
-        <f>IF(OR(Trades!M438="WIN",Trades!M438="LOSS"),E448+Trades!N438,E448)</f>
-        <v/>
-      </c>
-      <c r="F449" s="15">
-        <f>MIN(0,E449-MAX($E$13:E449))</f>
+      <c r="A449" t="n">
+        <v>448</v>
+      </c>
+      <c r="B449" s="4">
+        <f>IF(OR(Trades!M449="WIN",Trades!M449="LOSS"),B448+Trades!N449,B448)</f>
+        <v/>
+      </c>
+      <c r="C449" s="20">
+        <f>MIN(0,B449-MAX($B$2:B449))</f>
         <v/>
       </c>
     </row>
     <row r="450">
-      <c r="E450" s="4">
-        <f>IF(OR(Trades!M439="WIN",Trades!M439="LOSS"),E449+Trades!N439,E449)</f>
-        <v/>
-      </c>
-      <c r="F450" s="15">
-        <f>MIN(0,E450-MAX($E$13:E450))</f>
+      <c r="A450" t="n">
+        <v>449</v>
+      </c>
+      <c r="B450" s="4">
+        <f>IF(OR(Trades!M450="WIN",Trades!M450="LOSS"),B449+Trades!N450,B449)</f>
+        <v/>
+      </c>
+      <c r="C450" s="20">
+        <f>MIN(0,B450-MAX($B$2:B450))</f>
         <v/>
       </c>
     </row>
     <row r="451">
-      <c r="E451" s="4">
-        <f>IF(OR(Trades!M440="WIN",Trades!M440="LOSS"),E450+Trades!N440,E450)</f>
-        <v/>
-      </c>
-      <c r="F451" s="15">
-        <f>MIN(0,E451-MAX($E$13:E451))</f>
+      <c r="A451" t="n">
+        <v>450</v>
+      </c>
+      <c r="B451" s="4">
+        <f>IF(OR(Trades!M451="WIN",Trades!M451="LOSS"),B450+Trades!N451,B450)</f>
+        <v/>
+      </c>
+      <c r="C451" s="20">
+        <f>MIN(0,B451-MAX($B$2:B451))</f>
         <v/>
       </c>
     </row>
     <row r="452">
-      <c r="E452" s="4">
-        <f>IF(OR(Trades!M441="WIN",Trades!M441="LOSS"),E451+Trades!N441,E451)</f>
-        <v/>
-      </c>
-      <c r="F452" s="15">
-        <f>MIN(0,E452-MAX($E$13:E452))</f>
+      <c r="A452" t="n">
+        <v>451</v>
+      </c>
+      <c r="B452" s="4">
+        <f>IF(OR(Trades!M452="WIN",Trades!M452="LOSS"),B451+Trades!N452,B451)</f>
+        <v/>
+      </c>
+      <c r="C452" s="20">
+        <f>MIN(0,B452-MAX($B$2:B452))</f>
         <v/>
       </c>
     </row>
     <row r="453">
-      <c r="E453" s="4">
-        <f>IF(OR(Trades!M442="WIN",Trades!M442="LOSS"),E452+Trades!N442,E452)</f>
-        <v/>
-      </c>
-      <c r="F453" s="15">
-        <f>MIN(0,E453-MAX($E$13:E453))</f>
+      <c r="A453" t="n">
+        <v>452</v>
+      </c>
+      <c r="B453" s="4">
+        <f>IF(OR(Trades!M453="WIN",Trades!M453="LOSS"),B452+Trades!N453,B452)</f>
+        <v/>
+      </c>
+      <c r="C453" s="20">
+        <f>MIN(0,B453-MAX($B$2:B453))</f>
         <v/>
       </c>
     </row>
     <row r="454">
-      <c r="E454" s="4">
-        <f>IF(OR(Trades!M443="WIN",Trades!M443="LOSS"),E453+Trades!N443,E453)</f>
-        <v/>
-      </c>
-      <c r="F454" s="15">
-        <f>MIN(0,E454-MAX($E$13:E454))</f>
+      <c r="A454" t="n">
+        <v>453</v>
+      </c>
+      <c r="B454" s="4">
+        <f>IF(OR(Trades!M454="WIN",Trades!M454="LOSS"),B453+Trades!N454,B453)</f>
+        <v/>
+      </c>
+      <c r="C454" s="20">
+        <f>MIN(0,B454-MAX($B$2:B454))</f>
         <v/>
       </c>
     </row>
     <row r="455">
-      <c r="E455" s="4">
-        <f>IF(OR(Trades!M444="WIN",Trades!M444="LOSS"),E454+Trades!N444,E454)</f>
-        <v/>
-      </c>
-      <c r="F455" s="15">
-        <f>MIN(0,E455-MAX($E$13:E455))</f>
+      <c r="A455" t="n">
+        <v>454</v>
+      </c>
+      <c r="B455" s="4">
+        <f>IF(OR(Trades!M455="WIN",Trades!M455="LOSS"),B454+Trades!N455,B454)</f>
+        <v/>
+      </c>
+      <c r="C455" s="20">
+        <f>MIN(0,B455-MAX($B$2:B455))</f>
         <v/>
       </c>
     </row>
     <row r="456">
-      <c r="E456" s="4">
-        <f>IF(OR(Trades!M445="WIN",Trades!M445="LOSS"),E455+Trades!N445,E455)</f>
-        <v/>
-      </c>
-      <c r="F456" s="15">
-        <f>MIN(0,E456-MAX($E$13:E456))</f>
+      <c r="A456" t="n">
+        <v>455</v>
+      </c>
+      <c r="B456" s="4">
+        <f>IF(OR(Trades!M456="WIN",Trades!M456="LOSS"),B455+Trades!N456,B455)</f>
+        <v/>
+      </c>
+      <c r="C456" s="20">
+        <f>MIN(0,B456-MAX($B$2:B456))</f>
         <v/>
       </c>
     </row>
     <row r="457">
-      <c r="E457" s="4">
-        <f>IF(OR(Trades!M446="WIN",Trades!M446="LOSS"),E456+Trades!N446,E456)</f>
-        <v/>
-      </c>
-      <c r="F457" s="15">
-        <f>MIN(0,E457-MAX($E$13:E457))</f>
+      <c r="A457" t="n">
+        <v>456</v>
+      </c>
+      <c r="B457" s="4">
+        <f>IF(OR(Trades!M457="WIN",Trades!M457="LOSS"),B456+Trades!N457,B456)</f>
+        <v/>
+      </c>
+      <c r="C457" s="20">
+        <f>MIN(0,B457-MAX($B$2:B457))</f>
         <v/>
       </c>
     </row>
     <row r="458">
-      <c r="E458" s="4">
-        <f>IF(OR(Trades!M447="WIN",Trades!M447="LOSS"),E457+Trades!N447,E457)</f>
-        <v/>
-      </c>
-      <c r="F458" s="15">
-        <f>MIN(0,E458-MAX($E$13:E458))</f>
+      <c r="A458" t="n">
+        <v>457</v>
+      </c>
+      <c r="B458" s="4">
+        <f>IF(OR(Trades!M458="WIN",Trades!M458="LOSS"),B457+Trades!N458,B457)</f>
+        <v/>
+      </c>
+      <c r="C458" s="20">
+        <f>MIN(0,B458-MAX($B$2:B458))</f>
         <v/>
       </c>
     </row>
     <row r="459">
-      <c r="E459" s="4">
-        <f>IF(OR(Trades!M448="WIN",Trades!M448="LOSS"),E458+Trades!N448,E458)</f>
-        <v/>
-      </c>
-      <c r="F459" s="15">
-        <f>MIN(0,E459-MAX($E$13:E459))</f>
+      <c r="A459" t="n">
+        <v>458</v>
+      </c>
+      <c r="B459" s="4">
+        <f>IF(OR(Trades!M459="WIN",Trades!M459="LOSS"),B458+Trades!N459,B458)</f>
+        <v/>
+      </c>
+      <c r="C459" s="20">
+        <f>MIN(0,B459-MAX($B$2:B459))</f>
         <v/>
       </c>
     </row>
     <row r="460">
-      <c r="E460" s="4">
-        <f>IF(OR(Trades!M449="WIN",Trades!M449="LOSS"),E459+Trades!N449,E459)</f>
-        <v/>
-      </c>
-      <c r="F460" s="15">
-        <f>MIN(0,E460-MAX($E$13:E460))</f>
+      <c r="A460" t="n">
+        <v>459</v>
+      </c>
+      <c r="B460" s="4">
+        <f>IF(OR(Trades!M460="WIN",Trades!M460="LOSS"),B459+Trades!N460,B459)</f>
+        <v/>
+      </c>
+      <c r="C460" s="20">
+        <f>MIN(0,B460-MAX($B$2:B460))</f>
         <v/>
       </c>
     </row>
     <row r="461">
-      <c r="E461" s="4">
-        <f>IF(OR(Trades!M450="WIN",Trades!M450="LOSS"),E460+Trades!N450,E460)</f>
-        <v/>
-      </c>
-      <c r="F461" s="15">
-        <f>MIN(0,E461-MAX($E$13:E461))</f>
+      <c r="A461" t="n">
+        <v>460</v>
+      </c>
+      <c r="B461" s="4">
+        <f>IF(OR(Trades!M461="WIN",Trades!M461="LOSS"),B460+Trades!N461,B460)</f>
+        <v/>
+      </c>
+      <c r="C461" s="20">
+        <f>MIN(0,B461-MAX($B$2:B461))</f>
         <v/>
       </c>
     </row>
     <row r="462">
-      <c r="E462" s="4">
-        <f>IF(OR(Trades!M451="WIN",Trades!M451="LOSS"),E461+Trades!N451,E461)</f>
-        <v/>
-      </c>
-      <c r="F462" s="15">
-        <f>MIN(0,E462-MAX($E$13:E462))</f>
+      <c r="A462" t="n">
+        <v>461</v>
+      </c>
+      <c r="B462" s="4">
+        <f>IF(OR(Trades!M462="WIN",Trades!M462="LOSS"),B461+Trades!N462,B461)</f>
+        <v/>
+      </c>
+      <c r="C462" s="20">
+        <f>MIN(0,B462-MAX($B$2:B462))</f>
         <v/>
       </c>
     </row>
     <row r="463">
-      <c r="E463" s="4">
-        <f>IF(OR(Trades!M452="WIN",Trades!M452="LOSS"),E462+Trades!N452,E462)</f>
-        <v/>
-      </c>
-      <c r="F463" s="15">
-        <f>MIN(0,E463-MAX($E$13:E463))</f>
+      <c r="A463" t="n">
+        <v>462</v>
+      </c>
+      <c r="B463" s="4">
+        <f>IF(OR(Trades!M463="WIN",Trades!M463="LOSS"),B462+Trades!N463,B462)</f>
+        <v/>
+      </c>
+      <c r="C463" s="20">
+        <f>MIN(0,B463-MAX($B$2:B463))</f>
         <v/>
       </c>
     </row>
     <row r="464">
-      <c r="E464" s="4">
-        <f>IF(OR(Trades!M453="WIN",Trades!M453="LOSS"),E463+Trades!N453,E463)</f>
-        <v/>
-      </c>
-      <c r="F464" s="15">
-        <f>MIN(0,E464-MAX($E$13:E464))</f>
+      <c r="A464" t="n">
+        <v>463</v>
+      </c>
+      <c r="B464" s="4">
+        <f>IF(OR(Trades!M464="WIN",Trades!M464="LOSS"),B463+Trades!N464,B463)</f>
+        <v/>
+      </c>
+      <c r="C464" s="20">
+        <f>MIN(0,B464-MAX($B$2:B464))</f>
         <v/>
       </c>
     </row>
     <row r="465">
-      <c r="E465" s="4">
-        <f>IF(OR(Trades!M454="WIN",Trades!M454="LOSS"),E464+Trades!N454,E464)</f>
-        <v/>
-      </c>
-      <c r="F465" s="15">
-        <f>MIN(0,E465-MAX($E$13:E465))</f>
+      <c r="A465" t="n">
+        <v>464</v>
+      </c>
+      <c r="B465" s="4">
+        <f>IF(OR(Trades!M465="WIN",Trades!M465="LOSS"),B464+Trades!N465,B464)</f>
+        <v/>
+      </c>
+      <c r="C465" s="20">
+        <f>MIN(0,B465-MAX($B$2:B465))</f>
         <v/>
       </c>
     </row>
     <row r="466">
-      <c r="E466" s="4">
-        <f>IF(OR(Trades!M455="WIN",Trades!M455="LOSS"),E465+Trades!N455,E465)</f>
-        <v/>
-      </c>
-      <c r="F466" s="15">
-        <f>MIN(0,E466-MAX($E$13:E466))</f>
+      <c r="A466" t="n">
+        <v>465</v>
+      </c>
+      <c r="B466" s="4">
+        <f>IF(OR(Trades!M466="WIN",Trades!M466="LOSS"),B465+Trades!N466,B465)</f>
+        <v/>
+      </c>
+      <c r="C466" s="20">
+        <f>MIN(0,B466-MAX($B$2:B466))</f>
         <v/>
       </c>
     </row>
     <row r="467">
-      <c r="E467" s="4">
-        <f>IF(OR(Trades!M456="WIN",Trades!M456="LOSS"),E466+Trades!N456,E466)</f>
-        <v/>
-      </c>
-      <c r="F467" s="15">
-        <f>MIN(0,E467-MAX($E$13:E467))</f>
+      <c r="A467" t="n">
+        <v>466</v>
+      </c>
+      <c r="B467" s="4">
+        <f>IF(OR(Trades!M467="WIN",Trades!M467="LOSS"),B466+Trades!N467,B466)</f>
+        <v/>
+      </c>
+      <c r="C467" s="20">
+        <f>MIN(0,B467-MAX($B$2:B467))</f>
         <v/>
       </c>
     </row>
     <row r="468">
-      <c r="E468" s="4">
-        <f>IF(OR(Trades!M457="WIN",Trades!M457="LOSS"),E467+Trades!N457,E467)</f>
-        <v/>
-      </c>
-      <c r="F468" s="15">
-        <f>MIN(0,E468-MAX($E$13:E468))</f>
+      <c r="A468" t="n">
+        <v>467</v>
+      </c>
+      <c r="B468" s="4">
+        <f>IF(OR(Trades!M468="WIN",Trades!M468="LOSS"),B467+Trades!N468,B467)</f>
+        <v/>
+      </c>
+      <c r="C468" s="20">
+        <f>MIN(0,B468-MAX($B$2:B468))</f>
         <v/>
       </c>
     </row>
     <row r="469">
-      <c r="E469" s="4">
-        <f>IF(OR(Trades!M458="WIN",Trades!M458="LOSS"),E468+Trades!N458,E468)</f>
-        <v/>
-      </c>
-      <c r="F469" s="15">
-        <f>MIN(0,E469-MAX($E$13:E469))</f>
+      <c r="A469" t="n">
+        <v>468</v>
+      </c>
+      <c r="B469" s="4">
+        <f>IF(OR(Trades!M469="WIN",Trades!M469="LOSS"),B468+Trades!N469,B468)</f>
+        <v/>
+      </c>
+      <c r="C469" s="20">
+        <f>MIN(0,B469-MAX($B$2:B469))</f>
         <v/>
       </c>
     </row>
     <row r="470">
-      <c r="E470" s="4">
-        <f>IF(OR(Trades!M459="WIN",Trades!M459="LOSS"),E469+Trades!N459,E469)</f>
-        <v/>
-      </c>
-      <c r="F470" s="15">
-        <f>MIN(0,E470-MAX($E$13:E470))</f>
+      <c r="A470" t="n">
+        <v>469</v>
+      </c>
+      <c r="B470" s="4">
+        <f>IF(OR(Trades!M470="WIN",Trades!M470="LOSS"),B469+Trades!N470,B469)</f>
+        <v/>
+      </c>
+      <c r="C470" s="20">
+        <f>MIN(0,B470-MAX($B$2:B470))</f>
         <v/>
       </c>
     </row>
     <row r="471">
-      <c r="E471" s="4">
-        <f>IF(OR(Trades!M460="WIN",Trades!M460="LOSS"),E470+Trades!N460,E470)</f>
-        <v/>
-      </c>
-      <c r="F471" s="15">
-        <f>MIN(0,E471-MAX($E$13:E471))</f>
+      <c r="A471" t="n">
+        <v>470</v>
+      </c>
+      <c r="B471" s="4">
+        <f>IF(OR(Trades!M471="WIN",Trades!M471="LOSS"),B470+Trades!N471,B470)</f>
+        <v/>
+      </c>
+      <c r="C471" s="20">
+        <f>MIN(0,B471-MAX($B$2:B471))</f>
         <v/>
       </c>
     </row>
     <row r="472">
-      <c r="E472" s="4">
-        <f>IF(OR(Trades!M461="WIN",Trades!M461="LOSS"),E471+Trades!N461,E471)</f>
-        <v/>
-      </c>
-      <c r="F472" s="15">
-        <f>MIN(0,E472-MAX($E$13:E472))</f>
+      <c r="A472" t="n">
+        <v>471</v>
+      </c>
+      <c r="B472" s="4">
+        <f>IF(OR(Trades!M472="WIN",Trades!M472="LOSS"),B471+Trades!N472,B471)</f>
+        <v/>
+      </c>
+      <c r="C472" s="20">
+        <f>MIN(0,B472-MAX($B$2:B472))</f>
         <v/>
       </c>
     </row>
     <row r="473">
-      <c r="E473" s="4">
-        <f>IF(OR(Trades!M462="WIN",Trades!M462="LOSS"),E472+Trades!N462,E472)</f>
-        <v/>
-      </c>
-      <c r="F473" s="15">
-        <f>MIN(0,E473-MAX($E$13:E473))</f>
+      <c r="A473" t="n">
+        <v>472</v>
+      </c>
+      <c r="B473" s="4">
+        <f>IF(OR(Trades!M473="WIN",Trades!M473="LOSS"),B472+Trades!N473,B472)</f>
+        <v/>
+      </c>
+      <c r="C473" s="20">
+        <f>MIN(0,B473-MAX($B$2:B473))</f>
         <v/>
       </c>
     </row>
     <row r="474">
-      <c r="E474" s="4">
-        <f>IF(OR(Trades!M463="WIN",Trades!M463="LOSS"),E473+Trades!N463,E473)</f>
-        <v/>
-      </c>
-      <c r="F474" s="15">
-        <f>MIN(0,E474-MAX($E$13:E474))</f>
+      <c r="A474" t="n">
+        <v>473</v>
+      </c>
+      <c r="B474" s="4">
+        <f>IF(OR(Trades!M474="WIN",Trades!M474="LOSS"),B473+Trades!N474,B473)</f>
+        <v/>
+      </c>
+      <c r="C474" s="20">
+        <f>MIN(0,B474-MAX($B$2:B474))</f>
         <v/>
       </c>
     </row>
     <row r="475">
-      <c r="E475" s="4">
-        <f>IF(OR(Trades!M464="WIN",Trades!M464="LOSS"),E474+Trades!N464,E474)</f>
-        <v/>
-      </c>
-      <c r="F475" s="15">
-        <f>MIN(0,E475-MAX($E$13:E475))</f>
+      <c r="A475" t="n">
+        <v>474</v>
+      </c>
+      <c r="B475" s="4">
+        <f>IF(OR(Trades!M475="WIN",Trades!M475="LOSS"),B474+Trades!N475,B474)</f>
+        <v/>
+      </c>
+      <c r="C475" s="20">
+        <f>MIN(0,B475-MAX($B$2:B475))</f>
         <v/>
       </c>
     </row>
     <row r="476">
-      <c r="E476" s="4">
-        <f>IF(OR(Trades!M465="WIN",Trades!M465="LOSS"),E475+Trades!N465,E475)</f>
-        <v/>
-      </c>
-      <c r="F476" s="15">
-        <f>MIN(0,E476-MAX($E$13:E476))</f>
+      <c r="A476" t="n">
+        <v>475</v>
+      </c>
+      <c r="B476" s="4">
+        <f>IF(OR(Trades!M476="WIN",Trades!M476="LOSS"),B475+Trades!N476,B475)</f>
+        <v/>
+      </c>
+      <c r="C476" s="20">
+        <f>MIN(0,B476-MAX($B$2:B476))</f>
         <v/>
       </c>
     </row>
     <row r="477">
-      <c r="E477" s="4">
-        <f>IF(OR(Trades!M466="WIN",Trades!M466="LOSS"),E476+Trades!N466,E476)</f>
-        <v/>
-      </c>
-      <c r="F477" s="15">
-        <f>MIN(0,E477-MAX($E$13:E477))</f>
+      <c r="A477" t="n">
+        <v>476</v>
+      </c>
+      <c r="B477" s="4">
+        <f>IF(OR(Trades!M477="WIN",Trades!M477="LOSS"),B476+Trades!N477,B476)</f>
+        <v/>
+      </c>
+      <c r="C477" s="20">
+        <f>MIN(0,B477-MAX($B$2:B477))</f>
         <v/>
       </c>
     </row>
     <row r="478">
-      <c r="E478" s="4">
-        <f>IF(OR(Trades!M467="WIN",Trades!M467="LOSS"),E477+Trades!N467,E477)</f>
-        <v/>
-      </c>
-      <c r="F478" s="15">
-        <f>MIN(0,E478-MAX($E$13:E478))</f>
+      <c r="A478" t="n">
+        <v>477</v>
+      </c>
+      <c r="B478" s="4">
+        <f>IF(OR(Trades!M478="WIN",Trades!M478="LOSS"),B477+Trades!N478,B477)</f>
+        <v/>
+      </c>
+      <c r="C478" s="20">
+        <f>MIN(0,B478-MAX($B$2:B478))</f>
         <v/>
       </c>
     </row>
     <row r="479">
-      <c r="E479" s="4">
-        <f>IF(OR(Trades!M468="WIN",Trades!M468="LOSS"),E478+Trades!N468,E478)</f>
-        <v/>
-      </c>
-      <c r="F479" s="15">
-        <f>MIN(0,E479-MAX($E$13:E479))</f>
+      <c r="A479" t="n">
+        <v>478</v>
+      </c>
+      <c r="B479" s="4">
+        <f>IF(OR(Trades!M479="WIN",Trades!M479="LOSS"),B478+Trades!N479,B478)</f>
+        <v/>
+      </c>
+      <c r="C479" s="20">
+        <f>MIN(0,B479-MAX($B$2:B479))</f>
         <v/>
       </c>
     </row>
     <row r="480">
-      <c r="E480" s="4">
-        <f>IF(OR(Trades!M469="WIN",Trades!M469="LOSS"),E479+Trades!N469,E479)</f>
-        <v/>
-      </c>
-      <c r="F480" s="15">
-        <f>MIN(0,E480-MAX($E$13:E480))</f>
+      <c r="A480" t="n">
+        <v>479</v>
+      </c>
+      <c r="B480" s="4">
+        <f>IF(OR(Trades!M480="WIN",Trades!M480="LOSS"),B479+Trades!N480,B479)</f>
+        <v/>
+      </c>
+      <c r="C480" s="20">
+        <f>MIN(0,B480-MAX($B$2:B480))</f>
         <v/>
       </c>
     </row>
     <row r="481">
-      <c r="E481" s="4">
-        <f>IF(OR(Trades!M470="WIN",Trades!M470="LOSS"),E480+Trades!N470,E480)</f>
-        <v/>
-      </c>
-      <c r="F481" s="15">
-        <f>MIN(0,E481-MAX($E$13:E481))</f>
+      <c r="A481" t="n">
+        <v>480</v>
+      </c>
+      <c r="B481" s="4">
+        <f>IF(OR(Trades!M481="WIN",Trades!M481="LOSS"),B480+Trades!N481,B480)</f>
+        <v/>
+      </c>
+      <c r="C481" s="20">
+        <f>MIN(0,B481-MAX($B$2:B481))</f>
         <v/>
       </c>
     </row>
     <row r="482">
-      <c r="E482" s="4">
-        <f>IF(OR(Trades!M471="WIN",Trades!M471="LOSS"),E481+Trades!N471,E481)</f>
-        <v/>
-      </c>
-      <c r="F482" s="15">
-        <f>MIN(0,E482-MAX($E$13:E482))</f>
+      <c r="A482" t="n">
+        <v>481</v>
+      </c>
+      <c r="B482" s="4">
+        <f>IF(OR(Trades!M482="WIN",Trades!M482="LOSS"),B481+Trades!N482,B481)</f>
+        <v/>
+      </c>
+      <c r="C482" s="20">
+        <f>MIN(0,B482-MAX($B$2:B482))</f>
         <v/>
       </c>
     </row>
     <row r="483">
-      <c r="E483" s="4">
-        <f>IF(OR(Trades!M472="WIN",Trades!M472="LOSS"),E482+Trades!N472,E482)</f>
-        <v/>
-      </c>
-      <c r="F483" s="15">
-        <f>MIN(0,E483-MAX($E$13:E483))</f>
+      <c r="A483" t="n">
+        <v>482</v>
+      </c>
+      <c r="B483" s="4">
+        <f>IF(OR(Trades!M483="WIN",Trades!M483="LOSS"),B482+Trades!N483,B482)</f>
+        <v/>
+      </c>
+      <c r="C483" s="20">
+        <f>MIN(0,B483-MAX($B$2:B483))</f>
         <v/>
       </c>
     </row>
     <row r="484">
-      <c r="E484" s="4">
-        <f>IF(OR(Trades!M473="WIN",Trades!M473="LOSS"),E483+Trades!N473,E483)</f>
-        <v/>
-      </c>
-      <c r="F484" s="15">
-        <f>MIN(0,E484-MAX($E$13:E484))</f>
+      <c r="A484" t="n">
+        <v>483</v>
+      </c>
+      <c r="B484" s="4">
+        <f>IF(OR(Trades!M484="WIN",Trades!M484="LOSS"),B483+Trades!N484,B483)</f>
+        <v/>
+      </c>
+      <c r="C484" s="20">
+        <f>MIN(0,B484-MAX($B$2:B484))</f>
         <v/>
       </c>
     </row>
     <row r="485">
-      <c r="E485" s="4">
-        <f>IF(OR(Trades!M474="WIN",Trades!M474="LOSS"),E484+Trades!N474,E484)</f>
-        <v/>
-      </c>
-      <c r="F485" s="15">
-        <f>MIN(0,E485-MAX($E$13:E485))</f>
+      <c r="A485" t="n">
+        <v>484</v>
+      </c>
+      <c r="B485" s="4">
+        <f>IF(OR(Trades!M485="WIN",Trades!M485="LOSS"),B484+Trades!N485,B484)</f>
+        <v/>
+      </c>
+      <c r="C485" s="20">
+        <f>MIN(0,B485-MAX($B$2:B485))</f>
         <v/>
       </c>
     </row>
     <row r="486">
-      <c r="E486" s="4">
-        <f>IF(OR(Trades!M475="WIN",Trades!M475="LOSS"),E485+Trades!N475,E485)</f>
-        <v/>
-      </c>
-      <c r="F486" s="15">
-        <f>MIN(0,E486-MAX($E$13:E486))</f>
+      <c r="A486" t="n">
+        <v>485</v>
+      </c>
+      <c r="B486" s="4">
+        <f>IF(OR(Trades!M486="WIN",Trades!M486="LOSS"),B485+Trades!N486,B485)</f>
+        <v/>
+      </c>
+      <c r="C486" s="20">
+        <f>MIN(0,B486-MAX($B$2:B486))</f>
         <v/>
       </c>
     </row>
     <row r="487">
-      <c r="E487" s="4">
-        <f>IF(OR(Trades!M476="WIN",Trades!M476="LOSS"),E486+Trades!N476,E486)</f>
-        <v/>
-      </c>
-      <c r="F487" s="15">
-        <f>MIN(0,E487-MAX($E$13:E487))</f>
+      <c r="A487" t="n">
+        <v>486</v>
+      </c>
+      <c r="B487" s="4">
+        <f>IF(OR(Trades!M487="WIN",Trades!M487="LOSS"),B486+Trades!N487,B486)</f>
+        <v/>
+      </c>
+      <c r="C487" s="20">
+        <f>MIN(0,B487-MAX($B$2:B487))</f>
         <v/>
       </c>
     </row>
     <row r="488">
-      <c r="E488" s="4">
-        <f>IF(OR(Trades!M477="WIN",Trades!M477="LOSS"),E487+Trades!N477,E487)</f>
-        <v/>
-      </c>
-      <c r="F488" s="15">
-        <f>MIN(0,E488-MAX($E$13:E488))</f>
+      <c r="A488" t="n">
+        <v>487</v>
+      </c>
+      <c r="B488" s="4">
+        <f>IF(OR(Trades!M488="WIN",Trades!M488="LOSS"),B487+Trades!N488,B487)</f>
+        <v/>
+      </c>
+      <c r="C488" s="20">
+        <f>MIN(0,B488-MAX($B$2:B488))</f>
         <v/>
       </c>
     </row>
     <row r="489">
-      <c r="E489" s="4">
-        <f>IF(OR(Trades!M478="WIN",Trades!M478="LOSS"),E488+Trades!N478,E488)</f>
-        <v/>
-      </c>
-      <c r="F489" s="15">
-        <f>MIN(0,E489-MAX($E$13:E489))</f>
+      <c r="A489" t="n">
+        <v>488</v>
+      </c>
+      <c r="B489" s="4">
+        <f>IF(OR(Trades!M489="WIN",Trades!M489="LOSS"),B488+Trades!N489,B488)</f>
+        <v/>
+      </c>
+      <c r="C489" s="20">
+        <f>MIN(0,B489-MAX($B$2:B489))</f>
         <v/>
       </c>
     </row>
     <row r="490">
-      <c r="E490" s="4">
-        <f>IF(OR(Trades!M479="WIN",Trades!M479="LOSS"),E489+Trades!N479,E489)</f>
-        <v/>
-      </c>
-      <c r="F490" s="15">
-        <f>MIN(0,E490-MAX($E$13:E490))</f>
+      <c r="A490" t="n">
+        <v>489</v>
+      </c>
+      <c r="B490" s="4">
+        <f>IF(OR(Trades!M490="WIN",Trades!M490="LOSS"),B489+Trades!N490,B489)</f>
+        <v/>
+      </c>
+      <c r="C490" s="20">
+        <f>MIN(0,B490-MAX($B$2:B490))</f>
         <v/>
       </c>
     </row>
     <row r="491">
-      <c r="E491" s="4">
-        <f>IF(OR(Trades!M480="WIN",Trades!M480="LOSS"),E490+Trades!N480,E490)</f>
-        <v/>
-      </c>
-      <c r="F491" s="15">
-        <f>MIN(0,E491-MAX($E$13:E491))</f>
+      <c r="A491" t="n">
+        <v>490</v>
+      </c>
+      <c r="B491" s="4">
+        <f>IF(OR(Trades!M491="WIN",Trades!M491="LOSS"),B490+Trades!N491,B490)</f>
+        <v/>
+      </c>
+      <c r="C491" s="20">
+        <f>MIN(0,B491-MAX($B$2:B491))</f>
         <v/>
       </c>
     </row>
     <row r="492">
-      <c r="E492" s="4">
-        <f>IF(OR(Trades!M481="WIN",Trades!M481="LOSS"),E491+Trades!N481,E491)</f>
-        <v/>
-      </c>
-      <c r="F492" s="15">
-        <f>MIN(0,E492-MAX($E$13:E492))</f>
+      <c r="A492" t="n">
+        <v>491</v>
+      </c>
+      <c r="B492" s="4">
+        <f>IF(OR(Trades!M492="WIN",Trades!M492="LOSS"),B491+Trades!N492,B491)</f>
+        <v/>
+      </c>
+      <c r="C492" s="20">
+        <f>MIN(0,B492-MAX($B$2:B492))</f>
         <v/>
       </c>
     </row>
     <row r="493">
-      <c r="E493" s="4">
-        <f>IF(OR(Trades!M482="WIN",Trades!M482="LOSS"),E492+Trades!N482,E492)</f>
-        <v/>
-      </c>
-      <c r="F493" s="15">
-        <f>MIN(0,E493-MAX($E$13:E493))</f>
+      <c r="A493" t="n">
+        <v>492</v>
+      </c>
+      <c r="B493" s="4">
+        <f>IF(OR(Trades!M493="WIN",Trades!M493="LOSS"),B492+Trades!N493,B492)</f>
+        <v/>
+      </c>
+      <c r="C493" s="20">
+        <f>MIN(0,B493-MAX($B$2:B493))</f>
         <v/>
       </c>
     </row>
     <row r="494">
-      <c r="E494" s="4">
-        <f>IF(OR(Trades!M483="WIN",Trades!M483="LOSS"),E493+Trades!N483,E493)</f>
-        <v/>
-      </c>
-      <c r="F494" s="15">
-        <f>MIN(0,E494-MAX($E$13:E494))</f>
+      <c r="A494" t="n">
+        <v>493</v>
+      </c>
+      <c r="B494" s="4">
+        <f>IF(OR(Trades!M494="WIN",Trades!M494="LOSS"),B493+Trades!N494,B493)</f>
+        <v/>
+      </c>
+      <c r="C494" s="20">
+        <f>MIN(0,B494-MAX($B$2:B494))</f>
         <v/>
       </c>
     </row>
     <row r="495">
-      <c r="E495" s="4">
-        <f>IF(OR(Trades!M484="WIN",Trades!M484="LOSS"),E494+Trades!N484,E494)</f>
-        <v/>
-      </c>
-      <c r="F495" s="15">
-        <f>MIN(0,E495-MAX($E$13:E495))</f>
+      <c r="A495" t="n">
+        <v>494</v>
+      </c>
+      <c r="B495" s="4">
+        <f>IF(OR(Trades!M495="WIN",Trades!M495="LOSS"),B494+Trades!N495,B494)</f>
+        <v/>
+      </c>
+      <c r="C495" s="20">
+        <f>MIN(0,B495-MAX($B$2:B495))</f>
         <v/>
       </c>
     </row>
     <row r="496">
-      <c r="E496" s="4">
-        <f>IF(OR(Trades!M485="WIN",Trades!M485="LOSS"),E495+Trades!N485,E495)</f>
-        <v/>
-      </c>
-      <c r="F496" s="15">
-        <f>MIN(0,E496-MAX($E$13:E496))</f>
+      <c r="A496" t="n">
+        <v>495</v>
+      </c>
+      <c r="B496" s="4">
+        <f>IF(OR(Trades!M496="WIN",Trades!M496="LOSS"),B495+Trades!N496,B495)</f>
+        <v/>
+      </c>
+      <c r="C496" s="20">
+        <f>MIN(0,B496-MAX($B$2:B496))</f>
         <v/>
       </c>
     </row>
     <row r="497">
-      <c r="E497" s="4">
-        <f>IF(OR(Trades!M486="WIN",Trades!M486="LOSS"),E496+Trades!N486,E496)</f>
-        <v/>
-      </c>
-      <c r="F497" s="15">
-        <f>MIN(0,E497-MAX($E$13:E497))</f>
+      <c r="A497" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" s="4">
+        <f>IF(OR(Trades!M497="WIN",Trades!M497="LOSS"),B496+Trades!N497,B496)</f>
+        <v/>
+      </c>
+      <c r="C497" s="20">
+        <f>MIN(0,B497-MAX($B$2:B497))</f>
         <v/>
       </c>
     </row>
     <row r="498">
-      <c r="E498" s="4">
-        <f>IF(OR(Trades!M487="WIN",Trades!M487="LOSS"),E497+Trades!N487,E497)</f>
-        <v/>
-      </c>
-      <c r="F498" s="15">
-        <f>MIN(0,E498-MAX($E$13:E498))</f>
+      <c r="A498" t="n">
+        <v>497</v>
+      </c>
+      <c r="B498" s="4">
+        <f>IF(OR(Trades!M498="WIN",Trades!M498="LOSS"),B497+Trades!N498,B497)</f>
+        <v/>
+      </c>
+      <c r="C498" s="20">
+        <f>MIN(0,B498-MAX($B$2:B498))</f>
         <v/>
       </c>
     </row>
     <row r="499">
-      <c r="E499" s="4">
-        <f>IF(OR(Trades!M488="WIN",Trades!M488="LOSS"),E498+Trades!N488,E498)</f>
-        <v/>
-      </c>
-      <c r="F499" s="15">
-        <f>MIN(0,E499-MAX($E$13:E499))</f>
+      <c r="A499" t="n">
+        <v>498</v>
+      </c>
+      <c r="B499" s="4">
+        <f>IF(OR(Trades!M499="WIN",Trades!M499="LOSS"),B498+Trades!N499,B498)</f>
+        <v/>
+      </c>
+      <c r="C499" s="20">
+        <f>MIN(0,B499-MAX($B$2:B499))</f>
         <v/>
       </c>
     </row>
     <row r="500">
-      <c r="E500" s="4">
-        <f>IF(OR(Trades!M489="WIN",Trades!M489="LOSS"),E499+Trades!N489,E499)</f>
-        <v/>
-      </c>
-      <c r="F500" s="15">
-        <f>MIN(0,E500-MAX($E$13:E500))</f>
+      <c r="A500" t="n">
+        <v>499</v>
+      </c>
+      <c r="B500" s="4">
+        <f>IF(OR(Trades!M500="WIN",Trades!M500="LOSS"),B499+Trades!N500,B499)</f>
+        <v/>
+      </c>
+      <c r="C500" s="20">
+        <f>MIN(0,B500-MAX($B$2:B500))</f>
         <v/>
       </c>
     </row>
     <row r="501">
-      <c r="E501" s="4">
-        <f>IF(OR(Trades!M490="WIN",Trades!M490="LOSS"),E500+Trades!N490,E500)</f>
-        <v/>
-      </c>
-      <c r="F501" s="15">
-        <f>MIN(0,E501-MAX($E$13:E501))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="502">
-      <c r="E502" s="4">
-        <f>IF(OR(Trades!M491="WIN",Trades!M491="LOSS"),E501+Trades!N491,E501)</f>
-        <v/>
-      </c>
-      <c r="F502" s="15">
-        <f>MIN(0,E502-MAX($E$13:E502))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="503">
-      <c r="E503" s="4">
-        <f>IF(OR(Trades!M492="WIN",Trades!M492="LOSS"),E502+Trades!N492,E502)</f>
-        <v/>
-      </c>
-      <c r="F503" s="15">
-        <f>MIN(0,E503-MAX($E$13:E503))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="504">
-      <c r="E504" s="4">
-        <f>IF(OR(Trades!M493="WIN",Trades!M493="LOSS"),E503+Trades!N493,E503)</f>
-        <v/>
-      </c>
-      <c r="F504" s="15">
-        <f>MIN(0,E504-MAX($E$13:E504))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="505">
-      <c r="E505" s="4">
-        <f>IF(OR(Trades!M494="WIN",Trades!M494="LOSS"),E504+Trades!N494,E504)</f>
-        <v/>
-      </c>
-      <c r="F505" s="15">
-        <f>MIN(0,E505-MAX($E$13:E505))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="506">
-      <c r="E506" s="4">
-        <f>IF(OR(Trades!M495="WIN",Trades!M495="LOSS"),E505+Trades!N495,E505)</f>
-        <v/>
-      </c>
-      <c r="F506" s="15">
-        <f>MIN(0,E506-MAX($E$13:E506))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="507">
-      <c r="E507" s="4">
-        <f>IF(OR(Trades!M496="WIN",Trades!M496="LOSS"),E506+Trades!N496,E506)</f>
-        <v/>
-      </c>
-      <c r="F507" s="15">
-        <f>MIN(0,E507-MAX($E$13:E507))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="508">
-      <c r="E508" s="4">
-        <f>IF(OR(Trades!M497="WIN",Trades!M497="LOSS"),E507+Trades!N497,E507)</f>
-        <v/>
-      </c>
-      <c r="F508" s="15">
-        <f>MIN(0,E508-MAX($E$13:E508))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="509">
-      <c r="E509" s="4">
-        <f>IF(OR(Trades!M498="WIN",Trades!M498="LOSS"),E508+Trades!N498,E508)</f>
-        <v/>
-      </c>
-      <c r="F509" s="15">
-        <f>MIN(0,E509-MAX($E$13:E509))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="510">
-      <c r="E510" s="4">
-        <f>IF(OR(Trades!M499="WIN",Trades!M499="LOSS"),E509+Trades!N499,E509)</f>
-        <v/>
-      </c>
-      <c r="F510" s="15">
-        <f>MIN(0,E510-MAX($E$13:E510))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="511">
-      <c r="E511" s="4">
-        <f>IF(OR(Trades!M500="WIN",Trades!M500="LOSS"),E510+Trades!N500,E510)</f>
-        <v/>
-      </c>
-      <c r="F511" s="15">
-        <f>MIN(0,E511-MAX($E$13:E511))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="512">
-      <c r="E512" s="4">
-        <f>IF(OR(Trades!M501="WIN",Trades!M501="LOSS"),E511+Trades!N501,E511)</f>
-        <v/>
-      </c>
-      <c r="F512" s="15">
-        <f>MIN(0,E512-MAX($E$13:E512))</f>
+      <c r="A501" t="n">
+        <v>500</v>
+      </c>
+      <c r="B501" s="4">
+        <f>IF(OR(Trades!M501="WIN",Trades!M501="LOSS"),B500+Trades!N501,B500)</f>
+        <v/>
+      </c>
+      <c r="C501" s="20">
+        <f>MIN(0,B501-MAX($B$2:B501))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A25:F25"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
